--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>438.12</v>
+        <v>631.67</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>423.33</v>
+        <v>606.47</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>428.5</v>
+        <v>631.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>428.3</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>619.37</v>
+        <v>20.31</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>594.65</v>
+        <v>17.65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>632.5</v>
+        <v>20.18</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>636</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1095.37</v>
+        <v>777.17</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1040.47</v>
+        <v>747.67</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1109.9</v>
+        <v>765.65</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1085.5</v>
+        <v>764.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3407.33</v>
+        <v>181.7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3250.5</v>
+        <v>171.51</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3383.7</v>
+        <v>185.11</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3375</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>ANDHRAPAP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.23</v>
+        <v>74.16</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>16.4</v>
+        <v>69.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19.57</v>
+        <v>71.64</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.8</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>181.7</v>
+        <v>16.99</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>171.51</v>
+        <v>14.25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>185.11</v>
+        <v>15.27</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>184.5</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>73.01000000000001</v>
+        <v>1076.62</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>68.63</v>
+        <v>1076.59</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>73.36</v>
+        <v>1076.87</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>1076.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>ARCL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15.36</v>
+        <v>250.15</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>12.87</v>
+        <v>241.8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>16.87</v>
+        <v>262.39</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16.87</v>
+        <v>262.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1076.35</v>
+        <v>840.23</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1076.32</v>
+        <v>790.45</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1076.74</v>
+        <v>838.55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1076.74</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARCL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>240.99</v>
+        <v>697.8200000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>228.67</v>
+        <v>672.33</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>249.9</v>
+        <v>698.65</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>249.9</v>
+        <v>698</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1645</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1598.57</v>
+        <v>593.95</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1656</v>
+        <v>597.15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1656</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>681.33</v>
+        <v>120.57</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>664.33</v>
+        <v>118.88</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>680.85</v>
+        <v>121.12</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>686</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>BALAXI</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>180.44</v>
+        <v>24.62</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>170.3</v>
+        <v>22.83</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>176.41</v>
+        <v>23.12</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>179.82</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>177.22</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>593.95</v>
+        <v>170.83</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>597.15</v>
+        <v>172.45</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>597.09</v>
+        <v>172.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>120.57</v>
+        <v>393.32</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>118.88</v>
+        <v>365.13</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>121.12</v>
+        <v>377.95</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>120.8</v>
+        <v>385.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BIRLAPREC</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1845.27</v>
+        <v>61.6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1819.17</v>
+        <v>56.72</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1831.1</v>
+        <v>58.36</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1831.1</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BIOFILCHEM</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>35.9</v>
+        <v>38.61</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>31.69</v>
+        <v>35.14</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>34.51</v>
+        <v>37.86</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>374.95</v>
+        <v>1079.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>349.55</v>
+        <v>1079.27</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>392.35</v>
+        <v>1079.56</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>393.35</v>
+        <v>1079.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC</t>
+          <t>CFEL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>59.43</v>
+        <v>49.53</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>54.53</v>
+        <v>43.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.43</v>
+        <v>47.41</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>61.49</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CORDELIA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1518.03</v>
+        <v>113.09</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1457.1</v>
+        <v>107.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1558</v>
+        <v>112.33</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1558</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>2256.07</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>62.46</v>
+        <v>2144.7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>65.69</v>
+        <v>2217.9</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>66.38</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1079.03</v>
+        <v>186.83</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1079.01</v>
+        <v>175.78</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1079.43</v>
+        <v>179.89</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1079.43</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CENTEXT</t>
+          <t>DAVANGERE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>22.79</v>
+        <v>2.11</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>21.69</v>
+        <v>1.95</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>22.37</v>
+        <v>2.24</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>22.48</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CFEL</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>44.81</v>
+        <v>369.35</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>38.12</v>
+        <v>349.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>49.3</v>
+        <v>387.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>49.41</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CORDELIA</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>110.85</v>
+        <v>21</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>104.99</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>112.85</v>
+        <v>21.42</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>112.95</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>ELITECON</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>182.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>172.54</v>
+        <v>7.8</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>186.68</v>
+        <v>8.57</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>187.5</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DECNGOLD</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>231.47</v>
+        <v>2000.43</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>219.43</v>
+        <v>1945.57</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>229.73</v>
+        <v>1993</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>230.1</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>43.36</v>
+        <v>2.29</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>37.56</v>
+        <v>2.23</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46.08</v>
+        <v>2.38</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45.51</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>ESDS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>353.65</v>
+        <v>1716.83</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>334.4</v>
+        <v>1531.23</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>369.05</v>
+        <v>1824.7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>369.05</v>
+        <v>1827.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>62.84</v>
+        <v>26.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>55.44</v>
+        <v>24.18</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>68.42</v>
+        <v>26.15</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>67.7</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20.46</v>
+        <v>11.53</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20.46</v>
+        <v>10.88</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>21</v>
+        <v>11.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>21</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>62.48</v>
+        <v>1346.87</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>57.87</v>
+        <v>1303.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>64</v>
+        <v>1348</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>64</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EIFFL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>275.73</v>
+        <v>164.15</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>272.13</v>
+        <v>159.95</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>281.2</v>
+        <v>161.18</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>281.2</v>
+        <v>161.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>GRAVISSHO</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>372.55</v>
+        <v>41.75</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>345.27</v>
+        <v>37.06</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>380.2</v>
+        <v>46.97</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>380</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>GSLSU</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1975.3</v>
+        <v>28.75</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1917.53</v>
+        <v>26.98</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1978.9</v>
+        <v>28</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1975.1</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EMMVEE</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>343.7</v>
+        <v>2.25</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>329.82</v>
+        <v>2.25</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>346</v>
+        <v>2.29</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>344.8</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>2.2</v>
+        <v>1077.66</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2.14</v>
+        <v>1077.6</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2.28</v>
+        <v>1077.91</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2.29</v>
+        <v>1077.91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1353.97</v>
+        <v>26.35</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1326.03</v>
+        <v>25.35</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1355.5</v>
+        <v>27.44</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1358</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>INCREDIBLE</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1434.33</v>
+        <v>33.82</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1324.07</v>
+        <v>31.04</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1424</v>
+        <v>33.46</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1430.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FOSECOIND</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6280.67</v>
+        <v>16.54</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>6063.33</v>
+        <v>15.65</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>6194.5</v>
+        <v>16.9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6222</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>37.56</v>
+        <v>1063.87</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>31.33</v>
+        <v>1042.9</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>42.7</v>
+        <v>1077</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>42.7</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>INNOVANA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2.21</v>
+        <v>328.68</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2.21</v>
+        <v>300.83</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2.25</v>
+        <v>306.1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2.25</v>
+        <v>303.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1077.4</v>
+        <v>325.75</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1077.34</v>
+        <v>319.61</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1077.78</v>
+        <v>325.36</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1077.78</v>
+        <v>324.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HISARMETAL</t>
+          <t>ITETF</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>160.95</v>
+        <v>31.5</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>154.27</v>
+        <v>30.78</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>157.2</v>
+        <v>31.37</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>157.2</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IKIO</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>234.19</v>
+        <v>8.98</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>219.98</v>
+        <v>8.09</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>223.87</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>223</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>16.54</v>
+        <v>1022.35</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>15.65</v>
+        <v>945.0700000000001</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>16.9</v>
+        <v>1044.3</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>16.84</v>
+        <v>1031.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>INNOVANA</t>
+          <t>KAMANWALA</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>319.88</v>
+        <v>17.52</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>298.18</v>
+        <v>16.12</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>330.55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1378.47</v>
+        <v>12.13</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1378.47</v>
+        <v>11.93</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1405.8</v>
+        <v>12.6</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1405.8</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>KOTYARK</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>134.16</v>
+        <v>32.76</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>128.52</v>
+        <v>30.82</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>135.46</v>
+        <v>32.49</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>135.98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>709.65</v>
+        <v>420.33</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>660.58</v>
+        <v>417.32</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>723.15</v>
+        <v>419.5</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>725</v>
+        <v>420.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>11.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>11.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>12.01</v>
+        <v>0.08</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>12.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>KHADIM</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>123.1</v>
+        <v>42.85</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>119.32</v>
+        <v>40.22</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>121.01</v>
+        <v>44.4</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>121.01</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KOTARISUG</t>
+          <t>KUANTUM</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>29.82</v>
+        <v>78.88</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>28.2</v>
+        <v>75.05</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>28.57</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>28.7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>LIBAS</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>419.65</v>
+        <v>11.41</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>416.15</v>
+        <v>10.37</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>419.95</v>
+        <v>11.43</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>418</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1144.49</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1144.44</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.08</v>
+        <v>1144.75</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.08</v>
+        <v>1144.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>41.08</v>
+        <v>1007.78</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>38.19</v>
+        <v>1007.73</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>42.4</v>
+        <v>1008.02</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>42.6</v>
+        <v>1008.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KWIL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>42.62</v>
+        <v>1098.56</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>40.54</v>
+        <v>1098.32</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>43.04</v>
+        <v>1098.82</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>43.3</v>
+        <v>1098.83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LADDERUP</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>63.49</v>
+        <v>115.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>57.28</v>
+        <v>115.88</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>74.31</v>
+        <v>115.92</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>74.31</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1144.21</v>
+        <v>1102.94</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1144.16</v>
+        <v>1102.92</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1144.6</v>
+        <v>1103.18</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1144.59</v>
+        <v>1103.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1098.29</v>
+        <v>1121.2</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1098.09</v>
+        <v>1121.18</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1098.68</v>
+        <v>1121.45</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1098.68</v>
+        <v>1121.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>115.88</v>
+        <v>240.71</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>115.86</v>
+        <v>220.85</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>115.91</v>
+        <v>234.2</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>115.92</v>
+        <v>229.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1120.94</v>
+        <v>297.75</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1120.92</v>
+        <v>288.62</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1121.3</v>
+        <v>294.9</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1121.3</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>207.93</v>
+        <v>567.38</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>198.08</v>
+        <v>539.17</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>209.27</v>
+        <v>568.9</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>209.5</v>
+        <v>566</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MAHAPEXLTD</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>56.72</v>
+        <v>330.66</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>52.11</v>
+        <v>330.66</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>54.57</v>
+        <v>346.92</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>54.26</v>
+        <v>346.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>715.0700000000001</v>
+        <v>292.1</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>683.1799999999999</v>
+        <v>273.43</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>728.9</v>
+        <v>278.14</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>730</v>
+        <v>278.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>71.8</v>
+        <v>480.57</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>67.17</v>
+        <v>443.25</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>70.95</v>
+        <v>457.7</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>71.7</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MANGALAM</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>35.04</v>
+        <v>42.18</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>31.11</v>
+        <v>38.01</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>36.46</v>
+        <v>44.94</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>36.4</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>NAGREEKCAP</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>294.82</v>
+        <v>25.26</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>285.77</v>
+        <v>22.8</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>295.95</v>
+        <v>27.38</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>298.4</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>560.8200000000001</v>
+        <v>224.68</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>535.5</v>
+        <v>222.19</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>560.45</v>
+        <v>224.96</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>559</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>NIMBSPROJ</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>314.92</v>
+        <v>167.52</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>314.92</v>
+        <v>161.17</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>330.4</v>
+        <v>170</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>330.4</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>220.56</v>
+        <v>33.11</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>212.5</v>
+        <v>30.99</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>217.08</v>
+        <v>33.15</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>219.44</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MERCURYEV</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>41.53</v>
+        <v>1616.67</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>38.48</v>
+        <v>1548.33</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>41.86</v>
+        <v>1599.6</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>41.65</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>282.18</v>
+        <v>17</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>268.11</v>
+        <v>15.88</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>292.77</v>
+        <v>16.62</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>292.77</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1496.57</v>
+        <v>84.45</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1258.07</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1438.2</v>
+        <v>84.47</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1406.7</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2382.47</v>
+        <v>1.72</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2240.47</v>
+        <v>1.72</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2373</v>
+        <v>1.75</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2387.3</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>NICCOPAR</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>81.83</v>
+        <v>63.86</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>78.94</v>
+        <v>59.25</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>83</v>
+        <v>61.38</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>83</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>224.68</v>
+        <v>53.19</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>222.19</v>
+        <v>50.1</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>224.96</v>
+        <v>52.72</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>225.54</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>161.64</v>
+        <v>159.28</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>151.51</v>
+        <v>152.36</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>165.25</v>
+        <v>165.82</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>165.43</v>
+        <v>165.87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>NITIRAJ</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>234.7</v>
+        <v>885.4</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>225.37</v>
+        <v>851.17</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>233.25</v>
+        <v>878.65</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>237</v>
+        <v>872.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NRBBEARING</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>510.67</v>
+        <v>1001.97</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>485.92</v>
+        <v>872.27</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>514.65</v>
+        <v>995.95</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>516.8</v>
+        <v>994</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>135.66</v>
+        <v>1.01</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>129.4</v>
+        <v>0.99</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>133.06</v>
+        <v>1.06</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>133.97</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>ROML</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>56.41</v>
+        <v>43.24</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>55.05</v>
+        <v>41.85</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>55.78</v>
+        <v>43</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>55.7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>32.45</v>
+        <v>1253.13</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>30.12</v>
+        <v>1192.7</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>32.76</v>
+        <v>1265.4</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>32.87</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>241.26</v>
+        <v>6.4</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>231.97</v>
+        <v>6.2</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>237</v>
+        <v>6.63</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>237.01</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ORIENTTECH</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>250.73</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>230.9</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>249.64</v>
+        <v>66.98</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>247.47</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>15.3</v>
+        <v>283.13</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>13.34</v>
+        <v>269.72</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>15.54</v>
+        <v>282.6</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>15.48</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>82.87</v>
+        <v>1055.69</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>79.17</v>
+        <v>1055.67</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>84.23</v>
+        <v>1055.95</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>83.98999999999999</v>
+        <v>1055.95</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>1.69</v>
+        <v>17.41</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.69</v>
+        <v>16.79</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1.72</v>
+        <v>17.23</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.72</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>61.75</v>
+        <v>19.38</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>57.65</v>
+        <v>18.47</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>62.97</v>
+        <v>20.29</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>63.4</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SHERVANI</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>271.68</v>
+        <v>348.67</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>266.05</v>
+        <v>318.67</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>269.1</v>
+        <v>349.5</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>269.1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>22.84</v>
+        <v>201.81</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>20.98</v>
+        <v>198.28</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>23.71</v>
+        <v>203.98</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>23.56</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>SINGERIND</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>52.19</v>
+        <v>77.05</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>48.99</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>52.88</v>
+        <v>74.98</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>53.01</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>906.13</v>
+        <v>230.76</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>806.33</v>
+        <v>216.32</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1002.8</v>
+        <v>233.41</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1003</v>
+        <v>239.69</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.97</v>
+        <v>461.18</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.95</v>
+        <v>437.1</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>1.01</v>
+        <v>474.95</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1.01</v>
+        <v>474.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>SOLARA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1787.3</v>
+        <v>761.12</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1687.63</v>
+        <v>699.5</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1845.2</v>
+        <v>715.8</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>1840</v>
+        <v>715.35</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>STLSTRINF</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>6.4</v>
+        <v>21.85</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>6.2</v>
+        <v>20.1</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>6.63</v>
+        <v>25.44</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>6.63</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>20.95</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>19.38</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>65.67</v>
+        <v>20.44</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>65.67</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SUMEDHA</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>283.13</v>
+        <v>43.65</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>269.72</v>
+        <v>40.04</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>282.6</v>
+        <v>43.09</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>284.65</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>1055.43</v>
+        <v>1578.4</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>1055.41</v>
+        <v>1530.87</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1055.8</v>
+        <v>1575.9</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1055.8</v>
+        <v>1575.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>THEJO</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>2938.1</v>
+        <v>2233.97</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2838.63</v>
+        <v>2153.1</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>2906.2</v>
+        <v>2175.2</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>2919.7</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>TRACXN</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>446.25</v>
+        <v>31.62</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>428.15</v>
+        <v>29.01</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>468.15</v>
+        <v>31.21</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>468.15</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SHANKESH</t>
+          <t>TUTIALKA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>105.3</v>
+        <v>60.04</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>97.48</v>
+        <v>57.63</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>101.3</v>
+        <v>59.78</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>101.3</v>
+        <v>59.85</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>18.49</v>
+        <v>941.63</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>17.64</v>
+        <v>933.52</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>19.37</v>
+        <v>939.25</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>19.37</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SHIVATEX</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>183.32</v>
+        <v>395.92</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>169.81</v>
+        <v>360.9</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>178.05</v>
+        <v>388.35</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>179.99</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SIKA</t>
+          <t>VENTIVE</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1063.18</v>
+        <v>577.97</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>989.72</v>
+        <v>559.78</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1085.55</v>
+        <v>563.15</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1084</v>
+        <v>562</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>VGCL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>201.81</v>
+        <v>51.42</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>198.28</v>
+        <v>49.06</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>203.98</v>
+        <v>51.5</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>204</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>VGL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>2346.6</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>2284.7</v>
+        <v>57.72</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2354</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>2340</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SMSPHARMA</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>435.9</v>
+        <v>0.51</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>407.87</v>
+        <v>0.44</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>463.45</v>
+        <v>0.68</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>466</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SOLARA</t>
+          <t>VISHAL</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>739.1</v>
+        <v>19.27</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>691.8200000000001</v>
+        <v>17.95</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>749.15</v>
+        <v>18.35</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>749.85</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SSDL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>66.11</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>58.65</v>
+        <v>85.33</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>62.59</v>
+        <v>91.45</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>62.25</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>WSTCSTPAPR</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>195.44</v>
+        <v>723.73</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>191.33</v>
+        <v>688</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>195.14</v>
+        <v>713.3</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>195.02</v>
+        <v>714</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>ZFCVINDIA</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,538 +3741,16 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>34.89</v>
+        <v>2551.6</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>33.3</v>
+        <v>2477.83</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>36.6</v>
+        <v>2511.5</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>SUMEDHA</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>SWANDEF</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>2681.33</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>2556.93</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>2727.9</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>SYSTMTXC</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>71.12</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>71.12</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>72.53</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>TAALTECH</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>5253</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>4854.67</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>5375.5</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>5408</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>TAMBOLIIN</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>300.18</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>286.87</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>306.85</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>1544.33</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>1504.9</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>1541</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>TECHNOCRAF</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>443.1</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>412.17</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>442.3</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>437.5</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>THEJO</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>2209.23</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>2131.23</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>2192.6</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>VEDAVAAG</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>23.38</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>VELJAN</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>1924.33</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>1855.33</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>VGL</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>61.03</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>65.20999999999999</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>WABAG</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>2243.77</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>2097.57</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>2277.9</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>87.45999999999999</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>83.55</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>87.51000000000001</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>87.45</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>WSTCSTPAPR</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>707.5700000000001</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>674.05</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>713.8</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>714.85</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>ZFCVINDIA</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>2537.4</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>2461.63</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>2548.2</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>2536.1</v>
+        <v>2514</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>3IINFOLTD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>631.67</v>
+        <v>24.02</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>606.47</v>
+        <v>22.53</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>631.6</v>
+        <v>25.02</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>635.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.31</v>
+        <v>4.38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17.65</v>
+        <v>4.23</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>20.18</v>
+        <v>4.49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>20.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>777.17</v>
+        <v>181.7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>747.67</v>
+        <v>171.51</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>765.65</v>
+        <v>185.11</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>764.1</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>181.7</v>
+        <v>1076.89</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>171.51</v>
+        <v>1076.87</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>185.11</v>
+        <v>1077.02</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>184.5</v>
+        <v>1077.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ANDHRAPAP</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>74.16</v>
+        <v>833.77</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>69.8</v>
+        <v>807.53</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>71.64</v>
+        <v>825.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>71.02</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>16.99</v>
+        <v>81.98</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>14.25</v>
+        <v>77.73</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>15.27</v>
+        <v>80.45</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15.47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1076.62</v>
+        <v>885.1799999999999</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1076.59</v>
+        <v>807.42</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1076.87</v>
+        <v>907.45</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1076.89</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ARCL</t>
+          <t>ARTNIRMAN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>250.15</v>
+        <v>40.39</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>241.8</v>
+        <v>38.74</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>262.39</v>
+        <v>39.97</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>262.39</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>ASMS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>840.23</v>
+        <v>7.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>790.45</v>
+        <v>6.76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>838.55</v>
+        <v>6.86</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>838</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>697.8200000000001</v>
+        <v>622.67</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>672.33</v>
+        <v>597.05</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>698.65</v>
+        <v>620.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>698</v>
+        <v>621.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,7 +856,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BALAXI</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>24.62</v>
+        <v>305.97</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>22.83</v>
+        <v>303.7</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>23.12</v>
+        <v>309</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>23</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BANKIETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>177.22</v>
+        <v>58.47</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>170.83</v>
+        <v>57.36</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>172.45</v>
+        <v>57.75</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>172.45</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>393.32</v>
+        <v>97.86</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>365.13</v>
+        <v>90.56</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>377.95</v>
+        <v>97.62</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>385.5</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>61.6</v>
+        <v>1079.57</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>56.72</v>
+        <v>1079.54</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>58.36</v>
+        <v>1079.68</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>58.36</v>
+        <v>1079.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>38.61</v>
+        <v>386.73</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>35.14</v>
+        <v>370.4</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>37.86</v>
+        <v>386.8</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>37.8</v>
+        <v>385.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1079.3</v>
+        <v>1848.87</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1079.27</v>
+        <v>1800.33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1079.56</v>
+        <v>1860</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1079.57</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CFEL</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>49.53</v>
+        <v>140.81</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>43.12</v>
+        <v>133.59</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>47.41</v>
+        <v>140.77</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>47.29</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CORDELIA</t>
+          <t>DHARMAJ</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>113.09</v>
+        <v>271.38</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>107.03</v>
+        <v>264.63</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>112.33</v>
+        <v>269.4</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>112</v>
+        <v>270.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2256.07</v>
+        <v>2.62</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2144.7</v>
+        <v>2.5</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2217.9</v>
+        <v>2.66</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2235</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>186.83</v>
+        <v>21.42</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>175.78</v>
+        <v>21.42</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>179.89</v>
+        <v>21.84</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>180</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DAVANGERE</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>369.35</v>
+        <v>589.3200000000001</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>349.4</v>
+        <v>540.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>387.5</v>
+        <v>642.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>387.5</v>
+        <v>626.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>21</v>
+        <v>352.82</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>21</v>
+        <v>339.6</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>21.42</v>
+        <v>350.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>21.42</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ELITECON</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>50.49</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.8</v>
+        <v>49</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8.57</v>
+        <v>50.81</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.58</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>FINKURVE</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2000.43</v>
+        <v>76.91</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1945.57</v>
+        <v>69.22</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1993</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2005</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ESDS</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1716.83</v>
+        <v>129.36</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1531.23</v>
+        <v>123.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1824.7</v>
+        <v>128.89</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1827.4</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.06</v>
+        <v>110.79</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>24.18</v>
+        <v>110.75</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>26.15</v>
+        <v>110.76</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>26.79</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>11.53</v>
+        <v>486.95</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>10.88</v>
+        <v>467.32</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>11.7</v>
+        <v>482.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11.7</v>
+        <v>488.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1346.87</v>
+        <v>2.29</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1303.3</v>
+        <v>2.29</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1348</v>
+        <v>2.33</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1350</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>164.15</v>
+        <v>1077.93</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>159.95</v>
+        <v>1077.91</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>161.18</v>
+        <v>1078.05</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>161.33</v>
+        <v>1078.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO</t>
+          <t>HINDADH</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>41.75</v>
+        <v>376.97</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>37.06</v>
+        <v>354.45</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46.97</v>
+        <v>378.45</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46.97</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>28.75</v>
+        <v>1964.33</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>26.98</v>
+        <v>1934.5</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>28</v>
+        <v>1962</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>27.82</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2.25</v>
+        <v>23.09</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2.25</v>
+        <v>20.62</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2.29</v>
+        <v>23.04</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2.29</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1077.66</v>
+        <v>27.46</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1077.6</v>
+        <v>26.55</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1077.91</v>
+        <v>28.79</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1077.91</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>26.35</v>
+        <v>16.54</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>25.35</v>
+        <v>15.65</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>27.44</v>
+        <v>16.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>27.44</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>INCREDIBLE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>33.82</v>
+        <v>263.58</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>31.04</v>
+        <v>258.33</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>33.46</v>
+        <v>264.15</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>33.5</v>
+        <v>264.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>IVALUE</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>16.54</v>
+        <v>233.01</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>15.65</v>
+        <v>222.98</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>16.9</v>
+        <v>230.45</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.84</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1063.87</v>
+        <v>147.65</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1042.9</v>
+        <v>143.55</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1077</v>
+        <v>147.66</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1077</v>
+        <v>147.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INNOVANA</t>
+          <t>JKIPL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>328.68</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>300.83</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>306.1</v>
+        <v>96.72</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>303.7</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ITAXIS</t>
+          <t>KARMAENG</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>325.75</v>
+        <v>41.29</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>319.61</v>
+        <v>37.28</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>325.36</v>
+        <v>38.72</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>324.35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ITETF</t>
+          <t>KIRLFER</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>31.5</v>
+        <v>470.98</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>30.78</v>
+        <v>460.33</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>31.37</v>
+        <v>470.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>31.36</v>
+        <v>473.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>8.98</v>
+        <v>259.79</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>8.09</v>
+        <v>232.38</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>260.86</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1022.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>945.0700000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1044.3</v>
+        <v>0.08</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1031.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KAMANWALA</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>17.52</v>
+        <v>3.68</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.12</v>
+        <v>3.51</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>17</v>
+        <v>3.83</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>12.13</v>
+        <v>44.68</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>11.93</v>
+        <v>42.1</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>12.61</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KOTYARK</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>32.76</v>
+        <v>1144.76</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>30.82</v>
+        <v>1144.72</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>32.49</v>
+        <v>1144.88</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>33</v>
+        <v>1144.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>420.33</v>
+        <v>1008.03</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>417.32</v>
+        <v>1007.98</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>419.5</v>
+        <v>1008.16</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>420.9</v>
+        <v>1008.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1098.82</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1098.58</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.08</v>
+        <v>1098.94</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.08</v>
+        <v>1098.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>42.85</v>
+        <v>115.93</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>40.22</v>
+        <v>115.91</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>44.4</v>
+        <v>115.93</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>44.52</v>
+        <v>115.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KUANTUM</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>78.88</v>
+        <v>1103.21</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>75.05</v>
+        <v>1103.19</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>75.98999999999999</v>
+        <v>1103.32</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>76</v>
+        <v>1103.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LIBAS</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>11.41</v>
+        <v>1121.46</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>10.37</v>
+        <v>1121.44</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>11.43</v>
+        <v>1121.58</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>11.5</v>
+        <v>1121.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1144.49</v>
+        <v>571.12</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1144.44</v>
+        <v>541.73</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1144.75</v>
+        <v>572.1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1144.76</v>
+        <v>571</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1007.78</v>
+        <v>45.08</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1007.73</v>
+        <v>42.54</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1008.02</v>
+        <v>49.43</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1008.02</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>MONQ50</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1098.56</v>
+        <v>242.79</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1098.32</v>
+        <v>211.07</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1098.82</v>
+        <v>275.28</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1098.83</v>
+        <v>275.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>NAGREEKCAP</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>115.9</v>
+        <v>26.94</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>115.88</v>
+        <v>23.83</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>115.92</v>
+        <v>27.79</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>115.93</v>
+        <v>28.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1102.94</v>
+        <v>224.68</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1102.92</v>
+        <v>222.19</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1103.18</v>
+        <v>224.96</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1103.2</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1121.2</v>
+        <v>62.41</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1121.18</v>
+        <v>61.03</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1121.45</v>
+        <v>63</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1121.46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>ONIDA</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>240.71</v>
+        <v>33.54</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>220.85</v>
+        <v>31.99</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>234.2</v>
+        <v>33.05</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>229.4</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>297.75</v>
+        <v>49.39</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>288.62</v>
+        <v>47.51</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>294.9</v>
+        <v>51.81</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>290.55</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>ORCHASP</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>567.38</v>
+        <v>1.61</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>539.17</v>
+        <v>1.44</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>568.9</v>
+        <v>1.6</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>566</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>330.66</v>
+        <v>324.3</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>330.66</v>
+        <v>310.07</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>346.92</v>
+        <v>320.45</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>346.92</v>
+        <v>321.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>292.1</v>
+        <v>163.62</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>273.43</v>
+        <v>156.13</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>278.14</v>
+        <v>164.29</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>278.14</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>QUINT</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>480.57</v>
+        <v>49.2</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>443.25</v>
+        <v>45.79</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>457.7</v>
+        <v>57.88</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>456</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>42.18</v>
+        <v>5</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>38.01</v>
+        <v>4.67</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>44.94</v>
+        <v>5.19</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>44.94</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKCAP</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>25.26</v>
+        <v>1321.4</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>22.8</v>
+        <v>1206.83</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>27.38</v>
+        <v>1349.9</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>27.39</v>
+        <v>1349.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>224.68</v>
+        <v>30.01</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>222.19</v>
+        <v>29.01</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>224.96</v>
+        <v>29.92</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>225.54</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>167.52</v>
+        <v>6.4</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>161.17</v>
+        <v>6.2</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>170</v>
+        <v>6.63</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>170</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>33.11</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>30.99</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>33.15</v>
+        <v>68.31</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>33.4</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>1616.67</v>
+        <v>283.13</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1548.33</v>
+        <v>269.72</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1599.6</v>
+        <v>282.6</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1614</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>17</v>
+        <v>1055.95</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>15.88</v>
+        <v>1055.93</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>16.62</v>
+        <v>1056.07</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>16.62</v>
+        <v>1056.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>84.45</v>
+        <v>20.33</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>81.29000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>84.47</v>
+        <v>21.22</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>84.20999999999999</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SIEL</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.72</v>
+        <v>31.49</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.72</v>
+        <v>29.37</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.75</v>
+        <v>31.5</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.75</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>63.86</v>
+        <v>201.81</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>59.25</v>
+        <v>198.28</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>61.38</v>
+        <v>203.98</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>61.7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>SRD</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>53.19</v>
+        <v>39.86</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>50.1</v>
+        <v>38.36</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>52.72</v>
+        <v>40.09</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>52.75</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>159.28</v>
+        <v>941.63</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>152.36</v>
+        <v>933.52</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>165.82</v>
+        <v>939.25</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>165.87</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>VETO</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>885.4</v>
+        <v>128.66</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>851.17</v>
+        <v>124.7</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>878.65</v>
+        <v>127.94</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>872.25</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1001.97</v>
+        <v>0.51</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>872.27</v>
+        <v>0.44</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>995.95</v>
+        <v>0.68</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>994</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RCOM</t>
+          <t>VMSTMT</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,915 +2842,16 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1.01</v>
+        <v>47.83</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.99</v>
+        <v>45.56</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1.06</v>
+        <v>50.57</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>ROML</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>41.85</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>ROSSTECH</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>1253.13</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>1192.7</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>1265.4</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>66.98</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>1055.69</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>1055.67</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1055.95</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>1055.95</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SETCO</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>17.41</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>17.45</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SHEKHAWATI</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>20.32</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SHERVANI</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>348.67</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>318.67</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>349.5</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>SINGERIND</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>77.05</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>72.01000000000001</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>SMARTLINK</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>230.76</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>216.32</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>233.41</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>239.69</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>SOFTTECH</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>461.18</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>437.1</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>474.95</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>474.9</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SOLARA</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>761.12</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>699.5</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>715.8</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>715.35</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>STLSTRINF</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>25.44</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>25.44</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SUBEXLTD</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>20.53</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SUMEDHA</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>42.95</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>1578.4</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>1530.87</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>1575.9</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>1575.9</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>THEJO</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>2233.97</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>2153.1</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>2175.2</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>TRACXN</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>30.61</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>TUTIALKA</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>59.85</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>VALIANTORG</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>395.92</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>360.9</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>388.35</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>VENTIVE</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>577.97</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>559.78</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>563.15</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>VGCL</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>VGL</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>66.04000000000001</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>57.72</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>66.20999999999999</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>66.3</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>VISHAL</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>19.27</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>18.36</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>89.93000000000001</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>85.33</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>91.45</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>91.5</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>WSTCSTPAPR</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>723.73</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>688</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>713.3</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>ZFCVINDIA</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>2551.6</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>2477.83</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>2511.5</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>2514</v>
+        <v>50.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>24.02</v>
+        <v>25.03</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>22.53</v>
+        <v>23.62</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>25.02</v>
+        <v>25.76</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>25</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4.38</v>
+        <v>181.7</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4.23</v>
+        <v>171.51</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4.49</v>
+        <v>185.11</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4.5</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>181.7</v>
+        <v>1077.03</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>171.51</v>
+        <v>1077.01</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>185.11</v>
+        <v>1077.17</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>184.5</v>
+        <v>1077.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1076.89</v>
+        <v>845.52</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1076.87</v>
+        <v>814.33</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1077.02</v>
+        <v>826</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1077.03</v>
+        <v>827.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>ARIES</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>833.77</v>
+        <v>484.3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>807.53</v>
+        <v>459.85</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>825.3</v>
+        <v>477.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>827</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.98</v>
+        <v>15.49</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>77.73</v>
+        <v>13.74</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>80.45</v>
+        <v>15.87</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>80</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>885.1799999999999</v>
+        <v>628.67</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>807.42</v>
+        <v>606.22</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>907.45</v>
+        <v>633.25</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>906</v>
+        <v>636.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ARTNIRMAN</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40.39</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>38.74</v>
+        <v>593.95</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39.97</v>
+        <v>597.15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.69</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASMS</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7.01</v>
+        <v>120.57</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>6.76</v>
+        <v>118.88</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6.86</v>
+        <v>121.12</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6.89</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>622.67</v>
+        <v>310.53</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>597.05</v>
+        <v>306.55</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>620.6</v>
+        <v>311</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>621.5</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>100.83</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>593.95</v>
+        <v>93.81</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>597.15</v>
+        <v>102.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>597.09</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>CCHHL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>120.57</v>
+        <v>12.83</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>118.88</v>
+        <v>12.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>121.12</v>
+        <v>12.86</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>120.8</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>CSM</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>305.97</v>
+        <v>100.78</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>303.7</v>
+        <v>88.86</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>309</v>
+        <v>102.64</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>309</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BANKIETF</t>
+          <t>DHARMAJ</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.47</v>
+        <v>272.72</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>57.36</v>
+        <v>266.72</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>57.75</v>
+        <v>271.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>57.84</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>97.86</v>
+        <v>21.84</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>90.56</v>
+        <v>21.84</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>97.62</v>
+        <v>22.27</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>98.98999999999999</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>EIHOTEL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1079.57</v>
+        <v>294.63</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1079.54</v>
+        <v>284.6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1079.68</v>
+        <v>299.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1079.68</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>386.73</v>
+        <v>2.48</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>370.4</v>
+        <v>2.4</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>386.8</v>
+        <v>2.5</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>385.3</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>EQUIPPP</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1848.87</v>
+        <v>24.21</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1800.33</v>
+        <v>22.76</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1860</v>
+        <v>24.39</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1860</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>140.81</v>
+        <v>419.85</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>133.59</v>
+        <v>407.97</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>140.77</v>
+        <v>418.6</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>141</v>
+        <v>418.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>271.38</v>
+        <v>51.75</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>264.63</v>
+        <v>49.84</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>269.4</v>
+        <v>52.29</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>270.7</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>FOSECOIND</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>21.42</v>
+        <v>6932.33</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>21.42</v>
+        <v>6305.83</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>21.84</v>
+        <v>6765.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>21.84</v>
+        <v>6731</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2.39</v>
+        <v>131.32</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.33</v>
+        <v>124.46</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2.48</v>
+        <v>127.17</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2.49</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>GLOBUSSPR</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>589.3200000000001</v>
+        <v>844.73</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>540.12</v>
+        <v>816.63</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>642.3</v>
+        <v>830.75</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>626.2</v>
+        <v>831</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>352.82</v>
+        <v>491.48</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>339.6</v>
+        <v>472.02</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>350.2</v>
+        <v>484.05</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>350</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>50.49</v>
+        <v>2.33</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>49</v>
+        <v>2.33</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>50.81</v>
+        <v>2.37</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>50.9</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FINKURVE</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>76.91</v>
+        <v>680.83</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>69.22</v>
+        <v>665.7</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>72.98999999999999</v>
+        <v>681.45</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>72.48</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.25</v>
+        <v>541.87</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.17</v>
+        <v>521.02</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.35</v>
+        <v>557</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.35</v>
+        <v>557</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>129.36</v>
+        <v>1078.06</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>123.2</v>
+        <v>1078.04</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>128.89</v>
+        <v>1078.18</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>128</v>
+        <v>1078.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>HINDADH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>110.79</v>
+        <v>381.65</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>110.75</v>
+        <v>362.85</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>110.76</v>
+        <v>376.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>110.77</v>
+        <v>375.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>486.95</v>
+        <v>28.81</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>467.32</v>
+        <v>27.88</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>482.95</v>
+        <v>29.65</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>488.95</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>INDIANCARD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.29</v>
+        <v>218.8</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2.29</v>
+        <v>206.69</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2.33</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2.33</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1077.93</v>
+        <v>1101.13</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1077.91</v>
+        <v>1057.37</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1078.05</v>
+        <v>1098.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1078.04</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HINDADH</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>376.97</v>
+        <v>16.54</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>354.45</v>
+        <v>15.65</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>378.45</v>
+        <v>16.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>381</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ISHANCH</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1964.33</v>
+        <v>49.23</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1934.5</v>
+        <v>44.21</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1962</v>
+        <v>49.43</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1962</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>23.09</v>
+        <v>265.87</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20.62</v>
+        <v>260.47</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>23.04</v>
+        <v>266.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>23.14</v>
+        <v>266.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>27.46</v>
+        <v>148.95</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>26.55</v>
+        <v>144.77</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>28.79</v>
+        <v>147.28</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>28.81</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>16.54</v>
+        <v>782.0700000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>15.65</v>
+        <v>758.85</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>16.9</v>
+        <v>791.85</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16.84</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>KIRLFER</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>263.58</v>
+        <v>473.85</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>258.33</v>
+        <v>464.15</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>264.15</v>
+        <v>474.35</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>264.15</v>
+        <v>475.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IVALUE</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>233.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>222.98</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>230.45</v>
+        <v>0.08</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>230.4</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>147.65</v>
+        <v>3.83</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>143.55</v>
+        <v>3.74</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>147.66</v>
+        <v>4.01</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>147.88</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>JKIPL</t>
+          <t>LAXMICOT</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>95.70999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>92.26000000000001</v>
+        <v>12.53</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>96.72</v>
+        <v>13.08</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>96.95</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>KARMAENG</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>41.29</v>
+        <v>1144.9</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>37.28</v>
+        <v>1144.88</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>38.72</v>
+        <v>1145.02</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>39</v>
+        <v>1145.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>KIRLFER</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>470.98</v>
+        <v>1008.16</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>460.33</v>
+        <v>1008.15</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>470.9</v>
+        <v>1008.29</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>473.65</v>
+        <v>1008.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>259.79</v>
+        <v>1098.95</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>232.38</v>
+        <v>1098.89</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>260.86</v>
+        <v>1099.06</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>261.5</v>
+        <v>1099.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>115.95</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>115.93</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.08</v>
+        <v>115.95</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.08</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.68</v>
+        <v>1103.34</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.51</v>
+        <v>1103.32</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.83</v>
+        <v>1103.47</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.83</v>
+        <v>1103.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>44.68</v>
+        <v>1121.6</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>42.1</v>
+        <v>1121.58</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46.52</v>
+        <v>1121.72</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46.62</v>
+        <v>1121.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LOTUSEYE</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1144.76</v>
+        <v>115.61</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1144.72</v>
+        <v>110.69</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1144.88</v>
+        <v>113.12</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1144.88</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1008.03</v>
+        <v>19.71</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1007.98</v>
+        <v>18.46</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1008.16</v>
+        <v>19.53</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1008.16</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1098.82</v>
+        <v>13236</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1098.58</v>
+        <v>12917</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1098.94</v>
+        <v>13151</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1098.95</v>
+        <v>13190</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>115.93</v>
+        <v>818.67</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>115.91</v>
+        <v>797.85</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>115.93</v>
+        <v>817</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>115.95</v>
+        <v>817</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>MASPTOP50</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1103.21</v>
+        <v>101.99</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1103.19</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1103.32</v>
+        <v>103.83</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1103.34</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>MATRIMONY</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1121.46</v>
+        <v>532.85</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1121.44</v>
+        <v>503.53</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1121.58</v>
+        <v>530.8</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1121.58</v>
+        <v>522.7</v>
       </c>
     </row>
     <row r="56">
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>571.12</v>
+        <v>576.45</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>541.73</v>
+        <v>551.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>572.1</v>
+        <v>577.6</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="57">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>45.08</v>
+        <v>48.76</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>42.54</v>
+        <v>47.84</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>49.43</v>
+        <v>51.9</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>49.43</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="58">
@@ -2146,16 +2146,16 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>242.79</v>
+        <v>280</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>211.07</v>
+        <v>237.11</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>275.28</v>
+        <v>330.25</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>275.67</v>
+        <v>330.33</v>
       </c>
     </row>
     <row r="59">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>26.94</v>
+        <v>28.23</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>23.83</v>
+        <v>25.33</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>27.79</v>
+        <v>27.92</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>28.23</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="60">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>62.41</v>
+        <v>63.43</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>61.03</v>
+        <v>62.69</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>63</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>63</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ONIDA</t>
+          <t>ONMOBILE</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>33.54</v>
+        <v>51.85</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>31.99</v>
+        <v>48.79</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>33.05</v>
+        <v>51.31</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>32.6</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ONMOBILE</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>49.39</v>
+        <v>333.4</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>47.51</v>
+        <v>313.48</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>51.81</v>
+        <v>334.95</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>51.81</v>
+        <v>334.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ORCHASP</t>
+          <t>PGHH</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.61</v>
+        <v>7664.5</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.44</v>
+        <v>7490</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1.6</v>
+        <v>7613</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1.62</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>324.3</v>
+        <v>2.82</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>310.07</v>
+        <v>2.61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>320.45</v>
+        <v>2.66</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>321.9</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>163.62</v>
+        <v>1260.3</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>156.13</v>
+        <v>1218.33</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>164.29</v>
+        <v>1272.7</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>165</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>QUINT</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>49.2</v>
+        <v>167.95</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45.79</v>
+        <v>160.03</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>57.88</v>
+        <v>168.92</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>57.88</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>QUINT</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>5</v>
+        <v>56.59</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>4.67</v>
+        <v>54.18</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>5.19</v>
+        <v>63.66</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>5.19</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>RACLGEAR</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1321.4</v>
+        <v>1889.9</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1206.83</v>
+        <v>1734.13</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1349.9</v>
+        <v>1829</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1349.9</v>
+        <v>1838.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RSSOFTWARE</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>30.01</v>
+        <v>4455.6</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>29.01</v>
+        <v>4333.47</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>29.92</v>
+        <v>4380</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>29.65</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>6.4</v>
+        <v>1476.57</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>6.2</v>
+        <v>1433.2</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>6.63</v>
+        <v>1473.4</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>6.63</v>
+        <v>1475.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SANGINITA</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>4.97</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>68.31</v>
+        <v>5.44</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>68.31</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>283.13</v>
+        <v>1385.03</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>269.72</v>
+        <v>1252.1</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>282.6</v>
+        <v>1357.2</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>284.65</v>
+        <v>1351.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>RRECL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1055.95</v>
+        <v>138.49</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1055.93</v>
+        <v>123.4</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>1056.07</v>
+        <v>144</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1056.09</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>RSSOFTWARE</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>20.33</v>
+        <v>30.22</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>19.3</v>
+        <v>29.49</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>21.22</v>
+        <v>30</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>21.3</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SIEL</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>31.49</v>
+        <v>6.4</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>29.37</v>
+        <v>6.2</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>31.5</v>
+        <v>6.63</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>31.5</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>SANGAMIND</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>201.81</v>
+        <v>579.65</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>198.28</v>
+        <v>557.48</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>203.98</v>
+        <v>583.05</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>204</v>
+        <v>585.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SRD</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>39.86</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>38.36</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>40.09</v>
+        <v>69.67</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>40.15</v>
+        <v>69.67</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>941.63</v>
+        <v>283.13</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>933.52</v>
+        <v>269.72</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>939.25</v>
+        <v>282.6</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>128.66</v>
+        <v>1719.73</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>124.7</v>
+        <v>1666.1</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>127.94</v>
+        <v>1766.9</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>128</v>
+        <v>1766.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,45 +2813,422 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.51</v>
+        <v>1056.09</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.44</v>
+        <v>1056.07</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.68</v>
+        <v>1056.2</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.68</v>
+        <v>1056.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SILVERETF</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>201.81</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SRD</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>STARTECK</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>253.98</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>237.45</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>237.55</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>1860.5</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1837.47</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1867.3</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>1867.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SUYOG</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>668.48</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>647.35</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>664.25</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>664.65</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>1013.37</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>991.27</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1013.7</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>1013.7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>594.0700000000001</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>560.1</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>VADILALIND</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>7184.5</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>6935.83</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>7101</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>VETO</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>132.53</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>133.02</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD-RE1</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>VMSTMT</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>45.56</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>50.57</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>50.69</v>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>50.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>39.82</v>
+        <v>35</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>38.82</v>
+        <v>32.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>39.77</v>
+        <v>36.05</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>33.76</v>
+        <v>713.38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>30.93</v>
+        <v>667.73</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>35</v>
+        <v>715.05</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>35.08</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>ADDIND</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>444.85</v>
+        <v>80.27</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>430.1</v>
+        <v>73.52</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>437.25</v>
+        <v>77.2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>438</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>ADOR</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>683.45</v>
+        <v>1644.63</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>646.37</v>
+        <v>1592.17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>712.15</v>
+        <v>1638.9</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>722</v>
+        <v>1630.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>483.42</v>
+        <v>247.74</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>463.68</v>
+        <v>239.96</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>491.4</v>
+        <v>246.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>493.85</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADFFOODS</t>
+          <t>AERONEU</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>270.65</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>261.48</v>
+        <v>70.67</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>271.65</v>
+        <v>80.22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>272</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADOR</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1621.63</v>
+        <v>20.67</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1581.03</v>
+        <v>19.3</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1612.9</v>
+        <v>21.38</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1610.1</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ADVANCE</t>
+          <t>AMBALALSA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>118.45</v>
+        <v>41.97</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>110.7</v>
+        <v>39.8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>118.67</v>
+        <v>41.09</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>118.69</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>242.01</v>
+        <v>181.7</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>234.88</v>
+        <v>171.51</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>242.79</v>
+        <v>185.11</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>243</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>536.73</v>
+        <v>1078.26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>509.97</v>
+        <v>1078.24</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>527.2</v>
+        <v>1078.58</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>527.55</v>
+        <v>1078.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AHLEAST</t>
+          <t>ARIHANTSUP</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>139.28</v>
+        <v>247.83</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>134.98</v>
+        <v>237.63</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>136.41</v>
+        <v>242.7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>136.1</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ALBERTDAVD</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>872.28</v>
+        <v>394.13</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>846.2</v>
+        <v>374.42</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>871.1</v>
+        <v>402.75</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>879.4</v>
+        <v>401.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>19.9</v>
+        <v>397.65</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>18.7</v>
+        <v>381.53</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>19.86</v>
+        <v>394.35</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>20.05</v>
+        <v>387.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40.89</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.2</v>
+        <v>593.95</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>41.27</v>
+        <v>597.15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>41.49</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>181.7</v>
+        <v>120.57</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>171.51</v>
+        <v>118.88</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>185.11</v>
+        <v>121.12</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>184.5</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AMRUTANJAN</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>511.98</v>
+        <v>343.25</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>497.67</v>
+        <v>343.25</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>510.2</v>
+        <v>350.05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>512.8</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>BANARBEADS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>627.1799999999999</v>
+        <v>122.03</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>607.6</v>
+        <v>113.67</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>624.1</v>
+        <v>123.86</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>622.55</v>
+        <v>123.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>BEDMUTHA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1077.98</v>
+        <v>108.67</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1077.95</v>
+        <v>101.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1078.16</v>
+        <v>110.71</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1078.17</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>APOLSINHOT</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1228.27</v>
+        <v>848.92</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1211.33</v>
+        <v>827.52</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1217.1</v>
+        <v>850.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1217.1</v>
+        <v>852.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>241.33</v>
+        <v>17.51</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>231.83</v>
+        <v>16.64</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>243.1</v>
+        <v>17.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>243.05</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>BLUECLOUDS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>980.5</v>
+        <v>21.38</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>955.75</v>
+        <v>19.76</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>965.4</v>
+        <v>22.16</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>964.15</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6185.83</v>
+        <v>142.42</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6084</v>
+        <v>132.51</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6135.5</v>
+        <v>145.12</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>6195</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>1805.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>593.95</v>
+        <v>1725.27</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>597.15</v>
+        <v>1811.6</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>597.09</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BPLPHARMA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>120.57</v>
+        <v>1682.83</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>118.88</v>
+        <v>1540.33</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>121.12</v>
+        <v>1898</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>120.8</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AXTEL</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>453.2</v>
+        <v>3079.07</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>431.55</v>
+        <v>2947.87</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>442.3</v>
+        <v>3002.6</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>444.95</v>
+        <v>3001.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>334.4</v>
+        <v>1080.95</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>334.4</v>
+        <v>1080.93</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>343.2</v>
+        <v>1081.27</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>343.2</v>
+        <v>1081.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>355.43</v>
+        <v>138.82</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>338.98</v>
+        <v>124.29</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>350.15</v>
+        <v>152.24</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>350.9</v>
+        <v>152.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BALAJEE</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>25.9</v>
+        <v>3.02</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>24.71</v>
+        <v>2.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>25.38</v>
+        <v>3.26</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>25.02</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2268.53</v>
+        <v>83.55</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2158.33</v>
+        <v>75.37</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2226</v>
+        <v>83.98</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2220</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>117.21</v>
+        <v>5.91</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>111.87</v>
+        <v>5.91</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>115.86</v>
+        <v>6.2</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>116.39</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BANSALWIRE</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>323.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>311.2</v>
+        <v>66.64</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>323.35</v>
+        <v>76.84</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>322</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>DHARMAJ</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>17.05</v>
+        <v>304</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>16.22</v>
+        <v>288.85</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>17.12</v>
+        <v>295.15</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17.13</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>20.02</v>
+        <v>13359.67</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.19</v>
+        <v>13119</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.06</v>
+        <v>13390</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>20.08</v>
+        <v>13390</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>135.1</v>
+        <v>305.32</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>126.61</v>
+        <v>289.9</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>140.56</v>
+        <v>305.35</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>139.2</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1760.57</v>
+        <v>23.62</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1708.07</v>
+        <v>23.62</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1730</v>
+        <v>24.09</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1728.1</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>EASTSILK</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1290.27</v>
+        <v>71.94</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1207.07</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1296.5</v>
+        <v>72</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1285</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>EIFFL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3035.03</v>
+        <v>266.47</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2927.1</v>
+        <v>264.93</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3004.8</v>
+        <v>271.7</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3015</v>
+        <v>271.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>EKI</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1080.65</v>
+        <v>96.84</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1080.63</v>
+        <v>82.59</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1080.84</v>
+        <v>100.99</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1080.85</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>331.85</v>
+        <v>42.16</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>318.18</v>
+        <v>39.59</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>339.8</v>
+        <v>42.86</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>338</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CHEMCON</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>231</v>
+        <v>2852.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>222.15</v>
+        <v>2797.03</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>228.08</v>
+        <v>2855.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>226.25</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CMLL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>506.65</v>
+        <v>660.92</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>486.58</v>
+        <v>638.3200000000001</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>506.25</v>
+        <v>671.55</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>506.2</v>
+        <v>672.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>COUNCODOS</t>
+          <t>FMGOETZE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6.46</v>
+        <v>472.05</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>6.17</v>
+        <v>451.82</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>6.38</v>
+        <v>482.6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6.4</v>
+        <v>481.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>GALAXYSURF</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3737.17</v>
+        <v>2276.57</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>3589.93</v>
+        <v>2203.83</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>3800.1</v>
+        <v>2261.3</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>3801</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CRAVATEX</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>366.22</v>
+        <v>1497.53</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>326.67</v>
+        <v>1464.33</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>361.45</v>
+        <v>1497.2</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>365</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>GMBREW</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>117.74</v>
+        <v>979.35</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>108.14</v>
+        <v>952.53</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>138.4</v>
+        <v>978.8</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>138.4</v>
+        <v>980</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>274.88</v>
+        <v>102.25</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>255.05</v>
+        <v>96.75</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>266.3</v>
+        <v>102.68</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>266</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.85</v>
+        <v>633.03</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.67</v>
+        <v>609.85</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.97</v>
+        <v>630.3</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.97</v>
+        <v>632</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>GOLDTECH</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>101.04</v>
+        <v>46.32</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>96.27</v>
+        <v>44.43</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>100.22</v>
+        <v>48.51</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>77.8</v>
+        <v>3202.07</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>3146.23</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>85.2</v>
+        <v>3191</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>85.2</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DEEPAKFERT</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1388.63</v>
+        <v>222.78</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1346.77</v>
+        <v>206.15</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1361.4</v>
+        <v>234.78</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1360</v>
+        <v>234.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>GVPTECH</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>5.57</v>
+        <v>7.86</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>5.42</v>
+        <v>7.43</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>5.91</v>
+        <v>7.94</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>5.91</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>69.27</v>
+        <v>1079.3</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>62.99</v>
+        <v>1079.28</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>72.68000000000001</v>
+        <v>1079.63</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>72.2</v>
+        <v>1079.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>26.96</v>
+        <v>237.25</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>26.26</v>
+        <v>227.58</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>26.52</v>
+        <v>248.5</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>26.65</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ</t>
+          <t>HERANBA</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>296.67</v>
+        <v>182.28</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>281.45</v>
+        <v>168.96</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>300.55</v>
+        <v>187.6</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>299.9</v>
+        <v>189.46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DIGIDRIVE</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>18.09</v>
+        <v>17.21</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>17.48</v>
+        <v>16.56</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>17.88</v>
+        <v>16.85</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>18.1</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>HIMATSEIDE</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>298.43</v>
+        <v>70.09</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>284.73</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>295.05</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>293.4</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DPWIRES</t>
+          <t>HITECHGEAR</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>159.99</v>
+        <v>589.42</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>153.73</v>
+        <v>566.3200000000001</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>170.02</v>
+        <v>618.35</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>170.01</v>
+        <v>618.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>INDGN</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>29.82</v>
+        <v>611.35</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>27.94</v>
+        <v>591.9299999999999</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>31.58</v>
+        <v>608.95</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>31.71</v>
+        <v>608.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>23.16</v>
+        <v>298.23</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>23.16</v>
+        <v>268.57</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>23.62</v>
+        <v>309.9</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>23.62</v>
+        <v>308</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DYNPRO</t>
+          <t>INDNIPPON</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>234.7</v>
+        <v>1323</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>228.81</v>
+        <v>1253.97</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>232.85</v>
+        <v>1318.2</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>233.17</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>INDOMIM</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>638.6799999999999</v>
+        <v>1319.47</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>603.67</v>
+        <v>1241.28</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>646.7</v>
+        <v>1275.95</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>645.9</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>69.20999999999999</v>
+        <v>16.54</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>15.65</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>71.8</v>
+        <v>16.9</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>71.93000000000001</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EIMCOELECO</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2319.2</v>
+        <v>85.3</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2246.97</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2304.4</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2312</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EKI</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>84.16</v>
+        <v>1451.8</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>73.03</v>
+        <v>1449.6</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>1480.6</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>1480.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ELITECON</t>
+          <t>ISTLTD</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>9.039999999999999</v>
+        <v>668.33</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>8.49</v>
+        <v>652.98</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>660</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>9.58</v>
+        <v>660</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>JAGSNPHARM</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>41.27</v>
+        <v>243.08</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>38.93</v>
+        <v>229.75</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>40.82</v>
+        <v>242.29</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>40.66</v>
+        <v>241.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1468.07</v>
+        <v>25.73</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1428.7</v>
+        <v>24.42</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1480</v>
+        <v>25.13</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1480</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FMGOETZE</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>459.28</v>
+        <v>138.26</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>443.55</v>
+        <v>130.36</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>468.45</v>
+        <v>138.2</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>467</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FRONTSP</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1390.8</v>
+        <v>795.12</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1265.73</v>
+        <v>740.85</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1510.4</v>
+        <v>846.4</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1490.1</v>
+        <v>846.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GALAPREC</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1135.5</v>
+        <v>969.63</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1059.43</v>
+        <v>923.17</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1117.1</v>
+        <v>974.25</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1114.2</v>
+        <v>978</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>KANORICHEM</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1035.67</v>
+        <v>191.16</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>996.7</v>
+        <v>176.73</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1014</v>
+        <v>198.55</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1009</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>1491.8</v>
+        <v>327.4</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1453</v>
+        <v>321.28</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1482.6</v>
+        <v>327.95</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1480</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GINNIFILA</t>
+          <t>KCP</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>43.11</v>
+        <v>161.33</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>41.44</v>
+        <v>156.02</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>42.39</v>
+        <v>163.29</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>42.8</v>
+        <v>162.74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GKB</t>
+          <t>KECL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>71.41</v>
+        <v>125.45</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>120.15</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>67.68000000000001</v>
+        <v>126.17</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>67.2</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GMBREW</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>970.77</v>
+        <v>197.44</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>946.03</v>
+        <v>188.37</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>967.25</v>
+        <v>206.58</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>967</v>
+        <v>206.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>99</v>
+        <v>793.52</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>94.28</v>
+        <v>727.22</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>101.41</v>
+        <v>804.55</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>101.1</v>
+        <v>814</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>620.65</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>597.77</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>625.1</v>
+        <v>0.08</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>626</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>404.27</v>
+        <v>139</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>385.5</v>
+        <v>125.78</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>404.75</v>
+        <v>144.57</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>406.25</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>LCCINFOTEC</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>230.64</v>
+        <v>4.03</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>220.64</v>
+        <v>3.9</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>224.98</v>
+        <v>4.23</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>223.65</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>LEMERITE</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>44.22</v>
+        <v>20.76</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>42.58</v>
+        <v>19.51</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>46.28</v>
+        <v>21.06</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>46.28</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>211.07</v>
+        <v>1723.03</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>198.41</v>
+        <v>1673.83</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>221.83</v>
+        <v>1725.4</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>222.25</v>
+        <v>1725.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2010.4</v>
+        <v>1009.32</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1929.03</v>
+        <v>1007.54</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1981</v>
+        <v>1009.64</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1994.9</v>
+        <v>1009.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.52</v>
+        <v>1100.16</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.52</v>
+        <v>1100.14</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.58</v>
+        <v>1100.48</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.58</v>
+        <v>1100.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HALDYNGL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>148.06</v>
+        <v>116.08</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>141.83</v>
+        <v>116.06</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>144.68</v>
+        <v>116.1</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>144.1</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HBSL</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>55.74</v>
+        <v>1104.61</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>53.71</v>
+        <v>1104.5</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>55.02</v>
+        <v>1104.95</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>55.9</v>
+        <v>1104.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1079.02</v>
+        <v>1122.81</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1078.94</v>
+        <v>1122.79</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1079.2</v>
+        <v>1123.13</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1079.19</v>
+        <v>1123.14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HEALTHADD</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>17.05</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>16.86</v>
+        <v>72.55</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>16.96</v>
+        <v>79.67</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>16.91</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>MAKERSL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>237.25</v>
+        <v>190.56</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>227.58</v>
+        <v>184.03</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>248.5</v>
+        <v>188.4</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>248.5</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>HERANBA</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>172.32</v>
+        <v>234.7</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>167.27</v>
+        <v>223.85</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>172.27</v>
+        <v>229.12</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>172.9</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>470.75</v>
+        <v>267.77</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>443.27</v>
+        <v>258.32</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>468.05</v>
+        <v>280.05</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>459</v>
+        <v>280.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>16.98</v>
+        <v>447.52</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>16.45</v>
+        <v>447.52</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>16.99</v>
+        <v>456.4</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>17</v>
+        <v>456.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>HIMATSEIDE</t>
+          <t>MCCHRLS-B</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>68.02</v>
+        <v>681.48</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>635.17</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>69.47</v>
+        <v>681</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>70.45</v>
+        <v>682</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>MICEL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>390.42</v>
+        <v>35.4</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>376.37</v>
+        <v>35.4</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>381.8</v>
+        <v>36.1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>380.25</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>MMWL</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>565.97</v>
+        <v>14.44</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>546.33</v>
+        <v>13.72</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>588.95</v>
+        <v>15.09</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>588.95</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>INDBANK</t>
+          <t>MODTHREAD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>26.59</v>
+        <v>48.12</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>25.52</v>
+        <v>46.07</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>26.23</v>
+        <v>47.32</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>26.35</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>INDNIPPON</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>1305.17</v>
+        <v>8551.5</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1239.7</v>
+        <v>8409</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1315.9</v>
+        <v>8584.5</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1317</v>
+        <v>8572</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>1256.95</v>
+        <v>13.72</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1174.7</v>
+        <v>13.72</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1311.15</v>
+        <v>14.39</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1314.45</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>405.93</v>
+        <v>224.68</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>385.52</v>
+        <v>222.19</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>401.25</v>
+        <v>224.96</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>397.3</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>16.54</v>
+        <v>284.17</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>15.65</v>
+        <v>266.67</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>16.9</v>
+        <v>288.6</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>16.84</v>
+        <v>288.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>NKIND</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>59.63</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>78.68000000000001</v>
+        <v>57.43</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>82.86</v>
+        <v>60.36</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>82.75</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>INTLCONV</t>
+          <t>NORBTEAEXP</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>77.22</v>
+        <v>65.12</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>80.04000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>80.13</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>1414.93</v>
+        <v>1713.03</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1410.6</v>
+        <v>1671.87</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1451.6</v>
+        <v>1681.4</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>1451.6</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>162.63</v>
+        <v>161.98</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>157.56</v>
+        <v>152.94</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>164.01</v>
+        <v>167.67</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>163.52</v>
+        <v>167.67</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>IVALUE</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>234.17</v>
+        <v>59.3</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>218.34</v>
+        <v>55.96</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>234.43</v>
+        <v>60.46</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>233</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>PERMAGN</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>66.63</v>
+        <v>849.33</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>63.67</v>
+        <v>834.1799999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>65.5</v>
+        <v>852.45</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>847</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>25.1</v>
+        <v>1331.17</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>24.25</v>
+        <v>1243.23</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>25.26</v>
+        <v>1329.1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>25.3</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>134.93</v>
+        <v>7.77</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>127.44</v>
+        <v>7.35</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>138.39</v>
+        <v>7.71</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>138.01</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>JNKINDIA</t>
+          <t>PLASTIBLEN</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>427.05</v>
+        <v>197.82</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>409.92</v>
+        <v>187.22</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>422.45</v>
+        <v>202.99</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>425</v>
+        <v>202.86</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>POWERICA</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>2211.53</v>
+        <v>582.0700000000001</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>2080.3</v>
+        <v>558.3200000000001</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>2160.3</v>
+        <v>582.95</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>2140</v>
+        <v>584.9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>PREMIER</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>641.55</v>
+        <v>2.97</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>623.62</v>
+        <v>2.73</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>635.35</v>
+        <v>2.8</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>634</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>PRIMESECU</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>743.58</v>
+        <v>303.03</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>690.25</v>
+        <v>292.2</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>806.1</v>
+        <v>301.9</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>806.1</v>
+        <v>303.05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>PRIORITY</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>18.2</v>
+        <v>303.55</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>17.08</v>
+        <v>258.35</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>18.07</v>
+        <v>311.73</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>18.14</v>
+        <v>311</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>KIRIINDUS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>572.78</v>
+        <v>3558.33</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>541.88</v>
+        <v>3458.27</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>559.9</v>
+        <v>3594.1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>561</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>KNAGRI</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>212.02</v>
+        <v>670.17</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>202.78</v>
+        <v>618.13</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>213.63</v>
+        <v>690.7</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>209.99</v>
+        <v>695</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>405.93</v>
+        <v>55.62</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>390.07</v>
+        <v>51.91</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>398.2</v>
+        <v>56.75</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>398.7</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>187.92</v>
+        <v>20.7</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>179.13</v>
+        <v>20.15</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>196.75</v>
+        <v>20.9</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>196.75</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>RAJTV</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>749.9299999999999</v>
+        <v>10.26</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>699.75</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>783.85</v>
+        <v>10.76</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>777</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1193.95</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1115.47</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.08</v>
+        <v>1196.65</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0.08</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>4.77</v>
+        <v>712.65</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>4.76</v>
+        <v>651.67</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>5.06</v>
+        <v>711.3</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>5.07</v>
+        <v>708</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>REMSONSIND</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>335.13</v>
+        <v>116.56</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>325.93</v>
+        <v>104.02</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>338.15</v>
+        <v>116.8</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>339.9</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>LAKSHMIMIL</t>
+          <t>RKEC</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>7919.67</v>
+        <v>23.14</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>7679</v>
+        <v>20.27</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>7780.5</v>
+        <v>24.26</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>7721</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>LALITHAA</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>347.83</v>
+        <v>1690.53</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>332.7</v>
+        <v>1644.77</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>370.5</v>
+        <v>1676.3</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>370.5</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>2038.67</v>
+        <v>6.4</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1994.5</v>
+        <v>6.2</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>2026.2</v>
+        <v>6.63</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>2026.2</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LCCINFOTEC</t>
+          <t>SADBHIN</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>3.83</v>
+        <v>2.65</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>3.68</v>
+        <v>2.56</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>4.03</v>
+        <v>2.65</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>4.03</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>SALSTEEL</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>20</v>
+        <v>89.34</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>18.75</v>
+        <v>85.97</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>20.59</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>19.83</v>
+        <v>93.63</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>SAMBANDAM</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>1709.6</v>
+        <v>107.13</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>1661.1</v>
+        <v>104.17</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>1697.7</v>
+        <v>111.83</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>1695.8</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>1056.54</v>
+        <v>283.13</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>1056.48</v>
+        <v>269.72</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>1056.71</v>
+        <v>282.6</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>1056.71</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>SAYAJIHOTL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>1145.98</v>
+        <v>327</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>1145.87</v>
+        <v>314.03</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>1146.08</v>
+        <v>327</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>1146.09</v>
+        <v>327</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>1099.88</v>
+        <v>1057.29</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>1099.86</v>
+        <v>1057.27</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1100.05</v>
+        <v>1057.62</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1100.05</v>
+        <v>1057.62</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>116.05</v>
+        <v>3325</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>116.03</v>
+        <v>3083.13</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>116.06</v>
+        <v>3444.9</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>116.06</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SGL</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>1122.53</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1122.51</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>1122.71</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>1122.72</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>SHAHALLOYS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>90.42</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>85.69</v>
+        <v>90.36</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>90.91</v>
+        <v>92.83</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>90.8</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SHARDUL</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>74.19</v>
+        <v>55.78</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>70.13</v>
+        <v>54.48</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>75.58</v>
+        <v>55.4</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>75.29000000000001</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>SHBAJRG</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>222.81</v>
+        <v>164.86</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>213.18</v>
+        <v>155.34</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>219.05</v>
+        <v>165.32</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>218.5</v>
+        <v>166.8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>86.7</v>
+        <v>6.43</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>85.34999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>87</v>
+        <v>6.51</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>87</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MAHLOG</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>418.6</v>
+        <v>201.81</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>399.43</v>
+        <v>198.28</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>420.05</v>
+        <v>203.98</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>420</v>
+        <v>204</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,22 +4466,22 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>346.3</v>
+        <v>1547.03</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>329.45</v>
+        <v>1513.4</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>337.4</v>
+        <v>1539.8</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>336.9</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>SOMANYCERA</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>435.94</v>
+        <v>611.15</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>435.94</v>
+        <v>587.95</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>447.46</v>
+        <v>618.05</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>447.46</v>
+        <v>615</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>3373</v>
+        <v>49.35</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>3248.03</v>
+        <v>47</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>3427.7</v>
+        <v>49.95</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>3427.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>METALIETF</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>13.42</v>
+        <v>304.06</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>12.97</v>
+        <v>285.83</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>13.11</v>
+        <v>298.51</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>13.14</v>
+        <v>302</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>MICEL</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>34.49</v>
+        <v>235.31</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>34.45</v>
+        <v>226.03</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>35.4</v>
+        <v>239.46</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>35.4</v>
+        <v>239</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>13.87</v>
+        <v>52.16</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>13.08</v>
+        <v>49.97</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>14.38</v>
+        <v>54.61</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>14.38</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>201.84</v>
+        <v>11.61</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>191.63</v>
+        <v>11.44</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>199.2</v>
+        <v>12.18</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>199.35</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>152.4</v>
+        <v>406.02</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>142.97</v>
+        <v>380.43</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>155.26</v>
+        <v>410.65</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>154.46</v>
+        <v>407.15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>837.98</v>
+        <v>7.82</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>816.4299999999999</v>
+        <v>7.33</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>842</v>
+        <v>7.93</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>842.1</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>NDRAUTO</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>763.13</v>
+        <v>221.47</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>739.55</v>
+        <v>213.54</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>754.2</v>
+        <v>227.45</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>756</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>12.87</v>
+        <v>322.75</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>12.63</v>
+        <v>312.05</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>13.71</v>
+        <v>338.6</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>13.71</v>
+        <v>338.6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>224.68</v>
+        <v>878.25</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>222.19</v>
+        <v>830.55</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>224.96</v>
+        <v>883.7</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>225.54</v>
+        <v>886</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>NILAINFRA</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>7</v>
+        <v>514.13</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>6.67</v>
+        <v>489.97</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>7.06</v>
+        <v>501.55</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>7.1</v>
+        <v>498</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>TCPLPACK</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>1916.03</v>
+        <v>4133.93</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1852.23</v>
+        <v>3931.8</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1883.7</v>
+        <v>4106.8</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>1891</v>
+        <v>4103.8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>NIMBSPROJ</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,22 +4872,22 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>198.44</v>
+        <v>127.46</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>183.31</v>
+        <v>121.12</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>199.44</v>
+        <v>125.67</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>195.25</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NORBTEAEXP</t>
+          <t>TGVSL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>67.43000000000001</v>
+        <v>116.33</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>107.92</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>67.88</v>
+        <v>124.78</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>68</v>
+        <v>125</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>TNPL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>161.46</v>
+        <v>151</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>157.6</v>
+        <v>144.02</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>165</v>
+        <v>151.6</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>165</v>
+        <v>150.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NTCIND</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>140.7</v>
+        <v>163.98</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>132.83</v>
+        <v>153.68</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>139.02</v>
+        <v>162.91</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>139.2</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>UMAEXPORTS</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>340.77</v>
+        <v>20.81</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>329.68</v>
+        <v>20.81</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>335.3</v>
+        <v>21.22</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>335.3</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>41.43</v>
+        <v>941.63</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>38.52</v>
+        <v>933.52</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>42.52</v>
+        <v>939.25</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>42.1</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>VASCONEQ</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>207.28</v>
+        <v>35.45</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>189.4</v>
+        <v>32.57</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>201.62</v>
+        <v>34.76</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>199.9</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ONEPOINT</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>68.08</v>
+        <v>0.51</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>63.74</v>
+        <v>0.44</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>69.31</v>
+        <v>0.68</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>237.3</v>
+        <v>901.08</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>233.92</v>
+        <v>789.25</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>239</v>
+        <v>918.9</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>239</v>
+        <v>903.55</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>YOGI</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>233.88</v>
+        <v>165.37</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>224.74</v>
+        <v>158.05</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>227</v>
+        <v>161.1</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>227</v>
+        <v>161.11</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>ZFSTEERING</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>57.77</v>
+        <v>744.97</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>54.78</v>
+        <v>712.3</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>59.15</v>
+        <v>750.85</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>59.47</v>
+        <v>754.9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>1264.13</v>
+        <v>141.23</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>1195.1</v>
+        <v>132.65</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>1273.6</v>
+        <v>138.48</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>1270.3</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PHARMABEES</t>
+          <t>ZUARIIND</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5220,22 +5220,22 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>28.38</v>
+        <v>287.18</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>27.38</v>
+        <v>276.5</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>27.8</v>
+        <v>290.2</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>27.79</v>
+        <v>291.85</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>POEL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5249,2104 +5249,16 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>146</v>
+        <v>1191.4</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>137.31</v>
+        <v>1166.67</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>146.7</v>
+        <v>1203.9</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>POLYMED</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="n">
-        <v>1744.67</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>1701.7</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>1716</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>PREMIER</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G167" s="3" t="n">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>PREMIERPOL</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>84.16</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>100.51</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>99.3</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>PRITIKAUTO</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="G169" s="3" t="n">
-        <v>17.14</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>PROSTARM</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>139.08</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>131.34</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>139.26</v>
-      </c>
-      <c r="G170" s="3" t="n">
-        <v>138.75</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>PROTEAN</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>634.5700000000001</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>572.97</v>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>641.95</v>
-      </c>
-      <c r="G171" s="3" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>PSUBNKBEES</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="n">
-        <v>94.03</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>91.95999999999999</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>92.45</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>92.47</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>PYRAMID</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="n">
-        <v>161.78</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>155.01</v>
-      </c>
-      <c r="F173" s="3" t="n">
-        <v>161.52</v>
-      </c>
-      <c r="G173" s="3" t="n">
-        <v>162.24</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>QUINT</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>78.23999999999999</v>
-      </c>
-      <c r="F174" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="G174" s="3" t="n">
-        <v>88.8</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>RAJTV</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F175" s="3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="G175" s="3" t="n">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="n">
-        <v>1159.33</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>1048.12</v>
-      </c>
-      <c r="F176" s="3" t="n">
-        <v>1203.85</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>1200.05</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>RAYMONDLSL</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="n">
-        <v>687.63</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>655.13</v>
-      </c>
-      <c r="F177" s="3" t="n">
-        <v>688.85</v>
-      </c>
-      <c r="G177" s="3" t="n">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>RAYMONDREL</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="n">
-        <v>666.87</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>611.9</v>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>708.3</v>
-      </c>
-      <c r="G178" s="3" t="n">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>RELIABLE</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="F179" s="3" t="n">
-        <v>147.95</v>
-      </c>
-      <c r="G179" s="3" t="n">
-        <v>147.8</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>REMSONSIND</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="n">
-        <v>105.56</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>97.63</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>111.12</v>
-      </c>
-      <c r="G180" s="3" t="n">
-        <v>111.59</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>RKEC</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>22.84</v>
-      </c>
-      <c r="G181" s="3" t="n">
-        <v>22.84</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F182" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G182" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>SADBHIN</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="F183" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="G183" s="3" t="n">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>SAKUMA</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F185" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>SAYAJIHOTL</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>314.03</v>
-      </c>
-      <c r="F186" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="G186" s="3" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="n">
-        <v>1057.01</v>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>1056.99</v>
-      </c>
-      <c r="F187" s="3" t="n">
-        <v>1057.19</v>
-      </c>
-      <c r="G187" s="3" t="n">
-        <v>1057.2</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>SEIL</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="n">
-        <v>197.02</v>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>189.26</v>
-      </c>
-      <c r="F188" s="3" t="n">
-        <v>194.69</v>
-      </c>
-      <c r="G188" s="3" t="n">
-        <v>194.96</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>SHAHALLOYS</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="F189" s="3" t="n">
-        <v>92.01000000000001</v>
-      </c>
-      <c r="G189" s="3" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>SHEMAROO</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="n">
-        <v>122.48</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>118.69</v>
-      </c>
-      <c r="F190" s="3" t="n">
-        <v>122.91</v>
-      </c>
-      <c r="G190" s="3" t="n">
-        <v>121.62</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>SHIVAUM</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="n">
-        <v>504.8</v>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>498.33</v>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>513.2</v>
-      </c>
-      <c r="G191" s="3" t="n">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>SIGNPOST</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="n">
-        <v>276.97</v>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>268.25</v>
-      </c>
-      <c r="F192" s="3" t="n">
-        <v>272.8</v>
-      </c>
-      <c r="G192" s="3" t="n">
-        <v>272.3</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>SIKKO</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E193" s="3" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="F193" s="3" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="G193" s="3" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F194" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G194" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>SINGERIND</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="n">
-        <v>80.01000000000001</v>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="F195" s="3" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="G195" s="3" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>SIRCA</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="n">
-        <v>416.93</v>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>404.57</v>
-      </c>
-      <c r="F196" s="3" t="n">
-        <v>410.7</v>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="n">
-        <v>829.0700000000001</v>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>804.22</v>
-      </c>
-      <c r="F197" s="3" t="n">
-        <v>816.3</v>
-      </c>
-      <c r="G197" s="3" t="n">
-        <v>816.3</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>SOUTHBANK</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="F198" s="3" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>49.95</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>SREEL</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="n">
-        <v>297.26</v>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>280.76</v>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>299.57</v>
-      </c>
-      <c r="G199" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>SRGHFL</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>150.85</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>141.35</v>
-      </c>
-      <c r="F200" s="3" t="n">
-        <v>154.5</v>
-      </c>
-      <c r="G200" s="3" t="n">
-        <v>153.05</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>STERTOOLS</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="n">
-        <v>227.31</v>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>218.46</v>
-      </c>
-      <c r="F201" s="3" t="n">
-        <v>233.05</v>
-      </c>
-      <c r="G201" s="3" t="n">
-        <v>233.05</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="n">
-        <v>48.99</v>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>47.53</v>
-      </c>
-      <c r="F202" s="3" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="G202" s="3" t="n">
-        <v>52.18</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>SUMEETINDS</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="F203" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G203" s="3" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SUNDROP</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>745.35</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>706</v>
-      </c>
-      <c r="F204" s="3" t="n">
-        <v>756.2</v>
-      </c>
-      <c r="G204" s="3" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SUNFLAG</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>385.68</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>364.05</v>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="F206" s="3" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="G206" s="3" t="n">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>SUPRIYA</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="n">
-        <v>993.3200000000001</v>
-      </c>
-      <c r="E207" s="3" t="n">
-        <v>934.58</v>
-      </c>
-      <c r="F207" s="3" t="n">
-        <v>961.75</v>
-      </c>
-      <c r="G207" s="3" t="n">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>SURAJLTD</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="n">
-        <v>203.04</v>
-      </c>
-      <c r="E208" s="3" t="n">
-        <v>197.01</v>
-      </c>
-      <c r="F208" s="3" t="n">
-        <v>200.5</v>
-      </c>
-      <c r="G208" s="3" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>SURYAROSNI</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="n">
-        <v>215.88</v>
-      </c>
-      <c r="E209" s="3" t="n">
-        <v>211.42</v>
-      </c>
-      <c r="F209" s="3" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="G209" s="3" t="n">
-        <v>218.01</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>SUYOG</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>649.6799999999999</v>
-      </c>
-      <c r="F210" s="3" t="n">
-        <v>660.15</v>
-      </c>
-      <c r="G210" s="3" t="n">
-        <v>669.95</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>SWARAJ</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>305.45</v>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>286.08</v>
-      </c>
-      <c r="F211" s="3" t="n">
-        <v>322.5</v>
-      </c>
-      <c r="G211" s="3" t="n">
-        <v>322.5</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>SYSTMTXC</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="n">
-        <v>77.48</v>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F212" s="3" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="G212" s="3" t="n">
-        <v>79.05</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>TASTYBITE</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="n">
-        <v>10173</v>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>9809.33</v>
-      </c>
-      <c r="F213" s="3" t="n">
-        <v>9903</v>
-      </c>
-      <c r="G213" s="3" t="n">
-        <v>9882</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>190.06</v>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>185.31</v>
-      </c>
-      <c r="F214" s="3" t="n">
-        <v>188.02</v>
-      </c>
-      <c r="G214" s="3" t="n">
-        <v>188.02</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>TCIEXP</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="n">
-        <v>506.5</v>
-      </c>
-      <c r="E215" s="3" t="n">
-        <v>486.67</v>
-      </c>
-      <c r="F215" s="3" t="n">
-        <v>492.75</v>
-      </c>
-      <c r="G215" s="3" t="n">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>TCPLPACK</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>4062.3</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>3855.97</v>
-      </c>
-      <c r="F216" s="3" t="n">
-        <v>4058.8</v>
-      </c>
-      <c r="G216" s="3" t="n">
-        <v>4065.9</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>TEMBO</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="G217" s="3" t="n">
-        <v>59.84</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>TEXRAIL</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>123.94</v>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>117.69</v>
-      </c>
-      <c r="F218" s="3" t="n">
-        <v>126.77</v>
-      </c>
-      <c r="G218" s="3" t="n">
-        <v>126.9</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>TGVSL</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D219" s="3" t="n">
-        <v>109.75</v>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>105.35</v>
-      </c>
-      <c r="F219" s="3" t="n">
-        <v>109.31</v>
-      </c>
-      <c r="G219" s="3" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>TIMKEN</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="n">
-        <v>3258.6</v>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>3162.9</v>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>3256.9</v>
-      </c>
-      <c r="G220" s="3" t="n">
-        <v>3246.8</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>TIRUPATIFL</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>74.56999999999999</v>
-      </c>
-      <c r="F221" s="3" t="n">
-        <v>79.87</v>
-      </c>
-      <c r="G221" s="3" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="n">
-        <v>4996.17</v>
-      </c>
-      <c r="E222" s="3" t="n">
-        <v>4878.17</v>
-      </c>
-      <c r="F222" s="3" t="n">
-        <v>4928.5</v>
-      </c>
-      <c r="G222" s="3" t="n">
-        <v>4928.5</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>TVVISION</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F223" s="3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G223" s="3" t="n">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>UMAEXPORTS</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F224" s="3" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="G224" s="3" t="n">
-        <v>20.81</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>UNICHEMLAB</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="n">
-        <v>570.95</v>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>536.78</v>
-      </c>
-      <c r="F225" s="3" t="n">
-        <v>552.65</v>
-      </c>
-      <c r="G225" s="3" t="n">
-        <v>552.6</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>UNIVCABLES</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="n">
-        <v>1515.87</v>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>1464.83</v>
-      </c>
-      <c r="F226" s="3" t="n">
-        <v>1517</v>
-      </c>
-      <c r="G226" s="3" t="n">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C227" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E227" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F227" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G227" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>VASCONEQ</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>33.72</v>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="F228" s="3" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="G228" s="3" t="n">
-        <v>33.31</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F229" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G229" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>VIPCLOTHNG</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F230" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G230" s="3" t="n">
-        <v>21.74</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>VMM</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>106.05</v>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>103.14</v>
-      </c>
-      <c r="F231" s="3" t="n">
-        <v>105.46</v>
-      </c>
-      <c r="G231" s="3" t="n">
-        <v>105.46</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>VOEPL</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>521.03</v>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>493.38</v>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>497.65</v>
-      </c>
-      <c r="G232" s="3" t="n">
-        <v>496.25</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>VSTTILLERS</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="n">
-        <v>4462.93</v>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>4294.5</v>
-      </c>
-      <c r="F233" s="3" t="n">
-        <v>4516.7</v>
-      </c>
-      <c r="G233" s="3" t="n">
-        <v>4436</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>WEWIN</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C234" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>44.02</v>
-      </c>
-      <c r="F234" s="3" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>49.48</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>WHIRLPOOL</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>828.08</v>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>750.75</v>
-      </c>
-      <c r="F235" s="3" t="n">
-        <v>853.45</v>
-      </c>
-      <c r="G235" s="3" t="n">
-        <v>860.1</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="n">
-        <v>1163.33</v>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>1127.27</v>
-      </c>
-      <c r="F236" s="3" t="n">
-        <v>1157</v>
-      </c>
-      <c r="G236" s="3" t="n">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="n">
-        <v>1179.7</v>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>1156.57</v>
-      </c>
-      <c r="F237" s="3" t="n">
-        <v>1180.3</v>
-      </c>
-      <c r="G237" s="3" t="n">
-        <v>1180.3</v>
+        <v>1203.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>35</v>
+        <v>36.39</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>32.2</v>
+        <v>33.37</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>36.05</v>
+        <v>35.28</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>36</v>
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>713.38</v>
+        <v>113.47</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>667.73</v>
+        <v>102.04</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>715.05</v>
+        <v>116.66</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>714.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ADDIND</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>80.27</v>
+        <v>257.14</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>73.52</v>
+        <v>243.56</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>77.2</v>
+        <v>260.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ADOR</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1644.63</v>
+        <v>21.31</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1592.17</v>
+        <v>19.96</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1638.9</v>
+        <v>21.09</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1630.6</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>247.74</v>
+        <v>181.7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>239.96</v>
+        <v>171.51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>246.05</v>
+        <v>185.11</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>246</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AERONEU</t>
+          <t>ANDHRSUGAR</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>70.67</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>80.22</v>
+        <v>95.13</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>78</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>20.67</v>
+        <v>1078.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>19.3</v>
+        <v>1078.47</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>21.38</v>
+        <v>1078.72</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>21.25</v>
+        <v>1078.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA</t>
+          <t>APCL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>41.97</v>
+        <v>97.38</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>39.8</v>
+        <v>94.13</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>41.09</v>
+        <v>94.64</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>41.25</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>181.7</v>
+        <v>866.0700000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>171.51</v>
+        <v>839.72</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>185.11</v>
+        <v>854.35</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>184.5</v>
+        <v>854</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1078.26</v>
+        <v>402.2</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1078.24</v>
+        <v>381.03</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1078.58</v>
+        <v>387.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1078.59</v>
+        <v>388.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTSUP</t>
+          <t>AVADHSUGAR</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>247.83</v>
+        <v>788.85</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>237.63</v>
+        <v>746.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>242.7</v>
+        <v>808.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>245</v>
+        <v>811.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>394.13</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>374.42</v>
+        <v>593.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>402.75</v>
+        <v>597.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>401.95</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ASIANHOTNR</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>397.65</v>
+        <v>120.57</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>381.53</v>
+        <v>118.88</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>394.35</v>
+        <v>121.12</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>387.55</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>350.1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>593.95</v>
+        <v>350.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>597.15</v>
+        <v>357.05</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>597.09</v>
+        <v>357.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BALKRISHNA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>120.57</v>
+        <v>16.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>118.88</v>
+        <v>15.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>121.12</v>
+        <v>16.44</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>120.8</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>343.25</v>
+        <v>693.28</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>343.25</v>
+        <v>662.38</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>350.05</v>
+        <v>680.7</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>350.05</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BANARBEADS</t>
+          <t>BANARISUG</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>122.03</v>
+        <v>3421.07</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>113.67</v>
+        <v>3329.5</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>123.86</v>
+        <v>3383.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>123.05</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="19">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>108.67</v>
+        <v>112</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>101.6</v>
+        <v>103.83</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>110.71</v>
+        <v>109.23</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>109</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>848.92</v>
+        <v>384.85</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>827.52</v>
+        <v>355.45</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>850.3</v>
+        <v>380.85</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>852.4</v>
+        <v>380.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>BLUECLOUDS</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>17.51</v>
+        <v>22.65</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>16.64</v>
+        <v>20.48</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>17.1</v>
+        <v>21.71</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17.04</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>21.38</v>
+        <v>204.83</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>19.76</v>
+        <v>192.71</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22.16</v>
+        <v>201.93</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>22.39</v>
+        <v>203.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>BOHRAIND</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>142.42</v>
+        <v>15.94</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>132.51</v>
+        <v>14.19</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>145.12</v>
+        <v>15.79</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>145</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1805.1</v>
+        <v>275.42</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1725.27</v>
+        <v>261.97</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1811.6</v>
+        <v>280.8</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1823</v>
+        <v>280.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BPLPHARMA</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1682.83</v>
+        <v>1834.63</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1540.33</v>
+        <v>1746.77</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1898</v>
+        <v>1802.4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1898</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>BPLPHARMA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3079.07</v>
+        <v>1921.93</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2947.87</v>
+        <v>1703.67</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3002.6</v>
+        <v>2149.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3001.8</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1080.95</v>
+        <v>200.47</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1080.93</v>
+        <v>195.22</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1081.27</v>
+        <v>201.04</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1081.27</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>CGVAK</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>138.82</v>
+        <v>154.56</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>124.29</v>
+        <v>144.65</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>152.24</v>
+        <v>151.69</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>152.24</v>
+        <v>151.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>COMFINTE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.02</v>
+        <v>6.63</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.8</v>
+        <v>5.94</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.26</v>
+        <v>7.21</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.26</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>83.55</v>
+        <v>596.8200000000001</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>75.37</v>
+        <v>580.85</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>83.98</v>
+        <v>599.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>83.25</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>5.91</v>
+        <v>152.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5.91</v>
+        <v>135.62</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.2</v>
+        <v>167.46</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>6.2</v>
+        <v>167.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>121.44</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>66.64</v>
+        <v>114.74</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>76.84</v>
+        <v>122.77</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>76.8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ</t>
+          <t>DBSTOCKBRO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>304</v>
+        <v>31.56</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>288.85</v>
+        <v>30.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>295.15</v>
+        <v>31.66</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>302</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>13359.67</v>
+        <v>6.21</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13119</v>
+        <v>6.21</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>13390</v>
+        <v>6.51</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>13390</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>305.32</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>289.9</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>305.35</v>
+        <v>72.2</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>306</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>23.62</v>
+        <v>13531.67</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>23.62</v>
+        <v>13178.67</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>24.09</v>
+        <v>13640</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>24.09</v>
+        <v>13640</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>71.94</v>
+        <v>310.13</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>66.93000000000001</v>
+        <v>293.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>72</v>
+        <v>302.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>72</v>
+        <v>303.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EIFFL</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>266.47</v>
+        <v>24.09</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>264.93</v>
+        <v>24.09</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>271.7</v>
+        <v>24.57</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>271.7</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EKI</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>96.84</v>
+        <v>44.4</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>82.59</v>
+        <v>41.42</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>100.99</v>
+        <v>43.37</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>101.22</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>42.16</v>
+        <v>13139</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>39.59</v>
+        <v>12618</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>42.86</v>
+        <v>13139</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>42.86</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2852.4</v>
+        <v>1049.32</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2797.03</v>
+        <v>1047.84</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2855.7</v>
+        <v>1049.55</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2850</v>
+        <v>1049.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>660.92</v>
+        <v>200.43</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>638.3200000000001</v>
+        <v>189.16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>671.55</v>
+        <v>192.89</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>672.9</v>
+        <v>193.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FMGOETZE</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>472.05</v>
+        <v>283.63</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>451.82</v>
+        <v>269.08</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>482.6</v>
+        <v>288.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>481.25</v>
+        <v>288.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GALAXYSURF</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>2276.57</v>
+        <v>315.32</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2203.83</v>
+        <v>299.68</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>2261.3</v>
+        <v>313.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2259</v>
+        <v>313.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>ESAFSFB</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1497.53</v>
+        <v>43.42</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1464.33</v>
+        <v>40.86</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1497.2</v>
+        <v>43</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1500</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMBREW</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>979.35</v>
+        <v>12.65</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>952.53</v>
+        <v>11.6</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>978.8</v>
+        <v>12.92</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>980</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>102.25</v>
+        <v>676.65</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>96.75</v>
+        <v>651.98</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>102.68</v>
+        <v>675</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>102.19</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>633.03</v>
+        <v>60.29</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>609.85</v>
+        <v>55.91</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>630.3</v>
+        <v>57.4</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>632</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GOLDTECH</t>
+          <t>FCSSOFT</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>46.32</v>
+        <v>1.46</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>44.43</v>
+        <v>1.35</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>48.51</v>
+        <v>1.4</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>48.59</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>3202.07</v>
+        <v>2.82</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3146.23</v>
+        <v>2.81</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3191</v>
+        <v>2.87</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>3191</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>GANESHBE</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>222.78</v>
+        <v>134.06</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>206.15</v>
+        <v>126.07</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>234.78</v>
+        <v>137.32</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>234.52</v>
+        <v>137.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GVPTECH</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>7.86</v>
+        <v>1523.8</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>7.43</v>
+        <v>1474.7</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>7.94</v>
+        <v>1533.4</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>7.95</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1079.3</v>
+        <v>58.25</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1079.28</v>
+        <v>54.57</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1079.63</v>
+        <v>55.99</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1079.62</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>GILLANDERS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>237.25</v>
+        <v>109.35</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>227.58</v>
+        <v>103.19</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>248.5</v>
+        <v>107.38</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>248.5</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HERANBA</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>182.28</v>
+        <v>258.28</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>168.96</v>
+        <v>246.17</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>187.6</v>
+        <v>263.25</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>189.46</v>
+        <v>264.95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HILTON</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>17.21</v>
+        <v>232.31</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>16.56</v>
+        <v>216.78</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>16.85</v>
+        <v>230.4</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>16.96</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HIMATSEIDE</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>70.09</v>
+        <v>110.91</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>66.23999999999999</v>
+        <v>110.78</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>68.79000000000001</v>
+        <v>110.92</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>589.42</v>
+        <v>6636.67</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>566.3200000000001</v>
+        <v>6369.17</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>618.35</v>
+        <v>6653.5</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>618.35</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>611.35</v>
+        <v>806.4299999999999</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>591.9299999999999</v>
+        <v>765.22</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>608.95</v>
+        <v>785.65</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>608.95</v>
+        <v>785.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>298.23</v>
+        <v>1079.54</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>268.57</v>
+        <v>1079.52</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>309.9</v>
+        <v>1079.76</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>308</v>
+        <v>1079.76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>INDNIPPON</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1323</v>
+        <v>237.25</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1253.97</v>
+        <v>227.58</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1318.2</v>
+        <v>248.5</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1316</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1319.47</v>
+        <v>27.95</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1241.28</v>
+        <v>26.41</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1275.95</v>
+        <v>30.36</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1271</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>HITECHGEAR</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>16.54</v>
+        <v>618.85</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>15.65</v>
+        <v>592.98</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>16.9</v>
+        <v>648.85</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>16.84</v>
+        <v>649.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>85.3</v>
+        <v>29.81</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>28.38</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>85.06999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>84.55</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1451.8</v>
+        <v>16.54</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>1449.6</v>
+        <v>15.65</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1480.6</v>
+        <v>16.9</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>1480.6</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ISTLTD</t>
+          <t>INTENTECH</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>668.33</v>
+        <v>86.09</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>652.98</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>660</v>
+        <v>83.05</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>660</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>JAGSNPHARM</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>243.08</v>
+        <v>114.17</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>229.75</v>
+        <v>110.02</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>242.29</v>
+        <v>114.82</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>241.77</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>25.73</v>
+        <v>31.9</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>24.42</v>
+        <v>30.85</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>25.13</v>
+        <v>31.31</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>25.07</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>IWP</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>138.26</v>
+        <v>38.15</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>130.36</v>
+        <v>34.27</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>138.2</v>
+        <v>40.96</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>138</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>795.12</v>
+        <v>140.53</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>740.85</v>
+        <v>132.71</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>846.4</v>
+        <v>139.68</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>846.4</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>969.63</v>
+        <v>29.09</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>923.17</v>
+        <v>28.49</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>974.25</v>
+        <v>28.88</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>978</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KANORICHEM</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>191.16</v>
+        <v>269.4</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>176.73</v>
+        <v>256.97</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>198.55</v>
+        <v>269.95</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>199</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>327.4</v>
+        <v>847.0700000000001</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>321.28</v>
+        <v>794.67</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>327.95</v>
+        <v>863.15</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>327</v>
+        <v>855.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KCP</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>161.33</v>
+        <v>989.3</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>156.02</v>
+        <v>932.5</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>163.29</v>
+        <v>990</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>162.74</v>
+        <v>999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KECL</t>
+          <t>KANORICHEM</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>125.45</v>
+        <v>199.08</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>120.15</v>
+        <v>183.9</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>126.17</v>
+        <v>202.55</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>127.25</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>197.44</v>
+        <v>3643</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>188.37</v>
+        <v>3506.43</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>206.58</v>
+        <v>3658</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>206.58</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>KMSUGAR</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>793.52</v>
+        <v>32.29</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>727.22</v>
+        <v>30.16</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>804.55</v>
+        <v>32.67</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>814</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>KOPRAN</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>288.45</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>270.75</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.08</v>
+        <v>277.97</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.08</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LAMBODHARA</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>139</v>
+        <v>206.74</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>125.78</v>
+        <v>195.77</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>144.57</v>
+        <v>216.9</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>141.2</v>
+        <v>216.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LCCINFOTEC</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>4.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>3.9</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>4.23</v>
+        <v>0.08</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>4.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>LEMERITE</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>20.76</v>
+        <v>1731.87</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>19.51</v>
+        <v>1690.13</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>21.06</v>
+        <v>1730.7</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>21.3</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1723.03</v>
+        <v>1009.32</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>1673.83</v>
+        <v>1007.54</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1725.4</v>
+        <v>1009.64</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1725.4</v>
+        <v>1009.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1009.32</v>
+        <v>1100.93</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1007.54</v>
+        <v>1100.38</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1009.64</v>
+        <v>1100.63</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1009.64</v>
+        <v>1100.63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>1100.16</v>
+        <v>116.1</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1100.14</v>
+        <v>116.08</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1100.48</v>
+        <v>116.11</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1100.49</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>116.08</v>
+        <v>1104.86</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>116.06</v>
+        <v>1104.75</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>116.1</v>
+        <v>1105.09</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>116.11</v>
+        <v>1105.09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1104.61</v>
+        <v>1123.05</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1104.5</v>
+        <v>1123.03</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1104.95</v>
+        <v>1123.27</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1104.96</v>
+        <v>1123.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1122.81</v>
+        <v>151.27</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1122.79</v>
+        <v>137.35</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1123.13</v>
+        <v>148.2</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1123.14</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>MADHAV</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>77.68000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>72.55</v>
+        <v>33.97</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>79.67</v>
+        <v>35.82</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>79.59</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MAKERSL</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>190.56</v>
+        <v>240.85</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>184.03</v>
+        <v>230.24</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>188.4</v>
+        <v>236.35</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>188</v>
+        <v>237.65</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>234.7</v>
+        <v>537.33</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>223.85</v>
+        <v>517.02</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>229.12</v>
+        <v>541.3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>228</v>
+        <v>541</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>MARKOLINES</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>267.77</v>
+        <v>171.42</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>258.32</v>
+        <v>166.55</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>280.05</v>
+        <v>168.21</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>280.9</v>
+        <v>168.44</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>447.52</v>
+        <v>280.83</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>447.52</v>
+        <v>268.03</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>456.4</v>
+        <v>285.15</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>456.4</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MCCHRLS-B</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>681.48</v>
+        <v>456.46</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>635.17</v>
+        <v>456.46</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>681</v>
+        <v>465.52</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>682</v>
+        <v>465.52</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MICEL</t>
+          <t>MCCHRLS-B</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>35.4</v>
+        <v>684.27</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>35.4</v>
+        <v>657.63</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>36.1</v>
+        <v>677.9</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>36.1</v>
+        <v>677.9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>14.44</v>
+        <v>16.12</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>13.72</v>
+        <v>15.52</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>15.09</v>
+        <v>15.97</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>15.09</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MODTHREAD</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>48.12</v>
+        <v>171.52</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>46.07</v>
+        <v>161.27</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>47.32</v>
+        <v>173.55</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>47.8</v>
+        <v>172.05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>MTEDUCARE</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>8551.5</v>
+        <v>1.76</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>8409</v>
+        <v>1.62</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>8584.5</v>
+        <v>1.76</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>8572</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>MUNJALAU</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>13.72</v>
+        <v>108.96</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>13.72</v>
+        <v>104.86</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>14.39</v>
+        <v>106.87</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>14.39</v>
+        <v>106.47</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>224.68</v>
+        <v>1259.87</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>222.19</v>
+        <v>1217.37</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>224.96</v>
+        <v>1253.9</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>225.54</v>
+        <v>1253.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>NELCAST</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>284.17</v>
+        <v>118.85</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>266.67</v>
+        <v>109.8</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>288.6</v>
+        <v>116.65</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>288.6</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NKIND</t>
+          <t>NEUEON</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>59.63</v>
+        <v>14.4</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>57.43</v>
+        <v>14.4</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>60.36</v>
+        <v>15.1</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>60.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NORBTEAEXP</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>68.93000000000001</v>
+        <v>224.68</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>65.12</v>
+        <v>222.19</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>70.12</v>
+        <v>224.96</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>70</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>1713.03</v>
+        <v>293.5</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1671.87</v>
+        <v>279.85</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1681.4</v>
+        <v>301</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>1675</v>
+        <v>301</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>NRAIL</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>161.98</v>
+        <v>688.78</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>152.94</v>
+        <v>631.45</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>167.67</v>
+        <v>647.6</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>167.67</v>
+        <v>655.15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>OCCLLTD</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>59.3</v>
+        <v>168.01</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>55.96</v>
+        <v>160.27</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>60.46</v>
+        <v>174.52</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>60.85</v>
+        <v>175.95</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PERMAGN</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>849.33</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>834.1799999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>852.45</v>
+        <v>73.64</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>847</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1331.17</v>
+        <v>1.98</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1243.23</v>
+        <v>1.97</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1329.1</v>
+        <v>2.01</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1319</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>PAVNAIND</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>7.77</v>
+        <v>15.91</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>7.35</v>
+        <v>15.06</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>7.71</v>
+        <v>15.53</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>7.73</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PLASTIBLEN</t>
+          <t>PENIND</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>197.82</v>
+        <v>187.43</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>187.22</v>
+        <v>179.04</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>202.99</v>
+        <v>182.17</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>202.86</v>
+        <v>182.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>POWERICA</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>582.0700000000001</v>
+        <v>1347.2</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>558.3200000000001</v>
+        <v>1276.17</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>582.95</v>
+        <v>1296.1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>584.9</v>
+        <v>1291.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PREMIER</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>2.97</v>
+        <v>7.89</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>2.73</v>
+        <v>7.42</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>2.8</v>
+        <v>7.59</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>2.8</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PRIMESECU</t>
+          <t>PONNIERODE</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>303.03</v>
+        <v>402.7</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>292.2</v>
+        <v>378.03</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>301.9</v>
+        <v>390</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>303.05</v>
+        <v>391</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>303.55</v>
+        <v>4.69</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>258.35</v>
+        <v>4.42</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>311.73</v>
+        <v>4.84</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>311</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>3558.33</v>
+        <v>26.12</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>3458.27</v>
+        <v>23.52</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>3594.1</v>
+        <v>28.13</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>3596</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>670.17</v>
+        <v>3605.07</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>618.13</v>
+        <v>3509.47</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>690.7</v>
+        <v>3605.3</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>695</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>55.62</v>
+        <v>694.83</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>51.91</v>
+        <v>641.4</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>56.75</v>
+        <v>691.5</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>56.97</v>
+        <v>686.15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>RAJTV</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>20.7</v>
+        <v>10.77</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>20.15</v>
+        <v>10.43</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>20.9</v>
+        <v>11.14</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>20.98</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RAJTV</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>10.26</v>
+        <v>573.25</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>548.8200000000001</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>10.76</v>
+        <v>568.2</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>10.76</v>
+        <v>569</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>1193.95</v>
+        <v>193.21</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1115.47</v>
+        <v>183.33</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>1196.65</v>
+        <v>193.45</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1183</v>
+        <v>193.75</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>RTSPOWR</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>712.65</v>
+        <v>107.31</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>651.67</v>
+        <v>97.12</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>711.3</v>
+        <v>125.5</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>708</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>REMSONSIND</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>116.56</v>
+        <v>6.4</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>104.02</v>
+        <v>6.2</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>116.8</v>
+        <v>6.63</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>117.3</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RKEC</t>
+          <t>SAKHTISUG</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>23.14</v>
+        <v>19.23</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>20.27</v>
+        <v>18.05</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>24.26</v>
+        <v>18.42</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>24.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>SANGAMIND</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>1690.53</v>
+        <v>617.8200000000001</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>1644.77</v>
+        <v>581.0700000000001</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1676.3</v>
+        <v>629.3</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>1672</v>
+        <v>633.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>6.4</v>
+        <v>283.13</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>6.2</v>
+        <v>269.72</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>6.63</v>
+        <v>282.6</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>6.63</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>SADBHIN</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>2.65</v>
+        <v>235.18</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>2.56</v>
+        <v>224.11</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>2.65</v>
+        <v>234.4</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>2.67</v>
+        <v>236.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>SALSTEEL</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>89.34</v>
+        <v>53.43</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>85.97</v>
+        <v>49.67</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>53.54</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>93.63</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SAMBANDAM</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>107.13</v>
+        <v>1057.52</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>104.17</v>
+        <v>1057.5</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>111.83</v>
+        <v>1057.74</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>111.8</v>
+        <v>1057.75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SCHAND</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>283.13</v>
+        <v>144.67</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>269.72</v>
+        <v>137.74</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>282.6</v>
+        <v>144.65</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>284.65</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SAYAJIHOTL</t>
+          <t>SDBL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>327</v>
+        <v>75.97</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>314.03</v>
+        <v>72.08</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>327</v>
+        <v>80.62</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>327</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>1057.29</v>
+        <v>3496.67</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>1057.27</v>
+        <v>3213.13</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1057.62</v>
+        <v>3547.8</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1057.62</v>
+        <v>3525.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>SETCO</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>3325</v>
+        <v>18.56</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>3083.13</v>
+        <v>17.64</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>3444.9</v>
+        <v>18.52</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>3450</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SGL</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>740.5</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>715.12</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>729.5</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>729.1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SHAHALLOYS</t>
+          <t>SHBAJRG</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>93.45999999999999</v>
+        <v>168.48</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>90.36</v>
+        <v>160.64</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>92.83</v>
+        <v>169.72</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>170</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SHARDUL</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>55.78</v>
+        <v>27.41</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>54.48</v>
+        <v>26.2</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>55.4</v>
+        <v>28.75</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>55.4</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>SHBAJRG</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>164.86</v>
+        <v>748.3</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>155.34</v>
+        <v>725.8</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>165.32</v>
+        <v>752.8</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>166.8</v>
+        <v>747</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>SIKKO</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>6.43</v>
+        <v>4770.33</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>5.99</v>
+        <v>4539.33</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>6.51</v>
+        <v>4645.3</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>6.64</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>201.81</v>
+        <v>6.59</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>198.28</v>
+        <v>6.2</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>203.98</v>
+        <v>6.53</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>204</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,16 +4466,16 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>1547.03</v>
+        <v>201.81</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>1513.4</v>
+        <v>198.28</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1539.8</v>
+        <v>203.98</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>1552</v>
+        <v>204</v>
       </c>
     </row>
     <row r="139">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>611.15</v>
+        <v>619.58</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>587.95</v>
+        <v>597.55</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>618.05</v>
+        <v>620.05</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>615</v>
+        <v>619.1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>49.35</v>
+        <v>3523</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>47</v>
+        <v>3251</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>49.95</v>
+        <v>3578.7</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>49.9</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>SSDL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>304.06</v>
+        <v>76.14</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>285.83</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>298.51</v>
+        <v>81.52</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>302</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>235.31</v>
+        <v>226.62</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>226.03</v>
+        <v>218.22</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>239.46</v>
+        <v>221.54</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>239</v>
+        <v>221</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK</t>
+          <t>STARTECK</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>52.16</v>
+        <v>277.9</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>49.97</v>
+        <v>248.13</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>54.61</v>
+        <v>314</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>54.61</v>
+        <v>315</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>11.61</v>
+        <v>426.4</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>11.44</v>
+        <v>399.03</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>12.18</v>
+        <v>449.2</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>12.18</v>
+        <v>451.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>406.02</v>
+        <v>8.02</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>380.43</v>
+        <v>7.51</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>410.65</v>
+        <v>7.86</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>407.15</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>7.82</v>
+        <v>338.87</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>7.33</v>
+        <v>328.77</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>7.93</v>
+        <v>355.45</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>7.94</v>
+        <v>355.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>SWELECTES</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>221.47</v>
+        <v>607.9</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>213.54</v>
+        <v>568.33</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>227.45</v>
+        <v>590.4</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>226.2</v>
+        <v>585</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>322.75</v>
+        <v>601.85</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>312.05</v>
+        <v>574.0700000000001</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>338.6</v>
+        <v>585.95</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>338.6</v>
+        <v>591</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>878.25</v>
+        <v>1753.93</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>830.55</v>
+        <v>1704</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>883.7</v>
+        <v>1746.4</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>886</v>
+        <v>1743.4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>TANAA</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>514.13</v>
+        <v>362.2</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>489.97</v>
+        <v>331.13</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>501.55</v>
+        <v>352.85</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>498</v>
+        <v>357</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TCPLPACK</t>
+          <t>TARMAT</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>4133.93</v>
+        <v>57.34</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>3931.8</v>
+        <v>54.1</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>4106.8</v>
+        <v>56.87</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>4103.8</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>TATVA</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,16 +4872,16 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>127.46</v>
+        <v>1827.6</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>121.12</v>
+        <v>1728.27</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>125.67</v>
+        <v>1760.2</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>125.5</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="153">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>116.33</v>
+        <v>123.38</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>107.92</v>
+        <v>112.88</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>124.78</v>
+        <v>121.88</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>125</v>
+        <v>121.36</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TNPL</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>144.02</v>
+        <v>6.43</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>151.6</v>
+        <v>6.66</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>150.7</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>163.98</v>
+        <v>183.06</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>153.68</v>
+        <v>178.66</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>162.91</v>
+        <v>183.44</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>160.1</v>
+        <v>184.12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>UMAEXPORTS</t>
+          <t>TIPSFILMS</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>20.81</v>
+        <v>346.5</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>20.81</v>
+        <v>315.9</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>21.22</v>
+        <v>331.8</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>21.22</v>
+        <v>334.85</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>TNTELE</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>941.63</v>
+        <v>10.6</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>933.52</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>939.25</v>
+        <v>11.89</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>VASCONEQ</t>
+          <t>TREJHARA</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>35.45</v>
+        <v>143.63</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>32.57</v>
+        <v>134.02</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>34.76</v>
+        <v>139.74</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>34.78</v>
+        <v>141</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.51</v>
+        <v>450.33</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.44</v>
+        <v>427.37</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>0.68</v>
+        <v>458.15</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>0.68</v>
+        <v>458.05</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>901.08</v>
+        <v>941.63</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>789.25</v>
+        <v>933.52</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>918.9</v>
+        <v>939.25</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>903.55</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>YOGI</t>
+          <t>UTTAMSUGAR</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>165.37</v>
+        <v>293.55</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>158.05</v>
+        <v>268.82</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>161.1</v>
+        <v>294.75</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>161.11</v>
+        <v>293.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ZFSTEERING</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>744.97</v>
+        <v>1704.23</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>712.3</v>
+        <v>1605.03</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>750.85</v>
+        <v>1629.2</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>754.9</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ZIMLAB</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>141.23</v>
+        <v>0.51</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>132.65</v>
+        <v>0.44</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>138.48</v>
+        <v>0.68</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>139.15</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND</t>
+          <t>VIDYAWIRES</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5220,45 +5220,219 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>287.18</v>
+        <v>90.94</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>276.5</v>
+        <v>86.63</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>290.2</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>291.85</v>
+        <v>91.31999999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>VISHWARAJ</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>VIVIMEDLAB</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>VLEGOV</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>2349.67</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>2206.67</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>2323.8</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>WINDLAS</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>1114.65</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>1076.97</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>1102.55</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>XELPMOC</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>1166.67</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>1203.9</v>
-      </c>
-      <c r="G165" s="3" t="n">
-        <v>1203.9</v>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>1209.27</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>1181.73</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>1215</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>3BBLACKBIO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>36.39</v>
+        <v>1569.3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>33.37</v>
+        <v>1463.13</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>35.28</v>
+        <v>1622.7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36</v>
+        <v>1622.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>113.47</v>
+        <v>14.05</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>102.04</v>
+        <v>13.02</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>116.66</v>
+        <v>14.23</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>114</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>257.14</v>
+        <v>34.19</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>243.56</v>
+        <v>31.82</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>260.1</v>
+        <v>36.39</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>260.75</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>ALUFLUOR</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>21.31</v>
+        <v>622.47</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19.96</v>
+        <v>561.3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.09</v>
+        <v>632.55</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>21.42</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANDHRSUGAR</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>96.48999999999999</v>
+        <v>1078.74</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>93.26000000000001</v>
+        <v>1078.71</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>95.13</v>
+        <v>1078.86</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>95.28</v>
+        <v>1078.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ARVEE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1078.5</v>
+        <v>236.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1078.47</v>
+        <v>217.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1078.72</v>
+        <v>232.85</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1078.74</v>
+        <v>230.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>APCL</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>97.38</v>
+        <v>973.42</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>94.13</v>
+        <v>926</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>94.64</v>
+        <v>1062.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>94.5</v>
+        <v>1062.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>866.0700000000001</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>839.72</v>
+        <v>593.95</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>854.35</v>
+        <v>597.15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>854</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>402.2</v>
+        <v>120.57</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>381.03</v>
+        <v>118.88</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>387.2</v>
+        <v>121.12</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>388.05</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AVADHSUGAR</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>788.85</v>
+        <v>357.08</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>746.87</v>
+        <v>357.08</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>808.4</v>
+        <v>364.15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>811.1</v>
+        <v>364.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>33.13</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>593.95</v>
+        <v>32.15</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>597.15</v>
+        <v>33.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>597.09</v>
+        <v>33.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BILVYAPAR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>120.57</v>
+        <v>4.53</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>118.88</v>
+        <v>4.24</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>121.12</v>
+        <v>4.29</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>120.8</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>350.1</v>
+        <v>612.37</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>350.1</v>
+        <v>592.62</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>357.05</v>
+        <v>622.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>357.05</v>
+        <v>624.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BALKRISHNA</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>16.8</v>
+        <v>22.28</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15.8</v>
+        <v>20.86</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>16.44</v>
+        <v>22.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>16.74</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>CMLL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>693.28</v>
+        <v>533.7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>662.38</v>
+        <v>509.15</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>680.7</v>
+        <v>542.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>677</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG</t>
+          <t>CONTROLPR</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3421.07</v>
+        <v>604.08</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3329.5</v>
+        <v>585.73</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3383.7</v>
+        <v>608.5</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3371</v>
+        <v>608.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BEDMUTHA</t>
+          <t>COUNCODOS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>112</v>
+        <v>6.61</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>103.83</v>
+        <v>6.22</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>109.23</v>
+        <v>6.4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>109.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>384.85</v>
+        <v>165.18</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>355.45</v>
+        <v>146.71</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>380.85</v>
+        <v>175.74</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>380.7</v>
+        <v>175.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>22.65</v>
+        <v>124.84</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20.48</v>
+        <v>117.33</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>21.71</v>
+        <v>124.49</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>21.6</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>204.83</v>
+        <v>6.45</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>192.71</v>
+        <v>6.45</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>201.93</v>
+        <v>6.64</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>203.28</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BOHRAIND</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>15.94</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>14.19</v>
+        <v>70.38</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>15.79</v>
+        <v>78.69</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>15.97</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>275.42</v>
+        <v>24.98</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>261.97</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>280.8</v>
+        <v>25.24</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>280.5</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>DISAQ</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1834.63</v>
+        <v>12076.33</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1746.77</v>
+        <v>11692</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1802.4</v>
+        <v>11804</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1798</v>
+        <v>11825</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BPLPHARMA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1921.93</v>
+        <v>1230.13</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1703.67</v>
+        <v>1208.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2149.8</v>
+        <v>1251.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2150</v>
+        <v>1251.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>200.47</v>
+        <v>24.57</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>195.22</v>
+        <v>24.57</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>201.04</v>
+        <v>25.06</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>201</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CGVAK</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>154.56</v>
+        <v>1049.56</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>144.65</v>
+        <v>1049.54</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>151.69</v>
+        <v>1049.7</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>151.75</v>
+        <v>1049.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COMFINTE</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.63</v>
+        <v>382.85</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.94</v>
+        <v>356.13</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.21</v>
+        <v>369.35</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.21</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>596.8200000000001</v>
+        <v>289.98</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>580.85</v>
+        <v>274.07</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>599.2</v>
+        <v>282.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>608</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>152.7</v>
+        <v>13.27</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>135.62</v>
+        <v>12.07</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>167.46</v>
+        <v>13</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>167.46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>FAIRCHEMOR</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>121.44</v>
+        <v>687</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>114.74</v>
+        <v>665.98</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>122.77</v>
+        <v>674.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>124</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DBSTOCKBRO</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>31.56</v>
+        <v>111.74</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>30.2</v>
+        <v>106.89</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>31.66</v>
+        <v>112</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>31</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>6.21</v>
+        <v>2.87</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>6.21</v>
+        <v>2.87</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>6.51</v>
+        <v>2.92</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6.51</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>GANESHBE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>137.73</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>69.65000000000001</v>
+        <v>128.34</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>72.2</v>
+        <v>137.83</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>72.45</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>13531.67</v>
+        <v>665.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>13178.67</v>
+        <v>647.0700000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>13640</v>
+        <v>666.25</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>13640</v>
+        <v>666</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>310.13</v>
+        <v>1551.63</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>293.9</v>
+        <v>1494.73</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>302.8</v>
+        <v>1537.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>303.95</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>GILLANDERS</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>24.09</v>
+        <v>111.86</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>24.09</v>
+        <v>104.92</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>24.57</v>
+        <v>110.75</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>24.57</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>44.4</v>
+        <v>2959.67</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>41.42</v>
+        <v>2887.6</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>43.37</v>
+        <v>2989.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>43.4</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>13139</v>
+        <v>110.93</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12618</v>
+        <v>110.92</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>13139</v>
+        <v>110.94</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13200</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1049.32</v>
+        <v>6824.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1047.84</v>
+        <v>6467.5</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1049.55</v>
+        <v>7016.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1049.55</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>200.43</v>
+        <v>1114.07</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>189.16</v>
+        <v>1083.47</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>192.89</v>
+        <v>1105.8</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>193.05</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>283.63</v>
+        <v>2.67</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>269.08</v>
+        <v>2.57</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>288.7</v>
+        <v>2.61</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>288.95</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>315.32</v>
+        <v>237.25</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>299.68</v>
+        <v>227.58</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>313.9</v>
+        <v>248.5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>313.3</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ESAFSFB</t>
+          <t>HINDADH</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>43.42</v>
+        <v>392.97</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>40.86</v>
+        <v>376.53</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>43</v>
+        <v>385.25</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>43.02</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>12.65</v>
+        <v>30.46</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>11.6</v>
+        <v>29.03</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>12.92</v>
+        <v>33.39</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.92</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>676.65</v>
+        <v>16.54</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>651.98</v>
+        <v>15.65</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>675</v>
+        <v>16.9</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>675</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FCL</t>
+          <t>IWP</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60.29</v>
+        <v>40.28</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>55.91</v>
+        <v>34.32</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>57.4</v>
+        <v>36.88</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>57.55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FCSSOFT</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1.46</v>
+        <v>644.98</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.35</v>
+        <v>606.88</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1.4</v>
+        <v>658.65</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.41</v>
+        <v>658.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2.82</v>
+        <v>9.35</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2.81</v>
+        <v>8.31</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2.87</v>
+        <v>10.38</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2.87</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GANESHBE</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>134.06</v>
+        <v>1008</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>126.07</v>
+        <v>952.35</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>137.32</v>
+        <v>1010.35</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>137.38</v>
+        <v>1013.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1523.8</v>
+        <v>6430.17</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1474.7</v>
+        <v>6249</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1533.4</v>
+        <v>6524.5</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1534</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>58.25</v>
+        <v>362.67</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>54.57</v>
+        <v>341</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>55.99</v>
+        <v>371.25</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.3</v>
+        <v>372.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GILLANDERS</t>
+          <t>KRONOX</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>109.35</v>
+        <v>217.07</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>103.19</v>
+        <v>202.17</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>107.38</v>
+        <v>217.04</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>107.5</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GODIGIT</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>258.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>246.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>263.25</v>
+        <v>0.08</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>264.95</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>LANDSMILL</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>232.31</v>
+        <v>0.75</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>216.78</v>
+        <v>0.65</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>230.4</v>
+        <v>0.88</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>230.5</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>110.91</v>
+        <v>1009.32</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>110.78</v>
+        <v>1007.54</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>110.92</v>
+        <v>1009.64</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>110.92</v>
+        <v>1009.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>6636.67</v>
+        <v>116.13</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>6369.17</v>
+        <v>116.11</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>6653.5</v>
+        <v>116.12</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>6680</v>
+        <v>116.13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>806.4299999999999</v>
+        <v>1106.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>765.22</v>
+        <v>1105.04</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>785.65</v>
+        <v>1105.23</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>785.95</v>
+        <v>1105.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1079.54</v>
+        <v>1123.28</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1079.52</v>
+        <v>1123.26</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1079.76</v>
+        <v>1123.41</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1079.76</v>
+        <v>1123.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>237.25</v>
+        <v>110.99</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>227.58</v>
+        <v>104.23</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>248.5</v>
+        <v>112.57</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>248.5</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>27.95</v>
+        <v>432.72</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>26.41</v>
+        <v>408.42</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>30.36</v>
+        <v>438.25</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>30.36</v>
+        <v>436.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HITECHGEAR</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>618.85</v>
+        <v>465.58</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>592.98</v>
+        <v>464.75</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>648.85</v>
+        <v>474.83</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>649.25</v>
+        <v>474.83</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>29.81</v>
+        <v>176.25</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>28.38</v>
+        <v>168.63</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>28.9</v>
+        <v>176.39</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>28.99</v>
+        <v>176.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>16.54</v>
+        <v>172.49</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>15.65</v>
+        <v>164.77</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>16.9</v>
+        <v>171.65</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>16.84</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>INTENTECH</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>86.09</v>
+        <v>2434.57</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>81.65000000000001</v>
+        <v>2347.27</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>83.05</v>
+        <v>2435.3</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>83.02</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>114.17</v>
+        <v>224.68</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>110.02</v>
+        <v>222.19</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>114.82</v>
+        <v>224.96</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>114.82</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>31.9</v>
+        <v>1939.7</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>30.85</v>
+        <v>1869.7</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>31.31</v>
+        <v>1898.9</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>31.39</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IWP</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>38.15</v>
+        <v>293.5</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>34.27</v>
+        <v>279.85</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>40.96</v>
+        <v>301</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>41.05</v>
+        <v>301</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>140.53</v>
+        <v>363.53</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>132.71</v>
+        <v>343.62</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>139.68</v>
+        <v>361.5</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>139</v>
+        <v>367.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>29.09</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>28.49</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>28.88</v>
+        <v>75.11</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>29.05</v>
+        <v>75.11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>OSIAHYPER</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>269.4</v>
+        <v>2.31</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>256.97</v>
+        <v>2.17</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>269.95</v>
+        <v>2.33</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>270</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>847.0700000000001</v>
+        <v>277.15</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>794.67</v>
+        <v>260.47</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>863.15</v>
+        <v>268.55</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>855.1</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>989.3</v>
+        <v>2.01</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>932.5</v>
+        <v>2.01</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>990</v>
+        <v>2.05</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>999</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KANORICHEM</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>199.08</v>
+        <v>2169.63</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>183.9</v>
+        <v>2053.7</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>202.55</v>
+        <v>2127.5</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>205</v>
+        <v>2089.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>3643</v>
+        <v>4.86</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>3506.43</v>
+        <v>4.63</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>3658</v>
+        <v>4.83</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3658</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR</t>
+          <t>PRITIKAUTO</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>32.29</v>
+        <v>18.83</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>30.16</v>
+        <v>17.11</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>32.67</v>
+        <v>18.4</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>32.7</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KOPRAN</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>288.45</v>
+        <v>3655.73</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>270.75</v>
+        <v>3545.07</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>277.97</v>
+        <v>3605.5</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>277</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>QMSMEDI</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>206.74</v>
+        <v>207.72</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>195.77</v>
+        <v>197.63</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>216.9</v>
+        <v>216.79</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>216.9</v>
+        <v>216.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1588.87</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1510.17</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.08</v>
+        <v>1614.3</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1731.87</v>
+        <v>583.33</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1690.13</v>
+        <v>557.58</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1730.7</v>
+        <v>583.8</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1731</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1009.32</v>
+        <v>24.34</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>1007.54</v>
+        <v>22.43</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1009.64</v>
+        <v>28.88</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1009.64</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>RSYSTEMS</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1100.93</v>
+        <v>276.2</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1100.38</v>
+        <v>254.3</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1100.63</v>
+        <v>298.69</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1100.63</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>116.1</v>
+        <v>6.4</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>116.08</v>
+        <v>6.2</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>116.11</v>
+        <v>6.63</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>116.11</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>SANGAMIND</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>1104.86</v>
+        <v>639.27</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1104.75</v>
+        <v>601.72</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1105.09</v>
+        <v>645.55</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1105.09</v>
+        <v>644.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1123.05</v>
+        <v>283.13</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1123.03</v>
+        <v>269.72</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1123.27</v>
+        <v>282.6</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1123.29</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>151.27</v>
+        <v>240.72</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>137.35</v>
+        <v>227.95</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>148.2</v>
+        <v>237.69</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>148.99</v>
+        <v>236.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MADHAV</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>36.1</v>
+        <v>1057.75</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>33.97</v>
+        <v>1057.73</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>35.82</v>
+        <v>1057.87</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>34.39</v>
+        <v>1057.87</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MAFANG</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>240.85</v>
+        <v>3578.67</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>230.24</v>
+        <v>3364</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>236.35</v>
+        <v>3485.6</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>237.65</v>
+        <v>3494.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>537.33</v>
+        <v>422.03</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>517.02</v>
+        <v>401.03</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>541.3</v>
+        <v>428.95</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>541</v>
+        <v>429</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MARKOLINES</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>171.42</v>
+        <v>753.23</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>166.55</v>
+        <v>720.4</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>168.21</v>
+        <v>755.95</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>168.44</v>
+        <v>758</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>280.83</v>
+        <v>28.77</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>268.03</v>
+        <v>28.38</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>285.15</v>
+        <v>30.18</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>282</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>456.46</v>
+        <v>761</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>456.46</v>
+        <v>739.02</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>465.52</v>
+        <v>763.3</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>465.52</v>
+        <v>762.95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MCCHRLS-B</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>684.27</v>
+        <v>60.09</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>657.63</v>
+        <v>56.86</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>677.9</v>
+        <v>60.3</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>677.9</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>16.12</v>
+        <v>201.81</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>15.52</v>
+        <v>198.28</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>15.97</v>
+        <v>203.98</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>15.99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>171.52</v>
+        <v>813.95</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>161.27</v>
+        <v>788.78</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>173.55</v>
+        <v>820.85</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>172.05</v>
+        <v>827</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MTEDUCARE</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>1.76</v>
+        <v>98.19</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1.62</v>
+        <v>86.14</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1.76</v>
+        <v>92.98</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.78</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MUNJALAU</t>
+          <t>SOFTTECH</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>108.96</v>
+        <v>502.1</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>104.86</v>
+        <v>476.57</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>106.87</v>
+        <v>502.85</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>106.47</v>
+        <v>496.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1259.87</v>
+        <v>3649</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1217.37</v>
+        <v>3422.67</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1253.9</v>
+        <v>3720.9</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>1253.9</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NELCAST</t>
+          <t>SSDL</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>118.85</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>109.8</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>116.65</v>
+        <v>83.92</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>115.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NEUEON</t>
+          <t>STARTECK</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>14.4</v>
+        <v>309.23</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>14.4</v>
+        <v>273.2</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>15.1</v>
+        <v>335.4</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>15.1</v>
+        <v>333.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>STYLEBAAZA</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>224.68</v>
+        <v>394.17</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>222.19</v>
+        <v>378.95</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>224.96</v>
+        <v>405</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>225.54</v>
+        <v>407.8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>293.5</v>
+        <v>446.43</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>279.85</v>
+        <v>414.02</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>301</v>
+        <v>464.3</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>301</v>
+        <v>465</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>688.78</v>
+        <v>538.23</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>631.45</v>
+        <v>507.03</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>647.6</v>
+        <v>553.25</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>655.15</v>
+        <v>552.55</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>168.01</v>
+        <v>1007.4</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>160.27</v>
+        <v>965.03</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>174.52</v>
+        <v>985.05</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>175.95</v>
+        <v>984.95</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>72.23999999999999</v>
+        <v>355.77</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>342.77</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>73.64</v>
+        <v>373.2</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>73.64</v>
+        <v>373.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1.98</v>
+        <v>1084.22</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1.97</v>
+        <v>1010.52</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>2.01</v>
+        <v>1144.2</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2.01</v>
+        <v>1142.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>PAVNAIND</t>
+          <t>SYNCOMF</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>15.91</v>
+        <v>23.49</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>15.06</v>
+        <v>20.6</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>15.53</v>
+        <v>26.18</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>15.68</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PENIND</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>187.43</v>
+        <v>6.74</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>179.04</v>
+        <v>6.52</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>182.17</v>
+        <v>7.07</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>182.69</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>1347.2</v>
+        <v>184.46</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1276.17</v>
+        <v>179.64</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1296.1</v>
+        <v>183.92</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>1291.5</v>
+        <v>185.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>TNTELE</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>7.89</v>
+        <v>12.2</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>7.42</v>
+        <v>10.58</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>7.59</v>
+        <v>14.26</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>7.67</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PONNIERODE</t>
+          <t>UEL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>402.7</v>
+        <v>191.23</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>378.03</v>
+        <v>182.02</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>390</v>
+        <v>184.75</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>391</v>
+        <v>185.8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>4.69</v>
+        <v>941.63</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>4.42</v>
+        <v>933.52</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>4.84</v>
+        <v>939.25</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>4.9</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>26.12</v>
+        <v>20.09</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>23.52</v>
+        <v>19.32</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>28.13</v>
+        <v>20.77</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>28.3</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>3605.07</v>
+        <v>0.51</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>3509.47</v>
+        <v>0.44</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>3605.3</v>
+        <v>0.68</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>3610</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>694.83</v>
+        <v>5.66</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>641.4</v>
+        <v>5.45</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>691.5</v>
+        <v>5.55</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>686.15</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RAJTV</t>
+          <t>VMSTMT</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>10.77</v>
+        <v>48.53</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>10.43</v>
+        <v>46.57</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>11.14</v>
+        <v>48.99</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>11.28</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>573.25</v>
+        <v>668.87</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>548.8200000000001</v>
+        <v>637.23</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>568.2</v>
+        <v>667.15</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>569</v>
+        <v>671.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>XTGLOBAL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,1524 +3915,16 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>193.21</v>
+        <v>30.45</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>183.33</v>
+        <v>28.83</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>193.45</v>
+        <v>29.43</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>193.75</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>RTSPOWR</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>107.31</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>97.12</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>125.5</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>SAKHTISUG</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>18.42</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>SANGAMIND</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>617.8200000000001</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>581.0700000000001</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>629.3</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>633.9</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SATIN</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>235.18</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>224.11</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>234.4</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>236.44</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>53.43</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>53.55</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>1057.52</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>1057.5</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>1057.74</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>1057.75</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SCHAND</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>144.67</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>137.74</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>144.65</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>144.95</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SDBL</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>72.08</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>80.62</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>81.2</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SEDEMAC</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>3496.67</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>3213.13</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>3547.8</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>3525.2</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SETCO</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>18.56</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>18.41</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>SGMART</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>740.5</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>715.12</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>729.5</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>729.1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SHBAJRG</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>168.48</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>160.64</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>169.72</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>SHEKHAWATI</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>27.41</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>28.75</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>SHREEJISPG</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>748.3</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>725.8</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>752.8</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>SHRIPISTON</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>4770.33</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>4539.33</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>4645.3</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>4645</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>SIKKO</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>6.51</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>SOMANYCERA</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>619.58</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>597.55</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>620.05</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>619.1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>3523</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>3251</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>3578.7</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>3598</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SSDL</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>76.14</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>81.52</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>STALLION</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>226.62</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>218.22</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>221.54</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>STARTECK</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>277.9</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>248.13</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>314</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>SUNFLAG</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>426.4</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>399.03</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>449.2</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>451.7</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>SUPERSPIN</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SWARAJ</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>338.87</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>328.77</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>355.45</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>355.5</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>SWELECTES</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>607.9</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>568.33</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>590.4</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>SYMPHONY</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>601.85</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>574.0700000000001</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>585.95</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>1753.93</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>1704</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>1746.4</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>1743.4</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>TANAA</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>362.2</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>331.13</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>352.85</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>TARMAT</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>56.9</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>TATVA</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>1827.6</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>1728.27</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>1760.2</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>TGVSL</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>123.38</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>112.88</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>121.88</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>121.36</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>TIJARIA</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>TIMETECHNO</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>183.06</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>178.66</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>183.44</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>184.12</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>TIPSFILMS</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>346.5</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>315.9</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>331.8</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>334.85</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>TNTELE</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="G157" s="3" t="n">
-        <v>11.89</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>TREJHARA</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>143.63</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>134.02</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>139.74</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>TRUALT</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>450.33</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>427.37</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>458.15</v>
-      </c>
-      <c r="G159" s="3" t="n">
-        <v>458.05</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>UTTAMSUGAR</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>293.55</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>268.82</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>294.75</v>
-      </c>
-      <c r="G161" s="3" t="n">
-        <v>293.25</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>VENUSREM</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>1704.23</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>1605.03</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>1629.2</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>VIDYAWIRES</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>90.94</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>91.06999999999999</v>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>91.31999999999999</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>VISHWARAJ</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G165" s="3" t="n">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>VIVIMEDLAB</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>5.66</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>VLEGOV</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="G167" s="3" t="n">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>WHEELS</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>2349.67</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>2206.67</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>2323.8</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>2325</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>WINDLAS</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="n">
-        <v>1114.65</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>1076.97</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>1102.55</v>
-      </c>
-      <c r="G169" s="3" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>XELPMOC</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>78.36</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>89.56999999999999</v>
-      </c>
-      <c r="G170" s="3" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>1209.27</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>1181.73</v>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>1215</v>
-      </c>
-      <c r="G171" s="3" t="n">
-        <v>1215</v>
+        <v>29.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1569.3</v>
+        <v>1658</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1463.13</v>
+        <v>1539.63</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1622.7</v>
+        <v>1710.4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1622.5</v>
+        <v>1691.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.05</v>
+        <v>14.37</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13.02</v>
+        <v>14.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>14.23</v>
+        <v>14.63</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14.25</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>34.19</v>
+        <v>1233.9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>31.82</v>
+        <v>1200.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>36.39</v>
+        <v>1232</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>36.39</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ALUFLUOR</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>622.47</v>
+        <v>3319.03</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>561.3</v>
+        <v>3213.8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>632.55</v>
+        <v>3279.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>637</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ADDIND</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>181.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>171.51</v>
+        <v>75.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>185.11</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>184.5</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1078.74</v>
+        <v>14.88</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1078.71</v>
+        <v>13.57</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1078.86</v>
+        <v>14.67</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1078.86</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARVEE</t>
+          <t>AHLWEST</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>236.5</v>
+        <v>539.67</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>217.8</v>
+        <v>516.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>232.85</v>
+        <v>535.05</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>230.25</v>
+        <v>535.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AUGMONT</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>973.42</v>
+        <v>827.0700000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>926</v>
+        <v>803.03</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1062.2</v>
+        <v>818.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1062.2</v>
+        <v>814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>181.7</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>593.95</v>
+        <v>171.51</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>597.15</v>
+        <v>185.11</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>597.09</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>120.57</v>
+        <v>1078.88</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>118.88</v>
+        <v>1078.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>121.12</v>
+        <v>1079</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>120.8</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AURUM</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>357.08</v>
+        <v>227.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>357.08</v>
+        <v>217.38</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>364.15</v>
+        <v>232.37</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>364.15</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BHARATCOAL</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>33.13</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>32.15</v>
+        <v>593.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>33.5</v>
+        <v>597.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>33.45</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BILVYAPAR</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.53</v>
+        <v>2094.93</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4.24</v>
+        <v>1967.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>4.29</v>
+        <v>2231.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4.29</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>612.37</v>
+        <v>120.57</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>592.62</v>
+        <v>118.88</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>622.4</v>
+        <v>121.12</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>624.8</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22.28</v>
+        <v>2974.63</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20.86</v>
+        <v>2766.6</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>22.7</v>
+        <v>2963.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>22.7</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CMLL</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>533.7</v>
+        <v>364.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>509.15</v>
+        <v>364.18</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>542.9</v>
+        <v>371.35</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>540</v>
+        <v>371.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CONTROLPR</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>604.08</v>
+        <v>831.5</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>585.73</v>
+        <v>786.27</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>608.5</v>
+        <v>804.8</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>608.05</v>
+        <v>807.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COUNCODOS</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.61</v>
+        <v>622.77</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6.22</v>
+        <v>599.85</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>6.4</v>
+        <v>607.9</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>6.4</v>
+        <v>607.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>BLUECOAST</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>165.18</v>
+        <v>22.97</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>146.71</v>
+        <v>21.56</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175.74</v>
+        <v>22.07</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>175.83</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>124.84</v>
+        <v>1081.57</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>117.33</v>
+        <v>1080.78</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>124.49</v>
+        <v>1081.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>123.5</v>
+        <v>1081.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.45</v>
+        <v>1477.63</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>6.45</v>
+        <v>1397.23</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.64</v>
+        <v>1436.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.64</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>CMLL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80.15000000000001</v>
+        <v>545</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>70.38</v>
+        <v>518.6</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>78.69</v>
+        <v>532.05</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>78.2</v>
+        <v>534</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>CMRGREEN</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>24.98</v>
+        <v>229.9</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>23</v>
+        <v>220.05</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>25.24</v>
+        <v>224.83</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>24.76</v>
+        <v>225.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DISAQ</t>
+          <t>COMPUSOFT</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>12076.33</v>
+        <v>13.73</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>11692</v>
+        <v>13.12</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>11804</v>
+        <v>13.48</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11825</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1230.13</v>
+        <v>3875.27</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1208.8</v>
+        <v>3730.03</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1251.9</v>
+        <v>3846.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1251.9</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.57</v>
+        <v>175.76</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>24.57</v>
+        <v>159.02</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>25.06</v>
+        <v>174.84</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>25.06</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1049.56</v>
+        <v>292.25</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1049.54</v>
+        <v>270.27</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1049.7</v>
+        <v>311.65</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1049.71</v>
+        <v>311.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>382.85</v>
+        <v>127.14</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>356.13</v>
+        <v>121.25</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>369.35</v>
+        <v>126.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>369</v>
+        <v>125.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>289.98</v>
+        <v>6.64</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>274.07</v>
+        <v>6.64</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>282.6</v>
+        <v>6.77</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>282</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>13.27</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12.07</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>13</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>13</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>DGCONTENT</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>687</v>
+        <v>25.9</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>665.98</v>
+        <v>23.7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>674.7</v>
+        <v>25.43</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>680</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>DIFFNKG</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>111.74</v>
+        <v>450.07</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>106.89</v>
+        <v>428.05</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>112</v>
+        <v>438.75</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>110.66</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>2.87</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2.87</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2.92</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2.92</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GANESHBE</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>137.73</v>
+        <v>280.28</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>128.34</v>
+        <v>268.95</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>137.83</v>
+        <v>277.25</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>137.93</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>665.5</v>
+        <v>1628.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>647.0700000000001</v>
+        <v>1476.83</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>666.25</v>
+        <v>1788.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>666</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1551.63</v>
+        <v>25.06</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1494.73</v>
+        <v>25.06</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1537.8</v>
+        <v>25.56</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1545</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GILLANDERS</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>111.86</v>
+        <v>693.42</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>104.92</v>
+        <v>663.83</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>110.75</v>
+        <v>686.75</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>111.9</v>
+        <v>687</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2959.67</v>
+        <v>1049.71</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2887.6</v>
+        <v>1049.69</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2989.7</v>
+        <v>1049.84</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2985</v>
+        <v>1049.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>110.93</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>110.92</v>
+        <v>65.73</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>110.94</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>110.95</v>
+        <v>68.54000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ESSARSHPNG</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6824.5</v>
+        <v>18.18</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>6467.5</v>
+        <v>16.26</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7016.5</v>
+        <v>18.89</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>7000</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1114.07</v>
+        <v>2.92</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1083.47</v>
+        <v>2.91</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1105.8</v>
+        <v>2.97</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1101</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>GALAXYSURF</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2.67</v>
+        <v>2317.77</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2.57</v>
+        <v>2225.63</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2.61</v>
+        <v>2332.8</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2.61</v>
+        <v>2321.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>237.25</v>
+        <v>274.28</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>227.58</v>
+        <v>263.1</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>248.5</v>
+        <v>278.85</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>248.5</v>
+        <v>279.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HINDADH</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>392.97</v>
+        <v>674.67</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>376.53</v>
+        <v>658.98</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>385.25</v>
+        <v>675.85</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>382</v>
+        <v>675.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>30.46</v>
+        <v>378.8</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>29.03</v>
+        <v>358.68</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>33.39</v>
+        <v>374.2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>33.39</v>
+        <v>374.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>16.54</v>
+        <v>1577.63</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>15.65</v>
+        <v>1518.07</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>16.9</v>
+        <v>1560</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>16.84</v>
+        <v>1561.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IWP</t>
+          <t>GILLANDERS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>40.28</v>
+        <v>115.29</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>34.32</v>
+        <v>107.93</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>36.88</v>
+        <v>114.8</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>37</v>
+        <v>114.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>644.98</v>
+        <v>2.17</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>606.88</v>
+        <v>2.06</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>658.65</v>
+        <v>2.25</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>658.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>9.35</v>
+        <v>110.95</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>8.31</v>
+        <v>110.94</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>10.38</v>
+        <v>110.95</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>10.34</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1008</v>
+        <v>6981.83</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>952.35</v>
+        <v>6672.83</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1010.35</v>
+        <v>7015.5</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1013.5</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>6430.17</v>
+        <v>30.26</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>6249</v>
+        <v>29.43</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>6524.5</v>
+        <v>32.62</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>6500</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>GUFICBIO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>362.67</v>
+        <v>440.68</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>341</v>
+        <v>419.65</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>371.25</v>
+        <v>432</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>372.5</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>217.07</v>
+        <v>1120.37</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>202.17</v>
+        <v>1093.23</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>217.04</v>
+        <v>1125.4</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>217</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>237.25</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>227.58</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.08</v>
+        <v>248.5</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.08</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.75</v>
+        <v>32.93</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.65</v>
+        <v>32.07</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.88</v>
+        <v>35.05</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.88</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1009.32</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1007.54</v>
+        <v>65.97</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1009.64</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1009.64</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>116.13</v>
+        <v>348.1</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>116.11</v>
+        <v>343</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>116.12</v>
+        <v>346</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>116.13</v>
+        <v>346.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1106.9</v>
+        <v>16.54</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1105.04</v>
+        <v>15.65</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1105.23</v>
+        <v>16.9</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1105.25</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>JAIPURKURT</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1123.28</v>
+        <v>26.29</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>1123.26</v>
+        <v>24.68</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1123.41</v>
+        <v>26.69</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1123.42</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>110.99</v>
+        <v>127.03</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>104.23</v>
+        <v>121.1</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>112.57</v>
+        <v>128.39</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>114.5</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>432.72</v>
+        <v>664.12</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>408.42</v>
+        <v>612.53</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>438.25</v>
+        <v>645.1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>436.85</v>
+        <v>638</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>465.58</v>
+        <v>10.64</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>464.75</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>474.83</v>
+        <v>12.45</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>474.83</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>KAMAHOLD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>176.25</v>
+        <v>2275.93</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>168.63</v>
+        <v>2223.57</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>176.39</v>
+        <v>2286.8</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>176.88</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>172.49</v>
+        <v>562.3200000000001</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>164.77</v>
+        <v>540.02</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>171.65</v>
+        <v>550.35</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>171.99</v>
+        <v>551</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2434.57</v>
+        <v>6537.5</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2347.27</v>
+        <v>6317.5</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2435.3</v>
+        <v>6482.5</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2420</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>224.68</v>
+        <v>360.97</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>222.19</v>
+        <v>343.38</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>224.96</v>
+        <v>369.55</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>225.54</v>
+        <v>366.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>KKCL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1939.7</v>
+        <v>470.28</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1869.7</v>
+        <v>455.5</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1898.9</v>
+        <v>460.35</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1911</v>
+        <v>465</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>293.5</v>
+        <v>3056.6</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>279.85</v>
+        <v>2893.57</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>301</v>
+        <v>3041.5</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>301</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>363.53</v>
+        <v>376.22</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>343.62</v>
+        <v>349.67</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>361.5</v>
+        <v>358.95</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>367.85</v>
+        <v>357.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>73.65000000000001</v>
+        <v>1031.93</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>73.20999999999999</v>
+        <v>992.77</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>75.11</v>
+        <v>1032.8</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>75.11</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>OSIAHYPER</t>
+          <t>KRITI</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.31</v>
+        <v>62.5</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.17</v>
+        <v>60.08</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.33</v>
+        <v>61</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.33</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PARAGMILK</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>277.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>260.47</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>268.55</v>
+        <v>0.08</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>268.5</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>LALITHAA</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.01</v>
+        <v>379.75</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.01</v>
+        <v>360.3</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.05</v>
+        <v>381.9</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.05</v>
+        <v>383</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>LANDSMILL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2169.63</v>
+        <v>0.86</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2053.7</v>
+        <v>0.79</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2127.5</v>
+        <v>0.96</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2089.4</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>4.86</v>
+        <v>1057.39</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>4.63</v>
+        <v>1056.54</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>4.83</v>
+        <v>1057.5</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>4.84</v>
+        <v>1057.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>PRITIKAUTO</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>18.83</v>
+        <v>1009.63</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>17.11</v>
+        <v>1009.62</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>18.4</v>
+        <v>1010.02</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>18.39</v>
+        <v>1010.02</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>3655.73</v>
+        <v>116.14</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>3545.07</v>
+        <v>116.12</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>3605.5</v>
+        <v>116.15</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>3590</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>QMSMEDI</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>207.72</v>
+        <v>1123.42</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>197.63</v>
+        <v>1123.4</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>216.79</v>
+        <v>1123.55</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>216.79</v>
+        <v>1123.56</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1588.87</v>
+        <v>1888.9</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1510.17</v>
+        <v>1833.23</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1614.3</v>
+        <v>1884</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1619</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>MANAKSTEEL</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>583.33</v>
+        <v>113.99</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>557.58</v>
+        <v>106.92</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>583.8</v>
+        <v>110.33</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>583</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>24.34</v>
+        <v>237.63</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>22.43</v>
+        <v>229.23</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>28.88</v>
+        <v>240.66</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>28.88</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RSYSTEMS</t>
+          <t>MASKINVEST</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>276.2</v>
+        <v>149.26</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>254.3</v>
+        <v>141.32</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>298.69</v>
+        <v>150.95</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>301</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>MAXIND</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>6.4</v>
+        <v>161.33</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>6.2</v>
+        <v>151.04</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>6.63</v>
+        <v>160.83</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>6.63</v>
+        <v>158.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SANGAMIND</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>639.27</v>
+        <v>474.89</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>601.72</v>
+        <v>474.05</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>645.55</v>
+        <v>484.32</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>644.5</v>
+        <v>484.32</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>283.13</v>
+        <v>22.1</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>269.72</v>
+        <v>21.06</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>282.6</v>
+        <v>22.85</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>284.65</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>MHLXMIRU</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>240.72</v>
+        <v>180.06</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>227.95</v>
+        <v>173.13</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>237.69</v>
+        <v>179.21</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>236.78</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1057.75</v>
+        <v>428.95</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>1057.73</v>
+        <v>407.78</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1057.87</v>
+        <v>437.65</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>1057.87</v>
+        <v>434</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>MOLBIO</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>3578.67</v>
+        <v>1306</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>3364</v>
+        <v>1235.9</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>3485.6</v>
+        <v>1308.9</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>3494.1</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>422.03</v>
+        <v>206.72</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>401.03</v>
+        <v>197.22</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>428.95</v>
+        <v>206.16</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>429</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>MSPL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>753.23</v>
+        <v>34.53</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>720.4</v>
+        <v>32.66</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>755.95</v>
+        <v>33</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>758</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>28.77</v>
+        <v>7448</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>28.38</v>
+        <v>7129</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>30.18</v>
+        <v>7797</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>30.18</v>
+        <v>7797</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>761</v>
+        <v>392.03</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>739.02</v>
+        <v>376.45</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>763.3</v>
+        <v>392.85</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>762.95</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>60.09</v>
+        <v>2458.23</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>56.86</v>
+        <v>2372.97</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>60.3</v>
+        <v>2451.6</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>60.2</v>
+        <v>2450.4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>201.81</v>
+        <v>224.68</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>198.28</v>
+        <v>222.19</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>203.98</v>
+        <v>224.96</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>204</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>813.95</v>
+        <v>370.67</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>788.78</v>
+        <v>350.28</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>820.85</v>
+        <v>366.6</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>827</v>
+        <v>369.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>98.19</v>
+        <v>1678.23</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>86.14</v>
+        <v>1622.1</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>92.98</v>
+        <v>1652.5</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>1651.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>502.1</v>
+        <v>75.12</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>476.57</v>
+        <v>75.12</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>502.85</v>
+        <v>76.61</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>496.05</v>
+        <v>76.61</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>3649</v>
+        <v>39.18</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>3422.67</v>
+        <v>37.17</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>3720.9</v>
+        <v>40.08</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3700</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SSDL</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>82.26000000000001</v>
+        <v>264.95</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>75.43000000000001</v>
+        <v>234.12</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>83.92</v>
+        <v>258.51</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>84</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>STARTECK</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>309.23</v>
+        <v>491</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>273.2</v>
+        <v>469.62</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>335.4</v>
+        <v>484.25</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>333.05</v>
+        <v>484.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>STYLEBAAZA</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>394.17</v>
+        <v>1338.57</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>378.95</v>
+        <v>1292.7</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>405</v>
+        <v>1311</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>407.8</v>
+        <v>1310.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>446.43</v>
+        <v>2.05</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>414.02</v>
+        <v>2.05</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>464.3</v>
+        <v>2.09</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>465</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>PATELRMART</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>538.23</v>
+        <v>213.92</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>507.03</v>
+        <v>205.02</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>553.25</v>
+        <v>211.52</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>552.55</v>
+        <v>212.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>PAUSHAKLTD</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>1007.4</v>
+        <v>674.22</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>965.03</v>
+        <v>646.13</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>985.05</v>
+        <v>665.25</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>984.95</v>
+        <v>658.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>PIXTRANS</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>355.77</v>
+        <v>1753.57</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>342.77</v>
+        <v>1716.9</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>373.2</v>
+        <v>1726.9</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>373.2</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SYMBIOTEC</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1084.22</v>
+        <v>1118.03</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1010.52</v>
+        <v>1078.23</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1144.2</v>
+        <v>1120</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1142.9</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>POWERICA</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>23.49</v>
+        <v>606.7</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>20.6</v>
+        <v>570.02</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>26.18</v>
+        <v>600.6</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>26.64</v>
+        <v>601.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>6.74</v>
+        <v>2465.23</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>6.52</v>
+        <v>2392.7</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>7.07</v>
+        <v>2490.5</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>7.07</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>PRAKASH</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>184.46</v>
+        <v>123.9</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>179.64</v>
+        <v>116.41</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>183.92</v>
+        <v>123.72</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>185.07</v>
+        <v>122.86</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TNTELE</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>12.2</v>
+        <v>22658.33</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>10.58</v>
+        <v>21700</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>14.26</v>
+        <v>22190</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>14.26</v>
+        <v>22075</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>UEL</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>191.23</v>
+        <v>1635.53</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>182.02</v>
+        <v>1540.27</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>184.75</v>
+        <v>1584.8</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>185.8</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>QUICKHEAL</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>941.63</v>
+        <v>148.38</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>933.52</v>
+        <v>142.19</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>939.25</v>
+        <v>144.49</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>20.09</v>
+        <v>291.32</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>19.32</v>
+        <v>269.57</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>20.77</v>
+        <v>285.98</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>20.77</v>
+        <v>286.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.51</v>
+        <v>590.33</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.44</v>
+        <v>567.67</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0.68</v>
+        <v>582.4</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0.68</v>
+        <v>579.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>5.66</v>
+        <v>411.45</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>5.45</v>
+        <v>401.52</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>5.55</v>
+        <v>407</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>5.55</v>
+        <v>407.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>VMSTMT</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>48.53</v>
+        <v>90.97</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>46.57</v>
+        <v>87.23</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>48.99</v>
+        <v>88.08</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>48.89</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>RESPONIND</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>668.87</v>
+        <v>171.43</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>637.23</v>
+        <v>160.36</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>667.15</v>
+        <v>165.38</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>671.7</v>
+        <v>165.29</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>XTGLOBAL</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,16 +3915,1321 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>30.45</v>
+        <v>28.24</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>28.83</v>
+        <v>27.56</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>29.43</v>
+        <v>31.76</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>29.85</v>
+        <v>31.76</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>RHETAN</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>17.51</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>1475.27</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>1391.07</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>1503.2</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>RPTECH</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>944.23</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>950.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>RVTH</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>683.67</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>633.38</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>669.8</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SABEVENTS</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>SALSTEEL</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>SALZERELEC</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>543.1799999999999</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>529.35</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>531.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SAPPL</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>299.33</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>300.1</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>491.07</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SASTASUNDR</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>283.13</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>284.65</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SATIA</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>67.26000000000001</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>69.34</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1057.89</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>1057.87</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>1058.02</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>1058.02</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>1216.77</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>1184.43</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>1203.4</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SEKURITIND</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>112.64</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>107.97</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SHEKHAWATI</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>31.68</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1061.7</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>1016.73</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>1047.2</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>1041.95</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>767.67</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>753.17</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>770.4</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>766.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>62.16</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SIGMAADV</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>987.53</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>931.63</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>1025.7</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>1025.7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SILVERETF</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>201.81</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>827.4299999999999</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>797.37</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>810.7</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>811.9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SOFTTECH</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>511</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>486.35</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>493.5</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>492.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SOTL</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>764.83</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>698.52</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>3767.57</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>3539.37</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>3846.1</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>402.82</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>385.93</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>STEELCITY</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>1212.5</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>1148.13</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>1205.8</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>431.7</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>456.05</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>452.65</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>585.62</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>523.53</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>605</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SUYOG</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>699.1799999999999</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>639.77</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>695.1</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>672.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SWARAJ</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>351.77</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>390.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SYMBIOTEC</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>1140.53</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>1061.42</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1176.75</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>1179.55</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SYNCOMF</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>779.27</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>731.77</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>786.05</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>TICL</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>TIMETECHNO</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>186.57</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>182.36</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>182.8</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>TTL</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>UYFINCORP</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>VESUVIUS</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>428.18</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>424.2</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>425.45</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD-RE1</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>131.33</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>129.66</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>129.4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>VIDHIING</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>343.68</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>355.7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>VINEETLAB</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>VIPULLTD</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>11.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3BBLACKBIO</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1658</v>
+        <v>104.41</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1539.63</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1710.4</v>
+        <v>103.85</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1691.5</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.37</v>
+        <v>14.78</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>14.08</v>
+        <v>14.67</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>14.63</v>
+        <v>15.36</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14.63</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1233.9</v>
+        <v>12.79</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1200.5</v>
+        <v>12.2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1232</v>
+        <v>12.56</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1233</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>ACCELYA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3319.03</v>
+        <v>1120.83</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3213.8</v>
+        <v>1086.57</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3279.4</v>
+        <v>1094.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3269</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ADDIND</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>1352.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>75.8</v>
+        <v>1297.73</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>78.73999999999999</v>
+        <v>1326.4</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>1326.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14.88</v>
+        <v>1280.93</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13.57</v>
+        <v>1244.77</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>14.67</v>
+        <v>1276.1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>14.69</v>
+        <v>1276.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AHLWEST</t>
+          <t>ADFFOODS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>539.67</v>
+        <v>276.8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>516.4</v>
+        <v>263.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>535.05</v>
+        <v>281.4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>535.05</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>827.0700000000001</v>
+        <v>1386.07</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>803.03</v>
+        <v>1308.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>818.5</v>
+        <v>1401.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>814</v>
+        <v>1401.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>181.7</v>
+        <v>208.93</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>171.51</v>
+        <v>199.78</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>185.11</v>
+        <v>208.14</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>184.5</v>
+        <v>207.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ALICON</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1078.88</v>
+        <v>833.73</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1078.86</v>
+        <v>758.33</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1079</v>
+        <v>871.95</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1079</v>
+        <v>884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AURUM</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>227.31</v>
+        <v>698.33</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>217.38</v>
+        <v>671.85</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>232.37</v>
+        <v>702.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>231</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>181.7</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>593.95</v>
+        <v>171.51</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>597.15</v>
+        <v>185.11</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>597.09</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2094.93</v>
+        <v>1079.16</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1967.27</v>
+        <v>1079.14</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2231.2</v>
+        <v>1079.57</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2221</v>
+        <v>1079.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>AUSTENG</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>120.57</v>
+        <v>170.98</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>118.88</v>
+        <v>157.54</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>121.12</v>
+        <v>167.72</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>120.8</v>
+        <v>169.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2974.63</v>
+        <v>1230.27</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2766.6</v>
+        <v>1202.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2963.2</v>
+        <v>1217.1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2990</v>
+        <v>1217.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>364.2</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>364.18</v>
+        <v>593.95</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>371.35</v>
+        <v>597.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>371.35</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>831.5</v>
+        <v>2230.37</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>786.27</v>
+        <v>2067.03</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>804.8</v>
+        <v>2307.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>807.5</v>
+        <v>2311.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>622.77</v>
+        <v>120.57</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>599.85</v>
+        <v>118.88</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>607.9</v>
+        <v>121.12</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>607.6</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BLUECOAST</t>
+          <t>AZADIND</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22.97</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>21.56</v>
+        <v>81.33</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>22.07</v>
+        <v>85.95</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>22.06</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1081.57</v>
+        <v>371.43</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1080.78</v>
+        <v>371.42</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1081.7</v>
+        <v>378.75</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1081.71</v>
+        <v>378.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1477.63</v>
+        <v>1082.2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1397.23</v>
+        <v>1081.79</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1436.3</v>
+        <v>1082.28</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1432</v>
+        <v>1082.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CMLL</t>
+          <t>CLEDUCATE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>545</v>
+        <v>57.88</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>518.6</v>
+        <v>55.02</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>532.05</v>
+        <v>57.91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>534</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CMRGREEN</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>229.9</v>
+        <v>1823.07</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>220.05</v>
+        <v>1744.9</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>224.83</v>
+        <v>1826</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>225.2</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COMPUSOFT</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>13.73</v>
+        <v>226.16</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.12</v>
+        <v>215.76</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>13.48</v>
+        <v>230.04</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>13.51</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3875.27</v>
+        <v>306.18</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3730.03</v>
+        <v>285.97</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3846.5</v>
+        <v>312.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3795</v>
+        <v>311.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>175.76</v>
+        <v>3.05</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>159.02</v>
+        <v>2.78</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>174.84</v>
+        <v>2.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>177.6</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>292.25</v>
+        <v>340.85</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>270.27</v>
+        <v>322.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>311.65</v>
+        <v>342.95</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>311.7</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>127.14</v>
+        <v>6.77</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>121.25</v>
+        <v>6.77</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>126.1</v>
+        <v>6.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>125.98</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.64</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.64</v>
+        <v>70.75</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>6.77</v>
+        <v>72.61</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6.77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>83.48999999999999</v>
+        <v>3864.67</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>73.45999999999999</v>
+        <v>3765.7</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>80.51000000000001</v>
+        <v>3813</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>80.73999999999999</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DGCONTENT</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>25.9</v>
+        <v>1801.97</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>23.7</v>
+        <v>1604.5</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>25.43</v>
+        <v>1874</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>26.75</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DIFFNKG</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>450.07</v>
+        <v>25.56</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>428.05</v>
+        <v>25.56</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>438.75</v>
+        <v>26.07</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>439.6</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>152.99</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>70.34999999999999</v>
+        <v>143.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>71.81999999999999</v>
+        <v>158.57</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>72.44</v>
+        <v>159.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>280.28</v>
+        <v>13598.33</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>268.95</v>
+        <v>13027.67</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>277.25</v>
+        <v>13756</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>279</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>EBANK10</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1628.5</v>
+        <v>16.2</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1476.83</v>
+        <v>15.82</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1788.8</v>
+        <v>16.19</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1798</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>25.06</v>
+        <v>1049.99</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>25.06</v>
+        <v>1049.97</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>25.56</v>
+        <v>1050.39</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>25.56</v>
+        <v>1050.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>ELPROINTL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>693.42</v>
+        <v>173.91</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>663.83</v>
+        <v>170.49</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>686.75</v>
+        <v>174.31</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>687</v>
+        <v>174.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>EMAMIREAL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1049.71</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1049.69</v>
+        <v>66.72</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1049.84</v>
+        <v>67.14</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1049.85</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>ESTER</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>67.93000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>65.73</v>
+        <v>88.14</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>68.93000000000001</v>
+        <v>95.52</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ESSARSHPNG</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>18.18</v>
+        <v>459.53</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>16.26</v>
+        <v>426.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.89</v>
+        <v>475.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>18.97</v>
+        <v>469.5</v>
       </c>
     </row>
     <row r="42">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GALAXYSURF</t>
+          <t>FMNL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2317.77</v>
+        <v>8.43</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2225.63</v>
+        <v>7.87</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2332.8</v>
+        <v>8.08</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2321.6</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>GALAXYSURF</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>274.28</v>
+        <v>2397.03</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>263.1</v>
+        <v>2276.73</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>278.85</v>
+        <v>2376.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>279.15</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="45">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>674.67</v>
+        <v>679.17</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>658.98</v>
+        <v>664.58</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>675.85</v>
+        <v>679.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>675.05</v>
+        <v>680.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>378.8</v>
+        <v>190.73</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>358.68</v>
+        <v>176.16</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>374.2</v>
+        <v>194.27</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>374.5</v>
+        <v>194.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1577.63</v>
+        <v>166.23</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>1518.07</v>
+        <v>159.99</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1560</v>
+        <v>165.88</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1561.2</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GILLANDERS</t>
+          <t>GPTINFRA</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>115.29</v>
+        <v>119.66</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>107.93</v>
+        <v>114.72</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>114.8</v>
+        <v>118.66</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>114.49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>110.95</v>
+        <v>297.82</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>110.94</v>
+        <v>283</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>110.95</v>
+        <v>303.7</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>110.95</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>6981.83</v>
+        <v>32.72</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>6672.83</v>
+        <v>32.72</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>7015.5</v>
+        <v>35.88</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>7000</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>30.26</v>
+        <v>62.63</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>29.43</v>
+        <v>59.75</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>32.62</v>
+        <v>62.45</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>32.62</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GUFICBIO</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>440.68</v>
+        <v>4273.8</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>419.65</v>
+        <v>4150.37</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>432</v>
+        <v>4253.2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>429</v>
+        <v>4253.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>HBSL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1120.37</v>
+        <v>57.67</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1093.23</v>
+        <v>55.26</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1125.4</v>
+        <v>57.03</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1127</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>237.25</v>
+        <v>2312.7</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>227.58</v>
+        <v>2248.53</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>248.5</v>
+        <v>2308.1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>248.5</v>
+        <v>2308.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>HDFCPVTBAN</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>32.93</v>
+        <v>27.43</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>32.07</v>
+        <v>26.87</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>35.05</v>
+        <v>27.37</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>35.05</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>71.68000000000001</v>
+        <v>237.25</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>65.97</v>
+        <v>227.58</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>72.29000000000001</v>
+        <v>248.5</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>72.65000000000001</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>348.1</v>
+        <v>68.63</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>343</v>
+        <v>65.27</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>346</v>
+        <v>68.8</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>346.4</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>16.54</v>
+        <v>227.2</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>15.65</v>
+        <v>217.71</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>16.9</v>
+        <v>238.36</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>16.84</v>
+        <v>238.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>HMVL</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>26.29</v>
+        <v>76.02</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>24.68</v>
+        <v>71.02</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>26.69</v>
+        <v>77.44</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>26.75</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>127.03</v>
+        <v>1578.23</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>121.1</v>
+        <v>1524.13</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>128.39</v>
+        <v>1563</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>128.2</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>IDEAFORGE</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>664.12</v>
+        <v>745.42</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>612.53</v>
+        <v>716.3</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>645.1</v>
+        <v>735</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>638</v>
+        <v>731.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>IITL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>10.64</v>
+        <v>137.32</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>126.54</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>12.45</v>
+        <v>132.56</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>12.45</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KAMAHOLD</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2275.93</v>
+        <v>33.55</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2223.57</v>
+        <v>31.8</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2286.8</v>
+        <v>35.19</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2288</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>562.3200000000001</v>
+        <v>377.93</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>540.02</v>
+        <v>365.6</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>550.35</v>
+        <v>376.25</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>551</v>
+        <v>376.25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>6537.5</v>
+        <v>16.54</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>6317.5</v>
+        <v>15.65</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>6482.5</v>
+        <v>16.9</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>6500</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>360.97</v>
+        <v>1024.8</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>343.38</v>
+        <v>990.58</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>369.55</v>
+        <v>1035</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>366.55</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KKCL</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>470.28</v>
+        <v>1568.53</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>455.5</v>
+        <v>1480.03</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>460.35</v>
+        <v>1595.2</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>465</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>3056.6</v>
+        <v>209.35</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2893.57</v>
+        <v>200.44</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>3041.5</v>
+        <v>209.39</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>3010</v>
+        <v>210.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>376.22</v>
+        <v>313.27</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>349.67</v>
+        <v>305.08</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>358.95</v>
+        <v>309.81</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>357.8</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1031.93</v>
+        <v>129.77</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>992.77</v>
+        <v>123.02</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1032.8</v>
+        <v>130.8</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1026</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KRITI</t>
+          <t>JHS</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>62.5</v>
+        <v>12.24</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>60.08</v>
+        <v>10.27</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>61</v>
+        <v>11.7</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>60.5</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>373.6</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>349.05</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.08</v>
+        <v>371.15</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.08</v>
+        <v>371.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LALITHAA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>379.75</v>
+        <v>421.33</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>360.3</v>
+        <v>405.57</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>381.9</v>
+        <v>418.35</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>383</v>
+        <v>418.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL</t>
+          <t>KREBSBIO</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.86</v>
+        <v>64.73</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.79</v>
+        <v>56.51</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.96</v>
+        <v>68.05</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.96</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1057.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1056.54</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1057.5</v>
+        <v>0.08</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1057.5</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LAXMICOT</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1009.63</v>
+        <v>13.5</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1009.62</v>
+        <v>12.84</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1010.02</v>
+        <v>13.3</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1010.02</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>116.14</v>
+        <v>107.23</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>116.12</v>
+        <v>103.32</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>116.15</v>
+        <v>107.67</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>116.15</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1123.42</v>
+        <v>206.26</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1123.4</v>
+        <v>186.05</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1123.55</v>
+        <v>219.47</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1123.56</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1888.9</v>
+        <v>6389</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1833.23</v>
+        <v>6180.83</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1884</v>
+        <v>6247.5</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1871</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>MANAKSTEEL</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>113.99</v>
+        <v>1057.65</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>106.92</v>
+        <v>1057.63</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>110.33</v>
+        <v>1058.04</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>110</v>
+        <v>1058.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>237.63</v>
+        <v>1010.08</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>229.23</v>
+        <v>1010.07</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>240.66</v>
+        <v>1010.57</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>240</v>
+        <v>1010.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MASKINVEST</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>149.26</v>
+        <v>116.17</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>141.32</v>
+        <v>116.15</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>150.95</v>
+        <v>116.2</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>152.8</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MAXIND</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>161.33</v>
+        <v>1123.7</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>151.04</v>
+        <v>1123.68</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>160.83</v>
+        <v>1124.12</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>158.25</v>
+        <v>1124.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>474.89</v>
+        <v>376.2</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>474.05</v>
+        <v>340.3</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>484.32</v>
+        <v>400.8</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>484.32</v>
+        <v>398</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>LOYALTEX</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>22.1</v>
+        <v>213.98</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>21.06</v>
+        <v>206.52</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>22.85</v>
+        <v>207.5</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>22.85</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MHLXMIRU</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>180.06</v>
+        <v>3254.07</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>173.13</v>
+        <v>3105.6</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>179.21</v>
+        <v>3267.8</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>179.95</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>428.95</v>
+        <v>4.23</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>407.78</v>
+        <v>3.93</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>437.65</v>
+        <v>3.99</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>434</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>1306</v>
+        <v>242.78</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1235.9</v>
+        <v>232.88</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1308.9</v>
+        <v>240.08</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1312</v>
+        <v>237.14</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>MASPTOP50</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>206.72</v>
+        <v>101.66</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>197.22</v>
+        <v>97.88</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>206.16</v>
+        <v>101.54</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>207.8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MSPL</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>34.53</v>
+        <v>484.38</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>32.66</v>
+        <v>483.55</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>33</v>
+        <v>494</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>33.35</v>
+        <v>494</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7448</v>
+        <v>22.88</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>7129</v>
+        <v>21.63</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>7797</v>
+        <v>23.11</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>7797</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>392.03</v>
+        <v>474.65</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>376.45</v>
+        <v>445.77</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>392.85</v>
+        <v>449.6</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>393</v>
+        <v>451.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>2458.23</v>
+        <v>468.17</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>2372.97</v>
+        <v>444.28</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>2451.6</v>
+        <v>486.05</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>2450.4</v>
+        <v>486.05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>MOLBIO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>224.68</v>
+        <v>1402.83</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>222.19</v>
+        <v>1269.17</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>224.96</v>
+        <v>1513.1</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>225.54</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>370.67</v>
+        <v>208.72</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>350.28</v>
+        <v>200.27</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>366.6</v>
+        <v>204.78</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>369.1</v>
+        <v>205.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>MONEYBOXX</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>1678.23</v>
+        <v>53.12</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1622.1</v>
+        <v>49.71</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1652.5</v>
+        <v>54</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1651.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>75.12</v>
+        <v>128.69</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>75.12</v>
+        <v>120.11</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>76.61</v>
+        <v>133.72</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>76.61</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>39.18</v>
+        <v>224.68</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>37.17</v>
+        <v>222.19</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>40.08</v>
+        <v>224.96</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>40.4</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>264.95</v>
+        <v>773.37</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>234.12</v>
+        <v>732.63</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>258.51</v>
+        <v>804.65</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>255</v>
+        <v>804.65</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>NIRLON</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>491</v>
+        <v>614.8</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>469.62</v>
+        <v>598.95</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>484.25</v>
+        <v>606.8</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>484.45</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>NPBET</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>1338.57</v>
+        <v>280.65</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1292.7</v>
+        <v>273.25</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>1311</v>
+        <v>277.6</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>1310.9</v>
+        <v>277.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>2.05</v>
+        <v>1701.47</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2.05</v>
+        <v>1638.03</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>2.09</v>
+        <v>1701.4</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2.09</v>
+        <v>1686.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>PATELRMART</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>213.92</v>
+        <v>76.62</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>205.02</v>
+        <v>76.62</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>211.52</v>
+        <v>78.14</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>212.39</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PAUSHAKLTD</t>
+          <t>OMFREIGHT</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>674.22</v>
+        <v>95.25</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>646.13</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>665.25</v>
+        <v>97.5</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>658.6</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PIXTRANS</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1753.57</v>
+        <v>586.58</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>1716.9</v>
+        <v>543.6799999999999</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1726.9</v>
+        <v>608.65</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1725</v>
+        <v>606.45</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>1118.03</v>
+        <v>40.57</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1078.23</v>
+        <v>38.6</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1120</v>
+        <v>41.57</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1120</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>POWERICA</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>606.7</v>
+        <v>74.3</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>570.02</v>
+        <v>70.56</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>600.6</v>
+        <v>74.37</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>601.5</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>PACEDIGITK</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>2465.23</v>
+        <v>168.61</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>2392.7</v>
+        <v>160.29</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2490.5</v>
+        <v>167.35</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>2488</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PRAKASH</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>123.9</v>
+        <v>61.22</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>116.41</v>
+        <v>54.93</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>123.72</v>
+        <v>60.91</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>122.86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>22658.33</v>
+        <v>2.09</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>21700</v>
+        <v>2.09</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>22190</v>
+        <v>2.13</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>22075</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>PFS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>1635.53</v>
+        <v>29.56</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1540.27</v>
+        <v>27.4</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>1584.8</v>
+        <v>28.81</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1585</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>QUICKHEAL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>148.38</v>
+        <v>1047.77</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>142.19</v>
+        <v>976.33</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>144.49</v>
+        <v>1037.7</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>144.2</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>291.32</v>
+        <v>18.27</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>269.57</v>
+        <v>16.53</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>285.98</v>
+        <v>18.09</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>286.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>590.33</v>
+        <v>135.69</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>567.67</v>
+        <v>130.12</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>582.4</v>
+        <v>138.16</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>579.5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>411.45</v>
+        <v>31198.33</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>401.52</v>
+        <v>30195</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>407</v>
+        <v>31290</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>407.4</v>
+        <v>31290</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>90.97</v>
+        <v>683.6799999999999</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>87.23</v>
+        <v>675.22</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>88.08</v>
+        <v>682.05</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>87.7</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RESPONIND</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>171.43</v>
+        <v>1486.3</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>160.36</v>
+        <v>1427.67</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>165.38</v>
+        <v>1486.1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>165.29</v>
+        <v>1486.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>PVTBANIETF</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>28.24</v>
+        <v>27.29</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>27.56</v>
+        <v>26.65</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>31.76</v>
+        <v>27.15</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>31.76</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RHETAN</t>
+          <t>PVTBANKADD</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>16.71</v>
+        <v>27.26</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>16.21</v>
+        <v>26.84</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>17.51</v>
+        <v>27.18</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>17.51</v>
+        <v>27.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>1475.27</v>
+        <v>861.33</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>1391.07</v>
+        <v>822.8200000000001</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>1503.2</v>
+        <v>840.65</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>1486</v>
+        <v>836.15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RPTECH</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4002,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>944.23</v>
+        <v>344.8</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>889.3</v>
+        <v>327.35</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>953.5</v>
+        <v>345.45</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>950.1</v>
+        <v>345</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RVTH</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4031,22 +4031,22 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>683.67</v>
+        <v>412.65</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>633.38</v>
+        <v>403.28</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>669.8</v>
+        <v>411.4</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>670</v>
+        <v>411.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>6.4</v>
+        <v>31.86</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>6.2</v>
+        <v>31.83</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>6.63</v>
+        <v>34.93</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>6.63</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>SALSTEEL</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4089,22 +4089,22 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>98.7</v>
+        <v>1517.27</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>93.08</v>
+        <v>1432.73</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>99.06</v>
+        <v>1522.3</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>98</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>SALZERELEC</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>543.1799999999999</v>
+        <v>1811.37</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>529.35</v>
+        <v>1715.33</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>536.4</v>
+        <v>1818.9</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>531.9</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SAPPL</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4147,22 +4147,22 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>299.33</v>
+        <v>172.63</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>276.7</v>
+        <v>165.77</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>300.1</v>
+        <v>174.43</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>303</v>
+        <v>175</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>RVTH</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>505.57</v>
+        <v>727.92</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>491.07</v>
+        <v>651.72</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>497.3</v>
+        <v>776.7</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>496</v>
+        <v>779</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4205,22 +4205,22 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>283.13</v>
+        <v>6.4</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>269.72</v>
+        <v>6.2</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>282.6</v>
+        <v>6.63</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>284.65</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SATIA</t>
+          <t>SADBHIN</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4234,22 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>69.75</v>
+        <v>2.64</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>67.26000000000001</v>
+        <v>2.51</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>69.7</v>
+        <v>2.62</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>69.34</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>SAPPL</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>1057.89</v>
+        <v>305.97</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>1057.87</v>
+        <v>284.73</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>1058.02</v>
+        <v>308.5</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>1058.02</v>
+        <v>311.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4292,22 +4292,22 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>1216.77</v>
+        <v>283.13</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1184.43</v>
+        <v>269.72</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>1203.4</v>
+        <v>282.6</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>1190</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SEKURITIND</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4321,22 +4321,22 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>112.64</v>
+        <v>1058.17</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>107.97</v>
+        <v>1058.15</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>110.93</v>
+        <v>1058.58</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>112.4</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>30.2</v>
+        <v>1245.03</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>30.19</v>
+        <v>1189.3</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>31.68</v>
+        <v>1275.4</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>31.68</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SGFIN</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4379,22 +4379,22 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>1061.7</v>
+        <v>617.55</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>1016.73</v>
+        <v>589.25</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1047.2</v>
+        <v>631.85</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>1041.95</v>
+        <v>631.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>767.67</v>
+        <v>1080.37</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>753.17</v>
+        <v>1028.93</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>770.4</v>
+        <v>1064.1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>766.5</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SHIVAUM</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>62.11</v>
+        <v>555.8</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>58.59</v>
+        <v>546.17</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>62.09</v>
+        <v>554.6</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>62.16</v>
+        <v>551.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>SHRJAGP</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4466,22 +4466,22 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>987.53</v>
+        <v>678.53</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>931.63</v>
+        <v>638.38</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1025.7</v>
+        <v>673</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>1025.7</v>
+        <v>673</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4495,22 +4495,22 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>201.81</v>
+        <v>63.75</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>198.28</v>
+        <v>60.26</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>203.98</v>
+        <v>61.8</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>204</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4524,22 +4524,22 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>827.4299999999999</v>
+        <v>45.69</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>797.37</v>
+        <v>43.71</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>810.7</v>
+        <v>44.91</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>811.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SOFTTECH</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>511</v>
+        <v>1026.5</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>486.35</v>
+        <v>990.6</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>493.5</v>
+        <v>1076.9</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>492.5</v>
+        <v>1076.9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4582,22 +4582,22 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>764.83</v>
+        <v>201.81</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>698.52</v>
+        <v>198.28</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>718.8</v>
+        <v>203.98</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>715</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4611,22 +4611,22 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>3767.57</v>
+        <v>66.16</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>3539.37</v>
+        <v>61.08</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>3846.1</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>3850</v>
+        <v>74.18000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>402.82</v>
+        <v>3872.27</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>385.93</v>
+        <v>3633.7</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>408.1</v>
+        <v>3853.4</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>406</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>STEELCITY</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4669,22 +4669,22 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>82.5</v>
+        <v>231.53</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>80.42</v>
+        <v>218.52</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>81.34999999999999</v>
+        <v>231.81</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>232</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>SWARAJ</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4698,22 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>1212.5</v>
+        <v>386.68</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>1148.13</v>
+        <v>363.03</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1205.8</v>
+        <v>377.55</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1202</v>
+        <v>375</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>SYMBIOTEC</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4727,22 +4727,22 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>463.9</v>
+        <v>1197.55</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>431.7</v>
+        <v>1114.78</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>456.05</v>
+        <v>1198</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>452.65</v>
+        <v>1197.3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>585.62</v>
+        <v>1796.33</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>523.53</v>
+        <v>1693.7</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>605</v>
+        <v>1717.9</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>596</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SUYOG</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>699.1799999999999</v>
+        <v>284.15</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>639.77</v>
+        <v>268.57</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>695.1</v>
+        <v>280.8</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>672.3</v>
+        <v>284</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SWARAJ</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4814,22 +4814,22 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>373.52</v>
+        <v>804.28</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>351.77</v>
+        <v>752.35</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>388.6</v>
+        <v>792.15</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>390.5</v>
+        <v>793</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SYMBIOTEC</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4843,22 +4843,22 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>1140.53</v>
+        <v>7.43</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1061.42</v>
+        <v>7.34</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1176.75</v>
+        <v>7.79</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>1179.55</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>UNITEDPOLY</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4872,22 +4872,22 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>25.85</v>
+        <v>47.55</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>22.23</v>
+        <v>45.92</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>25.08</v>
+        <v>47.05</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>24.9</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4901,22 +4901,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>779.27</v>
+        <v>941.63</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>731.77</v>
+        <v>933.52</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>786.05</v>
+        <v>939.25</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>781</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>7.08</v>
+        <v>21.82</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>7.02</v>
+        <v>21.05</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>7.42</v>
+        <v>22.86</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>7.42</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>186.57</v>
+        <v>452.52</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>180.75</v>
+        <v>409.3</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>182.36</v>
+        <v>477.15</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>182.8</v>
+        <v>470.05</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TTL</t>
+          <t>VELJAN</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4988,22 +4988,22 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>8.06</v>
+        <v>2192.3</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>7.17</v>
+        <v>2065.67</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>8.07</v>
+        <v>2296.1</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>8.19</v>
+        <v>2296.1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>941.63</v>
+        <v>0.51</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>933.52</v>
+        <v>0.44</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>939.25</v>
+        <v>0.68</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>VISACHROME</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>20.86</v>
+        <v>36.8</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>20.24</v>
+        <v>34.31</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>21.8</v>
+        <v>35.91</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>21.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>WEALTH</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>428.18</v>
+        <v>923</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>390.78</v>
+        <v>861.77</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>424.2</v>
+        <v>889.95</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>425.45</v>
+        <v>885.2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.51</v>
+        <v>235.29</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.44</v>
+        <v>224.61</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>0.68</v>
+        <v>239.17</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>0.68</v>
+        <v>239</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5133,103 +5133,16 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>131.33</v>
+        <v>51.03</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>126.4</v>
+        <v>48.58</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>129.66</v>
+        <v>51.65</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>129.4</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>VIDHIING</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>361.43</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>343.68</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>357.6</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>355.7</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>VINEETLAB</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>37.9</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>VIPULLTD</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>11.01</v>
+        <v>50.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>104.41</v>
+        <v>448.8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>99.65000000000001</v>
+        <v>436.22</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>103.85</v>
+        <v>453.7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>104.5</v>
+        <v>453.6</v>
       </c>
     </row>
     <row r="3">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.78</v>
+        <v>15.37</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>14.67</v>
+        <v>15.37</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15.36</v>
+        <v>16.12</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>15.36</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.79</v>
+        <v>1295.43</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12.2</v>
+        <v>1259.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12.56</v>
+        <v>1284</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.6</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACCELYA</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1120.83</v>
+        <v>212.97</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1086.57</v>
+        <v>203.82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1094.2</v>
+        <v>211.24</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1090</v>
+        <v>210.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1352.8</v>
+        <v>706.67</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1297.73</v>
+        <v>684.53</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1326.4</v>
+        <v>699.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1326.4</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1280.93</v>
+        <v>181.7</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1244.77</v>
+        <v>171.51</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1276.1</v>
+        <v>185.11</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1276.1</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADFFOODS</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>276.8</v>
+        <v>2131.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>263.4</v>
+        <v>2086.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>281.4</v>
+        <v>2132</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>281</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1386.07</v>
+        <v>1079.45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1308.4</v>
+        <v>1079.43</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1401.1</v>
+        <v>1079.71</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1401.6</v>
+        <v>1079.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>208.93</v>
+        <v>1196.2</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>199.78</v>
+        <v>1098.77</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>208.14</v>
+        <v>1223.3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>207.15</v>
+        <v>1217.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ALICON</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>833.73</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>758.33</v>
+        <v>593.95</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>871.95</v>
+        <v>597.15</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>884</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>698.33</v>
+        <v>2327.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>671.85</v>
+        <v>2160.77</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>702.4</v>
+        <v>2282.3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>705</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>181.7</v>
+        <v>120.57</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>171.51</v>
+        <v>118.88</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>185.11</v>
+        <v>121.12</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>184.5</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1079.16</v>
+        <v>378.82</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1079.14</v>
+        <v>378.8</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1079.57</v>
+        <v>386.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1079.59</v>
+        <v>386.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AUSTENG</t>
+          <t>BANG</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>170.98</v>
+        <v>33.23</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>157.54</v>
+        <v>31.22</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>167.72</v>
+        <v>33.28</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>169.45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1230.27</v>
+        <v>19.21</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1202.3</v>
+        <v>17.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1217.1</v>
+        <v>19.99</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1217.1</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>1083</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>593.95</v>
+        <v>1082.08</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>597.15</v>
+        <v>1082.41</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>597.09</v>
+        <v>1082.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2230.37</v>
+        <v>886.97</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2067.03</v>
+        <v>863.85</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2307.3</v>
+        <v>882.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2311.9</v>
+        <v>882.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>120.57</v>
+        <v>1847.8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>118.88</v>
+        <v>1768.83</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>121.12</v>
+        <v>1852</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>120.8</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AZADIND</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>87.45999999999999</v>
+        <v>231.22</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>81.33</v>
+        <v>220.69</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>85.95</v>
+        <v>227.65</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>87.98999999999999</v>
+        <v>227.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>371.43</v>
+        <v>4866.33</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>371.42</v>
+        <v>4763.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>378.75</v>
+        <v>4832.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>378.75</v>
+        <v>4832.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1082.2</v>
+        <v>6.9</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1081.79</v>
+        <v>6.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1082.28</v>
+        <v>7.03</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1082.29</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CLEDUCATE</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>57.88</v>
+        <v>1980.03</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>55.02</v>
+        <v>1769.73</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>57.91</v>
+        <v>2130.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.96</v>
+        <v>2166.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1823.07</v>
+        <v>26.07</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1744.9</v>
+        <v>26.07</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1826</v>
+        <v>26.59</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1826</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>226.16</v>
+        <v>157.88</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>215.76</v>
+        <v>148.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>230.04</v>
+        <v>157.86</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>230</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>306.18</v>
+        <v>14007</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>285.97</v>
+        <v>13386</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>312.5</v>
+        <v>14251</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>311.8</v>
+        <v>14375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>ECAPINSURE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.05</v>
+        <v>23.13</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.78</v>
+        <v>22.41</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.9</v>
+        <v>22.94</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.93</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>ELDEHSG</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>340.85</v>
+        <v>778.3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>322.2</v>
+        <v>756.12</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>342.95</v>
+        <v>773.55</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>344</v>
+        <v>786</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.77</v>
+        <v>1050.26</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.77</v>
+        <v>1050.24</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.9</v>
+        <v>1050.52</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.9</v>
+        <v>1050.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>EMAMIREAL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>72.93000000000001</v>
+        <v>69.19</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>70.75</v>
+        <v>67.03</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>72.61</v>
+        <v>68.06</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>73</v>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3864.67</v>
+        <v>15.51</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3765.7</v>
+        <v>14.33</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3813</v>
+        <v>16.51</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3813</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1801.97</v>
+        <v>473.82</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1604.5</v>
+        <v>441.62</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1874</v>
+        <v>478.15</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1880</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>FERMENTA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>25.56</v>
+        <v>569.5700000000001</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>25.56</v>
+        <v>537.83</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>26.07</v>
+        <v>557.45</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>26.07</v>
+        <v>555.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>152.99</v>
+        <v>3.02</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>143.4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>158.57</v>
+        <v>3.07</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>159.82</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>GANDHITUBE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>13598.33</v>
+        <v>989.5</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>13027.67</v>
+        <v>954.53</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>13756</v>
+        <v>993.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>13800</v>
+        <v>998</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EBANK10</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>16.2</v>
+        <v>685</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>15.82</v>
+        <v>670.22</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>16.19</v>
+        <v>681.75</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>16.2</v>
+        <v>683.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>GPTINFRA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1049.99</v>
+        <v>121.3</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1049.97</v>
+        <v>116.01</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1050.39</v>
+        <v>120.38</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1050.38</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ELPROINTL</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>173.91</v>
+        <v>2.36</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>170.49</v>
+        <v>2.34</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>174.31</v>
+        <v>2.47</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>174.74</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EMAMIREAL</t>
+          <t>GREENPLY</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>68.70999999999999</v>
+        <v>307.55</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>66.72</v>
+        <v>293.28</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>67.14</v>
+        <v>308.45</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>67.02</v>
+        <v>308.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ESTER</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>97.36</v>
+        <v>35.39</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>88.14</v>
+        <v>35.39</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>95.52</v>
+        <v>37.67</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>GULFPETRO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>459.53</v>
+        <v>63.03</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>426.3</v>
+        <v>60.48</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>475.3</v>
+        <v>62.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>469.5</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>HAWKINCOOK</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2.97</v>
+        <v>8077.17</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2.96</v>
+        <v>7874.67</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>3.02</v>
+        <v>7977</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3.02</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FMNL</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.43</v>
+        <v>2334.87</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>7.87</v>
+        <v>2276.8</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>8.08</v>
+        <v>2346</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>8.18</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GALAXYSURF</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>2397.03</v>
+        <v>533.05</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2276.73</v>
+        <v>518.45</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>2376.9</v>
+        <v>531</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2362</v>
+        <v>531</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>HDFCPVTBAN</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>679.17</v>
+        <v>27.71</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>664.58</v>
+        <v>27.01</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>679.9</v>
+        <v>27.3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>680.1</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>190.73</v>
+        <v>237.25</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>176.16</v>
+        <v>227.58</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>194.27</v>
+        <v>248.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>194.65</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>166.23</v>
+        <v>238.55</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>159.99</v>
+        <v>229.37</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>165.88</v>
+        <v>250.27</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>165.9</v>
+        <v>250.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GPTINFRA</t>
+          <t>HILTON</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>119.66</v>
+        <v>17.08</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>114.72</v>
+        <v>16.27</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>118.66</v>
+        <v>16.77</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>118</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2.26</v>
+        <v>35.22</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2.2</v>
+        <v>33.94</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2.36</v>
+        <v>36.94</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2.36</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GREENPLY</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>297.82</v>
+        <v>16.54</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>283</v>
+        <v>15.65</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>303.7</v>
+        <v>16.9</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>304</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>32.72</v>
+        <v>1037.1</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>32.72</v>
+        <v>1000.45</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>35.88</v>
+        <v>1020.5</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>35.88</v>
+        <v>1020.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>62.63</v>
+        <v>1604.33</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>59.75</v>
+        <v>1523.4</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>62.45</v>
+        <v>1612.1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>62</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>4273.8</v>
+        <v>213.23</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>4150.37</v>
+        <v>203.14</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>4253.2</v>
+        <v>205.71</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>4253.2</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HBSL</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>57.67</v>
+        <v>314.57</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>55.26</v>
+        <v>306.91</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>57.03</v>
+        <v>312.02</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>57.43</v>
+        <v>310.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2312.7</v>
+        <v>131.47</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2248.53</v>
+        <v>125.18</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2308.1</v>
+        <v>127.98</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2308.1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HDFCPVTBAN</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>27.43</v>
+        <v>4282.8</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>26.87</v>
+        <v>4084.13</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>27.37</v>
+        <v>4193.7</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>27</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>237.25</v>
+        <v>382.13</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>227.58</v>
+        <v>359.05</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>248.5</v>
+        <v>379.2</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>248.5</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>68.63</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>65.27</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>68.8</v>
+        <v>0.08</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>69.03</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>227.2</v>
+        <v>221.26</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>217.71</v>
+        <v>197.05</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>238.36</v>
+        <v>213.99</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>238.37</v>
+        <v>215.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HMVL</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>76.02</v>
+        <v>1057.92</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>71.02</v>
+        <v>1057.85</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>77.44</v>
+        <v>1058.17</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>78.3</v>
+        <v>1058.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1578.23</v>
+        <v>1147.44</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1524.13</v>
+        <v>1147.41</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1563</v>
+        <v>1147.71</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1563</v>
+        <v>1147.71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IDEAFORGE</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>745.42</v>
+        <v>1010.08</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>716.3</v>
+        <v>1010.07</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>735</v>
+        <v>1010.57</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>731.2</v>
+        <v>1010.57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IITL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>137.32</v>
+        <v>116.21</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>126.54</v>
+        <v>116.19</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>132.56</v>
+        <v>116.22</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>139</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>33.55</v>
+        <v>1123.99</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>31.8</v>
+        <v>1123.97</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>35.19</v>
+        <v>1124.28</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>35.19</v>
+        <v>1124.28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>377.93</v>
+        <v>410.65</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>365.6</v>
+        <v>365.17</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>376.25</v>
+        <v>446.25</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>376.25</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>16.54</v>
+        <v>3280.23</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>15.65</v>
+        <v>3155.33</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>16.9</v>
+        <v>3219.5</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>16.84</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1024.8</v>
+        <v>250.64</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>990.58</v>
+        <v>240.61</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1035</v>
+        <v>259.42</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1035</v>
+        <v>260.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>MASPTOP50</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1568.53</v>
+        <v>104.66</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1480.03</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1595.2</v>
+        <v>107.09</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1601</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>209.35</v>
+        <v>1601.43</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>200.44</v>
+        <v>1546.87</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>209.39</v>
+        <v>1608.2</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>210.5</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ITAXIS</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>313.27</v>
+        <v>494.06</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>305.08</v>
+        <v>494.06</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>309.81</v>
+        <v>503.85</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>309</v>
+        <v>503.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>MBLINFRA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>129.77</v>
+        <v>23.67</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>123.02</v>
+        <v>22.23</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>130.8</v>
+        <v>23.9</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>131</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>JHS</t>
+          <t>MMWL</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>12.24</v>
+        <v>15.57</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>10.27</v>
+        <v>15.19</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>11.7</v>
+        <v>16.33</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>11.65</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>MOLDTECH</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>373.6</v>
+        <v>211.32</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>349.05</v>
+        <v>203.39</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>371.15</v>
+        <v>213.5</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>371.75</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>421.33</v>
+        <v>133.68</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>405.57</v>
+        <v>124.47</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>418.35</v>
+        <v>135.29</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>418.35</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KREBSBIO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>64.73</v>
+        <v>2286.53</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>56.51</v>
+        <v>2181.37</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>68.05</v>
+        <v>2297.1</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>2297.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>224.68</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>222.19</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.08</v>
+        <v>224.96</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.08</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>LAXMICOT</t>
+          <t>NILE</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>13.5</v>
+        <v>1295.2</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>12.84</v>
+        <v>1209.07</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>13.3</v>
+        <v>1226</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>13.44</v>
+        <v>1217.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>107.23</v>
+        <v>807.83</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>103.32</v>
+        <v>769.77</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>107.67</v>
+        <v>842</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>107.25</v>
+        <v>842.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>NORBTEAEXP</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>206.26</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>186.05</v>
+        <v>63.42</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>219.47</v>
+        <v>65.59</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>219</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>6389</v>
+        <v>1764.07</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>6180.83</v>
+        <v>1668.13</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>6247.5</v>
+        <v>1820.8</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>6202</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1057.65</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1057.63</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1058.04</v>
+        <v>79.7</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1058.05</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>OMFREIGHT</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1010.08</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>1010.07</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1010.57</v>
+        <v>100.95</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1010.57</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>116.17</v>
+        <v>612.67</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>116.15</v>
+        <v>574.55</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>116.2</v>
+        <v>632.15</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>116.22</v>
+        <v>635</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>1123.7</v>
+        <v>42.05</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1123.68</v>
+        <v>40.27</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1124.12</v>
+        <v>43.52</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1124.13</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>ONEPOINT</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>376.2</v>
+        <v>76.63</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>340.3</v>
+        <v>72.64</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>400.8</v>
+        <v>78.33</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>398</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LOYALTEX</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>213.98</v>
+        <v>80.53</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>206.52</v>
+        <v>77.19</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>207.5</v>
+        <v>81.13</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>207</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>3254.07</v>
+        <v>64.62</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>3105.6</v>
+        <v>58.01</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3267.8</v>
+        <v>63.5</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3279</v>
+        <v>64.31</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>4.23</v>
+        <v>2.13</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>3.93</v>
+        <v>2.13</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>3.99</v>
+        <v>2.17</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>3.99</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>242.78</v>
+        <v>138.26</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>232.88</v>
+        <v>132.83</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>240.08</v>
+        <v>137.03</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>237.14</v>
+        <v>136.47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MASPTOP50</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>101.66</v>
+        <v>31560</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>97.88</v>
+        <v>30700</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>101.54</v>
+        <v>31500</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>102</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>484.38</v>
+        <v>686.87</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>483.55</v>
+        <v>678.05</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>494</v>
+        <v>685.05</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>494</v>
+        <v>685</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MBLINFRA</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>22.88</v>
+        <v>352.2</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>21.63</v>
+        <v>331.82</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>23.11</v>
+        <v>339.35</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>23.5</v>
+        <v>340.35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>474.65</v>
+        <v>416.68</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>445.77</v>
+        <v>406.2</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>449.6</v>
+        <v>416.55</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>451.1</v>
+        <v>416.55</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>RELINFRA</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3190,22 +3190,22 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>468.17</v>
+        <v>46.52</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>444.28</v>
+        <v>45.95</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>486.05</v>
+        <v>48.8</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>486.05</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>1402.83</v>
+        <v>1562.23</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>1269.17</v>
+        <v>1477.03</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>1513.1</v>
+        <v>1607.2</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1507</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3248,22 +3248,22 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>208.72</v>
+        <v>177.62</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>200.27</v>
+        <v>169.35</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>204.78</v>
+        <v>175.57</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>205.9</v>
+        <v>175.99</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>53.12</v>
+        <v>6.4</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>49.71</v>
+        <v>6.2</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>54</v>
+        <v>6.63</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>54</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>SAPPL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3306,22 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>128.69</v>
+        <v>318.3</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>120.11</v>
+        <v>294.7</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>133.72</v>
+        <v>327.1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>133.6</v>
+        <v>320.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>224.68</v>
+        <v>283.13</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>222.19</v>
+        <v>269.72</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>224.96</v>
+        <v>282.6</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>225.54</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>773.37</v>
+        <v>1058.46</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>732.63</v>
+        <v>1058.44</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>804.65</v>
+        <v>1058.76</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>804.65</v>
+        <v>1058.77</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NIRLON</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>614.8</v>
+        <v>1279.97</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>598.95</v>
+        <v>1215.5</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>606.8</v>
+        <v>1268.1</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>605</v>
+        <v>1281.7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NPBET</t>
+          <t>SGFIN</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3422,22 +3422,22 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>280.65</v>
+        <v>648.4</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>273.25</v>
+        <v>613.88</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>277.6</v>
+        <v>677.95</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>277.6</v>
+        <v>679</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>SHRJAGP</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>1701.47</v>
+        <v>702.27</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1638.03</v>
+        <v>658.35</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1701.4</v>
+        <v>685</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>1686.3</v>
+        <v>685</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>76.62</v>
+        <v>67.55</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>76.62</v>
+        <v>61.42</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>78.14</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>78.14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>OMFREIGHT</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3509,22 +3509,22 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>95.25</v>
+        <v>5.25</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>88.98999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>97.5</v>
+        <v>5.07</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>97</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>586.58</v>
+        <v>201.81</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>543.6799999999999</v>
+        <v>198.28</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>608.65</v>
+        <v>203.98</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>606.45</v>
+        <v>204</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3567,22 +3567,22 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>40.57</v>
+        <v>218.39</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>38.6</v>
+        <v>209.57</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>41.57</v>
+        <v>222.7</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>41.5</v>
+        <v>222.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ONEPOINT</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>74.3</v>
+        <v>105.91</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>70.56</v>
+        <v>93.63</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>74.37</v>
+        <v>114.5</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>74.2</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PACEDIGITK</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3625,22 +3625,22 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>168.61</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>160.29</v>
+        <v>67.33</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>167.35</v>
+        <v>78.72</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>167</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>SUPREME</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>61.22</v>
+        <v>31.75</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>54.93</v>
+        <v>30.08</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>60.91</v>
+        <v>30.91</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>62</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>2.09</v>
+        <v>823.3200000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>2.09</v>
+        <v>779.6799999999999</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>2.13</v>
+        <v>812.9</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>2.13</v>
+        <v>814.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PFS</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>29.56</v>
+        <v>7.79</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>27.4</v>
+        <v>7.7</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>28.81</v>
+        <v>8.17</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>28.7</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>1047.77</v>
+        <v>941.63</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>976.33</v>
+        <v>933.52</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1037.7</v>
+        <v>939.25</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1050</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>18.27</v>
+        <v>22.9</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>16.53</v>
+        <v>22.22</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>18.09</v>
+        <v>23.98</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>135.69</v>
+        <v>483.53</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>130.12</v>
+        <v>439.35</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>138.16</v>
+        <v>475.65</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>139</v>
+        <v>475</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>VCL</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3828,22 +3828,22 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>31198.33</v>
+        <v>1.37</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>30195</v>
+        <v>1.31</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>31290</v>
+        <v>1.43</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>31290</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>VELJAN</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>683.6799999999999</v>
+        <v>2297.93</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>675.22</v>
+        <v>2183.7</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>682.05</v>
+        <v>2410.9</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>680</v>
+        <v>2410.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3886,22 +3886,22 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1486.3</v>
+        <v>0.51</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1427.67</v>
+        <v>0.44</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1486.1</v>
+        <v>0.68</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1486.1</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PVTBANIETF</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>27.29</v>
+        <v>5.78</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>26.65</v>
+        <v>5.71</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>27.15</v>
+        <v>5.99</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>27.47</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PVTBANKADD</t>
+          <t>XELPMOC</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>27.26</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>26.84</v>
+        <v>82.28</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>27.18</v>
+        <v>89.86</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>27.01</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>ZODIAC</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3973,1176 +3973,16 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>861.33</v>
+        <v>219.76</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>822.8200000000001</v>
+        <v>210.44</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>840.65</v>
+        <v>215.1</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>836.15</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>RATNAVEER</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>344.8</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>327.35</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>345.45</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>412.65</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>403.28</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>411.4</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>411.4</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>RETAIL</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>31.83</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>34.93</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>34.93</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>ROSSTECH</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>1517.27</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>1432.73</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>1522.3</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>RPEL</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>1811.37</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>1715.33</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>1818.9</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>172.63</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>165.77</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>174.43</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>RVTH</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>727.92</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>651.72</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SADBHIN</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SAPPL</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>305.97</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>284.73</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>308.5</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>311.6</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>1058.17</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>1058.15</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>1058.58</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>1058.59</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>1245.03</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>1189.3</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>1275.4</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>SGFIN</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>617.55</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>589.25</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>631.85</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>631.9</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>SHILPAMED</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>1080.37</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>1028.93</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>1064.1</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>SHIVAUM</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>555.8</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>546.17</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>554.6</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>551.5</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>SHRJAGP</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>678.53</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>638.38</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>673</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>SHUKRAPHAR</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>60.26</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SIGMA</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SIGMAADV</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>1026.5</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>990.6</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>1076.9</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>1076.9</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>SMLT</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>74.18000000000001</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>74.18000000000001</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>3872.27</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>3633.7</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>3853.4</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>3867</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>STALLION</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>231.53</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>218.52</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>231.81</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SWARAJ</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>386.68</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>363.03</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>377.55</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>SYMBIOTEC</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>1197.55</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>1114.78</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>1198</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>1197.3</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>1796.33</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>1693.7</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>1717.9</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>TARIL</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>284.15</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>268.57</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>280.8</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>TDPOWERSYS</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>804.28</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>752.35</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>792.15</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>TICL</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>7.79</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>UNITEDPOLY</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>46.99</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>UYFINCORP</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>22.89</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>VALIANTORG</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>452.52</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>409.3</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>477.15</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>470.05</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>VELJAN</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>2192.3</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>2065.67</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>2296.1</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>2296.1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G157" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>VISACHROME</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>35.91</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>WEALTH</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>923</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>861.77</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>889.95</v>
-      </c>
-      <c r="G159" s="3" t="n">
-        <v>885.2</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>WELSPUNLIV</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>235.29</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>224.61</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>239.17</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>WEWIN</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="G161" s="3" t="n">
-        <v>50.75</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>39.52</v>
+        <v>41.1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>38.33</v>
+        <v>39.76</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>41.07</v>
+        <v>43.12</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>41.07</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AARVI</t>
+          <t>AGRITECH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>141.49</v>
+        <v>96.03</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>136.15</v>
+        <v>88.05</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>138.26</v>
+        <v>95.7</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>138.02</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>17.77</v>
+        <v>181.7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>17.56</v>
+        <v>171.51</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>18.64</v>
+        <v>185.11</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18.64</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>ANNU</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>217.69</v>
+        <v>46.97</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>209</v>
+        <v>44.8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>216.09</v>
+        <v>47.01</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>213</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ALKALI</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>90.02</v>
+        <v>1081.93</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>1080.25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>89.15000000000001</v>
+        <v>1080.61</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>89</v>
+        <v>1080.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8.6</v>
+        <v>1278.37</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7.76</v>
+        <v>1198.97</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9</v>
+        <v>1337.8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9.08</v>
+        <v>1337.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>40.66</v>
+        <v>147.43</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>38.39</v>
+        <v>136.41</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>40.27</v>
+        <v>148.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>40</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>181.7</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>171.51</v>
+        <v>593.95</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>185.11</v>
+        <v>597.15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>184.5</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ANNU</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46.25</v>
+        <v>120.57</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>44.04</v>
+        <v>118.88</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46.33</v>
+        <v>121.12</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>46.7</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1080.03</v>
+        <v>409.9</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1080</v>
+        <v>409.88</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1080.17</v>
+        <v>418</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1080.18</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARFIN</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>104.98</v>
+        <v>913.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>95.81</v>
+        <v>841.6799999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>107.52</v>
+        <v>892.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>106.48</v>
+        <v>887.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>265.91</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>93.25</v>
+        <v>255.37</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>95.62</v>
+        <v>272.43</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>95.15000000000001</v>
+        <v>272.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ARVSMART</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>616.15</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>591.28</v>
+        <v>62.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>608.5</v>
+        <v>70.13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>605.4</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1435</v>
+        <v>22.89</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1382.43</v>
+        <v>21.74</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1408.5</v>
+        <v>23.54</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1408.5</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHOICEGOLD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>25.71</v>
+        <v>146.67</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>24.37</v>
+        <v>144.9</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>25.18</v>
+        <v>147.08</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>25.1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AVADHSUGAR</t>
+          <t>CPEDU</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>941.85</v>
+        <v>183.64</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>884.1</v>
+        <v>177.45</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>939.55</v>
+        <v>183.95</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>943.75</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>1282.63</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>593.95</v>
+        <v>1237.8</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>597.15</v>
+        <v>1267.5</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>597.09</v>
+        <v>1265.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>120.57</v>
+        <v>1603.83</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>118.88</v>
+        <v>1559.9</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>121.12</v>
+        <v>1621.9</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>120.8</v>
+        <v>1620.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>401.9</v>
+        <v>21.45</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>401.55</v>
+        <v>20.09</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>409.85</v>
+        <v>23.03</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>409.85</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>883.75</v>
+        <v>28.21</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>824.23</v>
+        <v>28.21</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>856.55</v>
+        <v>28.77</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>852.1</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BEDMUTHA</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>110.85</v>
+        <v>1051.09</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>106.66</v>
+        <v>1051.02</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>108.5</v>
+        <v>1051.42</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>108</v>
+        <v>1051.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>256.63</v>
+        <v>1.84</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>247.04</v>
+        <v>1.79</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>259.46</v>
+        <v>1.91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>259.05</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BHARATGEAR</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>105.22</v>
+        <v>327.83</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>101.4</v>
+        <v>319.15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>105.73</v>
+        <v>330</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>106.94</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1475.43</v>
+        <v>3.25</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1401.2</v>
+        <v>3.21</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1500.7</v>
+        <v>3.25</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1500</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BPLPHARMA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1922.57</v>
+        <v>302.88</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1806.17</v>
+        <v>287.9</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1892.8</v>
+        <v>296.55</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1890</v>
+        <v>295.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>GLOBALE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>64.26000000000001</v>
+        <v>11.57</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>57.27</v>
+        <v>10.81</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>12.01</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>70.53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3355.53</v>
+        <v>111.09</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3254.67</v>
+        <v>111.08</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3334.8</v>
+        <v>111.11</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3334.8</v>
+        <v>111.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>GSEC10ADD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.04</v>
+        <v>26.44</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21.03</v>
+        <v>26.39</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>23.08</v>
+        <v>26.53</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>23.12</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COFFEEDAY</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>31.86</v>
+        <v>553.37</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>29.6</v>
+        <v>542.58</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>30.53</v>
+        <v>556.65</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>30.41</v>
+        <v>556.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>342.32</v>
+        <v>1081.32</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>326.37</v>
+        <v>1081.3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>356.65</v>
+        <v>1081.65</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>356.75</v>
+        <v>1081.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>7.31</v>
+        <v>237.25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>7.31</v>
+        <v>227.58</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>7.45</v>
+        <v>248.5</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>7.45</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DHABRIYA</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>479.65</v>
+        <v>533.83</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>452.23</v>
+        <v>508.22</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>485.95</v>
+        <v>538.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>488</v>
+        <v>542</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DSFCL</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>29.67</v>
+        <v>48.91</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>27.92</v>
+        <v>46.22</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>28.76</v>
+        <v>49.59</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>29.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>27.66</v>
+        <v>428.18</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>27.66</v>
+        <v>406.73</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>28.21</v>
+        <v>426.85</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>28.21</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DSSL</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1067.22</v>
+        <v>1643</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1000.63</v>
+        <v>1594.63</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1030.1</v>
+        <v>1690.2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1027</v>
+        <v>1690.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>721.85</v>
+        <v>648.75</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>679.6</v>
+        <v>629.4299999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>714.15</v>
+        <v>643.45</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>725</v>
+        <v>643.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>729.13</v>
+        <v>16.54</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>673.3</v>
+        <v>15.65</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>692.15</v>
+        <v>16.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>690</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1050.84</v>
+        <v>1017.52</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1050.78</v>
+        <v>996.77</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1050.97</v>
+        <v>1023.4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1050.97</v>
+        <v>1023.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>ITADD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1.76</v>
+        <v>30.19</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.72</v>
+        <v>29.45</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1.83</v>
+        <v>30.37</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.84</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ESDS</t>
+          <t>KAVDEFENCE</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1360.07</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1330.2</v>
+        <v>88.55</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1426.9</v>
+        <v>92.19</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1426.9</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FAIRCHEMOR</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>734.5</v>
+        <v>17.38</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>686.5</v>
+        <v>16.74</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>720.9</v>
+        <v>17.17</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>713.9</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>3.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>3.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>3.25</v>
+        <v>0.08</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>3.25</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FREDUN</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1545.73</v>
+        <v>539.72</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1407.53</v>
+        <v>517.28</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1531.7</v>
+        <v>551.65</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1538</v>
+        <v>551.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>270.23</v>
+        <v>1148.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>258.08</v>
+        <v>1148.28</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>266.35</v>
+        <v>1148.65</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>263.4</v>
+        <v>1148.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GAJA</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>146.87</v>
+        <v>1011.17</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>139.33</v>
+        <v>1011.17</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>145.1</v>
+        <v>1011.55</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>146</v>
+        <v>1011.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>296.23</v>
+        <v>116.29</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>283.22</v>
+        <v>116.27</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>296.45</v>
+        <v>116.32</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>300</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.59</v>
+        <v>1124.81</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.49</v>
+        <v>1124.79</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.51</v>
+        <v>1125.13</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.53</v>
+        <v>1125.13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GILLETTE</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>7239.5</v>
+        <v>1683.9</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>7007.67</v>
+        <v>1622.13</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>7263.5</v>
+        <v>1679.9</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>7290</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GLFL</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>5.65</v>
+        <v>1310.67</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>5.09</v>
+        <v>1272.83</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>5.6</v>
+        <v>1312.7</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>5.16</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>METROBRAND</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>505.27</v>
+        <v>849.1</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>486.72</v>
+        <v>819.52</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>496.8</v>
+        <v>864.65</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>494.5</v>
+        <v>870</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>MLKFOOD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>197.1</v>
+        <v>86.78</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>188.92</v>
+        <v>84.5</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>192.6</v>
+        <v>87.16</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>193.2</v>
+        <v>87.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>111.06</v>
+        <v>2356</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>111.05</v>
+        <v>2292.13</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>111.07</v>
+        <v>2360</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>111.08</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSEC10ADD</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>26.44</v>
+        <v>224.68</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>26.39</v>
+        <v>222.19</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>26.53</v>
+        <v>224.96</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>26.53</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>OILCOUNTUB</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>490.98</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>467.98</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>492.1</v>
+        <v>86.25</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>490.2</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GUJRAFFIA</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>44.15</v>
+        <v>49.58</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>40.72</v>
+        <v>47.17</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>43.47</v>
+        <v>50.06</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>43.5</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>ONWARDTEC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1081.07</v>
+        <v>305.37</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1080.95</v>
+        <v>292.9</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1081.2</v>
+        <v>307</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1081.2</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HEALTHX</t>
+          <t>ORIENTELEC</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>297.28</v>
+        <v>164.67</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>281.7</v>
+        <v>160.09</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>292.9</v>
+        <v>164.77</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>293</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>PARNAXLAB</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>237.25</v>
+        <v>117.88</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>227.58</v>
+        <v>111.89</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>248.5</v>
+        <v>115.16</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>248.5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HEXATRADEX</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>158.17</v>
+        <v>2.29</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>153.12</v>
+        <v>2.29</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>155.1</v>
+        <v>2.33</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>156.8</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>510.33</v>
+        <v>14.21</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>496.25</v>
+        <v>13.42</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>511.4</v>
+        <v>14.81</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>513.05</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>47.35</v>
+        <v>116.83</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>44.95</v>
+        <v>113.05</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>47.69</v>
+        <v>116.98</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>47.77</v>
+        <v>116.98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>416.55</v>
+        <v>1160.4</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>399.73</v>
+        <v>1129.6</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>417</v>
+        <v>1158</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>414</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HINDOILEXP</t>
+          <t>RAJRILTD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>171.93</v>
+        <v>20.81</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>165.79</v>
+        <v>20.81</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>169.4</v>
+        <v>21.22</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>169.75</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>RAMBHAJO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>350.83</v>
+        <v>366.02</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>343.03</v>
+        <v>340.52</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>350.55</v>
+        <v>357.45</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>RELINFRA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>89.37</v>
+        <v>56.53</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>77.93000000000001</v>
+        <v>54.65</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>97.27</v>
+        <v>59.29</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>94.01000000000001</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>34.11</v>
+        <v>6.4</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>31.23</v>
+        <v>6.2</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>34.88</v>
+        <v>6.63</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>35</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ICEMAKE</t>
+          <t>SAMBHAAV</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>670.17</v>
+        <v>5.91</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>630.08</v>
+        <v>5.06</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>660.25</v>
+        <v>5.68</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>653.95</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1354.77</v>
+        <v>283.13</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1332.6</v>
+        <v>269.72</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1349</v>
+        <v>282.6</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1349</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>368.82</v>
+        <v>1059.3</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>325.32</v>
+        <v>1059.28</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>356.9</v>
+        <v>1059.62</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>353.8</v>
+        <v>1059.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>SHIVAUM</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>16.54</v>
+        <v>554.33</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>15.65</v>
+        <v>547.23</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>16.9</v>
+        <v>552.75</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>16.84</v>
+        <v>555</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>201.81</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>64.28</v>
+        <v>198.28</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>68.61</v>
+        <v>203.98</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>68.05</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>JAIPURKURT</t>
+          <t>SIMPLXREA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>30.65</v>
+        <v>125.5</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>27.25</v>
+        <v>123.48</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>32.4</v>
+        <v>131.65</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>32.39</v>
+        <v>131.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JKIPL</t>
+          <t>STERTOOLS</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>102.42</v>
+        <v>232.28</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>96.52</v>
+        <v>219.6</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>103.48</v>
+        <v>225.24</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>106.75</v>
+        <v>224.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE</t>
+          <t>SWANDEF</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>2813.27</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>86.48</v>
+        <v>2670.37</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>93.66</v>
+        <v>2816.8</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>92.2</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KMCSHIL</t>
+          <t>TAKE</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>180.69</v>
+        <v>12.73</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>170.69</v>
+        <v>12.54</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>177.28</v>
+        <v>13.35</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>177.58</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KOTYARK</t>
+          <t>TARAPUR</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>31.37</v>
+        <v>14.22</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>28.74</v>
+        <v>13.19</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>31.06</v>
+        <v>16.58</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>30.5</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1524.87</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1490.8</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.08</v>
+        <v>1514.1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.08</v>
+        <v>1514.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>TECHNVISN</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1148.04</v>
+        <v>4411.17</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1148.02</v>
+        <v>4223.33</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1148.18</v>
+        <v>4487.7</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1148.2</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1010.84</v>
+        <v>4897.83</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1010.84</v>
+        <v>4748.17</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1011.11</v>
+        <v>4889.5</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1011.11</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>TOYAMSL</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>1102.23</v>
+        <v>0.74</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1101.9</v>
+        <v>0.72</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1102.07</v>
+        <v>0.76</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1102.08</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>116.27</v>
+        <v>179.3</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>116.25</v>
+        <v>162.88</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>116.27</v>
+        <v>181.76</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>116.28</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1124.57</v>
+        <v>20.07</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1124.55</v>
+        <v>18.43</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1124.71</v>
+        <v>18.96</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1124.72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LOTUSCHO</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>667.5</v>
+        <v>941.63</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>593.63</v>
+        <v>933.52</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>658.9</v>
+        <v>939.25</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>653.7</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MANBA</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>144.93</v>
+        <v>24.1</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>139.88</v>
+        <v>22.48</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>146.82</v>
+        <v>24.76</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>147.99</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>VASUPRADA</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1648.13</v>
+        <v>99.3</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1600.43</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1651.2</v>
+        <v>99.5</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1648</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MATRIMONY</t>
+          <t>VERANDA</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>538.42</v>
+        <v>32.78</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>507.42</v>
+        <v>32.1</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>517.8</v>
+        <v>34.39</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>515</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MEGASTAR</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>308.6</v>
+        <v>0.51</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>280.46</v>
+        <v>0.44</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>292.31</v>
+        <v>0.68</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>290.25</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>VHLTD</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>332.25</v>
+        <v>136.85</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>313.3</v>
+        <v>132</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>328.35</v>
+        <v>142.9</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>329.8</v>
+        <v>142.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MLKFOOD</t>
+          <t>VIRAT</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.02</v>
+        <v>416.65</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>83.22</v>
+        <v>376.35</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>85.15000000000001</v>
+        <v>435.4</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>425</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>501.52</v>
+        <v>828.75</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>469.72</v>
+        <v>789.4</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>483.25</v>
+        <v>821.95</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>484.5</v>
+        <v>817.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>18.3</v>
+        <v>94.98</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>18.04</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>19.77</v>
+        <v>97.52</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>19.78</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>MONQ50</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,1756 +3161,16 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>258.68</v>
+        <v>455.08</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>213.52</v>
+        <v>439.78</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>243.73</v>
+        <v>448.55</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>241.99</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>MOTOGENFIN</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>25.26</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>2327</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>2273.63</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>2303.4</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>2303.4</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>NAVKARURB</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>NELCAST</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>142.07</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>125.91</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>141.52</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>NIFMID150</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>224.68</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>222.19</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>224.96</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>225.54</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>OILCOUNTUB</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>84.56</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>84.56</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>OMPOWER</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>167.09</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>157.25</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>166.11</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>164.37</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>ONEGLOBAL</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>586.65</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>548.25</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>561.3</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>556.05</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>ONELIFECAP</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>45.02</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>49.51</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>ONIXSOLAR</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>358.33</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>344.33</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>371.2</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>372.85</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>ONMOBILE</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>51.89</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>49.07</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>ONWARDTEC</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>300.28</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>290.78</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>294.6</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>293.8</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>ORCHASP</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>PARAGMILK</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>314.23</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>294.15</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>303.25</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>PARSVNATH</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>PCJEWELLER</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>13.92</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>PERMAGN</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>889.15</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>845.7</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>855.75</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>853.05</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>1139.6</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>1108.03</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>PNGSREVA</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>650.5700000000001</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>571.3200000000001</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>701.95</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>676.95</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>PREMIER</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>PREMIERPOL</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>104.7</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>96.55</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>98.25</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>PWL</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>138.99</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>131.22</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>140.48</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>RAJOOENG</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>59.92</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>RAJRILTD</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>20.81</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>RAMBHAJO</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>353.38</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>327.03</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>356.55</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>354.8</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>RELINFRA</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>53.84</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>56.49</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>REPCOHOME</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>341.98</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>328.25</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>337.1</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>337.6</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>RHETAN</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>18.27</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>SAHLIBHFI</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>79.37</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>77.91</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>77.98999999999999</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>1059.06</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>1059.04</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>1059.18</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>1059.18</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SEJALLTD</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>717.62</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>662.33</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>678.55</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>SHANTI</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SHYAMMETL</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>1068.1</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>1038.83</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>1066.8</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>1072.9</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SILINV</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>467.8</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>455</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>462.1</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SRTL</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>36.49</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>STUDDS</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>422.52</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>403.28</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>416</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>418.95</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SUPTANERY</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>8.890000000000001</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>TECHNVISN</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>4215.8</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>4030.43</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>4384.5</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>4410</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>TFCILTD</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>142.05</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>146.65</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>TOYAMSL</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>TURTLEMINT</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>72.38</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>68.02</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>69.31</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>UDAYJEW</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>169.12</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>160.44</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>168.73</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>167.02</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>UNIINFO</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>10.65</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>VCL</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>VEDAVAAG</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>22.08</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>22.14</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>VELJAN</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="n">
-        <v>2660</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>2603.8</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>2762.9</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>2790.7</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>VERANDA</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>32.76</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>32.76</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>VGCL</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>47.15</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>48.03</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>129.33</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>136.1</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>136.1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>VIDYAWIRES</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>100.42</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>95.03</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>98.03</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>VIVIMEDLAB</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>6.91</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>VIYASH</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>242.69</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>231.91</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>235.86</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>235.8</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>VMART</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>812.8200000000001</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>773.42</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>811.15</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>822.85</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>VOEPL</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>531.58</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>501.95</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>532.6</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>533.05</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>92.34999999999999</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>88.64</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>93.73999999999999</v>
+        <v>449.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>AARON</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>41.1</v>
+        <v>131.24</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>39.76</v>
+        <v>122.1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>43.12</v>
+        <v>132.36</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>43.12</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AGRITECH</t>
+          <t>ABANSENT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>96.03</v>
+        <v>31.32</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>88.05</v>
+        <v>28.78</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>95.7</v>
+        <v>33.18</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>95</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>181.7</v>
+        <v>382.47</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>171.51</v>
+        <v>371.77</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>185.11</v>
+        <v>380.25</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>184.5</v>
+        <v>380.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ANNU</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46.97</v>
+        <v>719.95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>44.8</v>
+        <v>688.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>47.01</v>
+        <v>705.6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>47.05</v>
+        <v>707.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ABSLBANETF</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1081.93</v>
+        <v>56.89</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1080.25</v>
+        <v>56.01</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1080.61</v>
+        <v>56.19</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1080.6</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AUGMONT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1278.37</v>
+        <v>1765.97</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1198.97</v>
+        <v>1706.57</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1337.8</v>
+        <v>1754</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1337.8</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>AGRITECH</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>147.43</v>
+        <v>101.03</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>136.41</v>
+        <v>91</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>148.6</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>150.79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>557.1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>593.95</v>
+        <v>547.02</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>597.15</v>
+        <v>551.85</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>597.09</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>ALLDIGI</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>120.57</v>
+        <v>796.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>118.88</v>
+        <v>779.12</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>121.12</v>
+        <v>801.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>120.8</v>
+        <v>798.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BAFNAPH</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>409.9</v>
+        <v>181.7</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>409.88</v>
+        <v>171.51</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>418</v>
+        <v>185.11</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>418</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>ANNU</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>913.9</v>
+        <v>48.05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>841.6799999999999</v>
+        <v>45.46</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>892.1</v>
+        <v>46.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>887.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>AONESILVER</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>265.91</v>
+        <v>8.42</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>255.37</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>272.43</v>
+        <v>8.35</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>272.43</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>ASIANHOTNR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>69.56999999999999</v>
+        <v>342.17</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>62.27</v>
+        <v>328.22</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>70.13</v>
+        <v>340.4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>69.8</v>
+        <v>334.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>AUGMONT</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>22.89</v>
+        <v>1339.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>21.74</v>
+        <v>1266.6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.54</v>
+        <v>1368.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>23.54</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CHOICEGOLD</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>146.67</v>
+        <v>150</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>144.9</v>
+        <v>140.34</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>147.08</v>
+        <v>149.28</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>147</v>
+        <v>151.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CPEDU</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>183.64</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>177.45</v>
+        <v>593.95</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>183.95</v>
+        <v>597.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>183.95</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1282.63</v>
+        <v>120.57</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1237.8</v>
+        <v>118.88</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1267.5</v>
+        <v>121.12</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1265.5</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>BAFNAPH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1603.83</v>
+        <v>418.07</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1559.9</v>
+        <v>418.05</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1621.9</v>
+        <v>426.35</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1620.5</v>
+        <v>426.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DHRUV</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>21.45</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20.09</v>
+        <v>9717.33</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.03</v>
+        <v>10034</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>23.03</v>
+        <v>10034</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.21</v>
+        <v>300.82</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>28.21</v>
+        <v>291.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>28.77</v>
+        <v>298.85</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>28.77</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1051.09</v>
+        <v>967.87</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1051.02</v>
+        <v>950.33</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1051.42</v>
+        <v>957.25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1051.41</v>
+        <v>957.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER</t>
+          <t>BANKBETA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.84</v>
+        <v>57.41</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.79</v>
+        <v>56.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.91</v>
+        <v>56.83</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.92</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>BANKIETF</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>327.83</v>
+        <v>56.93</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>319.15</v>
+        <v>56.09</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>330</v>
+        <v>56.38</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>330</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>BAYERCROP</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3.25</v>
+        <v>3543.23</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3.21</v>
+        <v>3409.03</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.25</v>
+        <v>3538.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.25</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>302.88</v>
+        <v>2219.43</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>287.9</v>
+        <v>2074.77</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>296.55</v>
+        <v>2332.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>295.05</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GLOBALE</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11.57</v>
+        <v>275.83</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10.81</v>
+        <v>264.7</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.01</v>
+        <v>286.05</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12</v>
+        <v>286.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>111.09</v>
+        <v>43.48</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>111.08</v>
+        <v>42.68</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>111.11</v>
+        <v>45.6</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>111.12</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GSEC10ADD</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>26.44</v>
+        <v>1575.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>26.39</v>
+        <v>1534.23</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>26.53</v>
+        <v>1570</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>26.53</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>553.37</v>
+        <v>155.62</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>542.58</v>
+        <v>138.49</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>556.65</v>
+        <v>157.01</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>556.65</v>
+        <v>157.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1081.32</v>
+        <v>58.24</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1081.3</v>
+        <v>53.01</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1081.65</v>
+        <v>63.25</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1081.67</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>BRAHMINFRA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>237.25</v>
+        <v>149.37</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>227.58</v>
+        <v>139.8</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>248.5</v>
+        <v>148.79</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>248.5</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>BSHSL</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>533.83</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>508.22</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>538.5</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>542</v>
+        <v>88.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HILINFRA</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>48.91</v>
+        <v>23.55</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46.22</v>
+        <v>22.56</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>49.59</v>
+        <v>23.07</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>50.2</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HINDCOMPOS</t>
+          <t>CARYSIL</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>428.18</v>
+        <v>1028.17</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>406.73</v>
+        <v>999.83</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>426.85</v>
+        <v>1017.3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>426</v>
+        <v>1021.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>CASHIETF</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1643</v>
+        <v>1083.21</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1594.63</v>
+        <v>1083.03</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1690.2</v>
+        <v>1083.45</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1690.2</v>
+        <v>1083.44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>648.75</v>
+        <v>135.03</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>629.4299999999999</v>
+        <v>129.98</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>643.45</v>
+        <v>136.27</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>643.5</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>16.54</v>
+        <v>1591.77</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>15.65</v>
+        <v>1552.8</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>16.9</v>
+        <v>1580.7</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>16.84</v>
+        <v>1580.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1017.52</v>
+        <v>1258.33</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>996.77</v>
+        <v>1213.47</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1023.4</v>
+        <v>1232</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1023.4</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ITADD</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>30.19</v>
+        <v>446.65</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>29.45</v>
+        <v>435.85</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>30.37</v>
+        <v>440.75</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>30.61</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>94.01000000000001</v>
+        <v>4213.87</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>88.55</v>
+        <v>3953.47</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>92.19</v>
+        <v>4134.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>17.38</v>
+        <v>10465.67</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>16.74</v>
+        <v>10081.67</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>17.17</v>
+        <v>10815</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16.91</v>
+        <v>10825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1299.33</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1245.8</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.08</v>
+        <v>1301.2</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.08</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>539.72</v>
+        <v>112.93</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>517.28</v>
+        <v>108.67</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>551.65</v>
+        <v>112.77</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>551.65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1148.3</v>
+        <v>231.22</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1148.28</v>
+        <v>223.58</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1148.65</v>
+        <v>231.17</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1148.64</v>
+        <v>230.85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>DBCORP</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1011.17</v>
+        <v>174.9</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1011.17</v>
+        <v>168.33</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1011.55</v>
+        <v>176.33</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1011.55</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>116.29</v>
+        <v>145.7</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>116.27</v>
+        <v>136.8</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>116.32</v>
+        <v>147.51</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>116.33</v>
+        <v>147.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1124.81</v>
+        <v>209.62</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1124.79</v>
+        <v>198.74</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1125.13</v>
+        <v>214.89</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1125.13</v>
+        <v>214.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1683.9</v>
+        <v>1631.87</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1622.13</v>
+        <v>1581.93</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1679.9</v>
+        <v>1618.3</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1666</v>
+        <v>1615.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1310.67</v>
+        <v>34.28</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1272.83</v>
+        <v>31.92</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1312.7</v>
+        <v>33.63</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1318</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>METROBRAND</t>
+          <t>DHRUV</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>849.1</v>
+        <v>23.14</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>819.52</v>
+        <v>20.88</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>864.65</v>
+        <v>22.19</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>870</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MLKFOOD</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>86.78</v>
+        <v>385</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>84.5</v>
+        <v>360.32</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>87.16</v>
+        <v>379.7</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>87.95</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2356</v>
+        <v>2384.4</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2292.13</v>
+        <v>2229.23</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2360</v>
+        <v>2370.1</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>2360</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>224.68</v>
+        <v>28.77</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>222.19</v>
+        <v>28.77</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>224.96</v>
+        <v>29.34</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>225.54</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>OILCOUNTUB</t>
+          <t>DYNPRO</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>84.56999999999999</v>
+        <v>231.92</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>84.56999999999999</v>
+        <v>224.09</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>86.25</v>
+        <v>233.72</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>86.25</v>
+        <v>233.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>49.58</v>
+        <v>7065.33</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>47.17</v>
+        <v>6859</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>50.06</v>
+        <v>7119</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>50.25</v>
+        <v>7119</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ONWARDTEC</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>305.37</v>
+        <v>1051.35</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>292.9</v>
+        <v>1051.28</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>307</v>
+        <v>1051.62</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>307</v>
+        <v>1051.62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ORIENTELEC</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>164.67</v>
+        <v>329.75</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>160.09</v>
+        <v>322.23</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>164.77</v>
+        <v>328.2</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>163.3</v>
+        <v>328.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PARNAXLAB</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>117.88</v>
+        <v>1385.97</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>111.89</v>
+        <v>1335.9</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>115.16</v>
+        <v>1401.2</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>115</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>GALAXYSURF</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2.29</v>
+        <v>2524.43</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>2.29</v>
+        <v>2415.77</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2.33</v>
+        <v>2532.5</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2.33</v>
+        <v>2511.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>14.21</v>
+        <v>709.87</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>13.42</v>
+        <v>690.37</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>14.81</v>
+        <v>723.45</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>14.75</v>
+        <v>723</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>116.83</v>
+        <v>2290.3</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>113.05</v>
+        <v>2212.07</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>116.98</v>
+        <v>2283</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>116.98</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1160.4</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1129.6</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1158</v>
+        <v>89.5</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1158</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RAJRILTD</t>
+          <t>GODIGIT</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>20.81</v>
+        <v>275.22</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>20.81</v>
+        <v>264.28</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>21.22</v>
+        <v>279.4</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>21.22</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO</t>
+          <t>GRANDOAK</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>366.02</v>
+        <v>38.67</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>340.52</v>
+        <v>34.71</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>357.45</v>
+        <v>37.25</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>357</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RELINFRA</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2378,22 +2378,22 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>56.53</v>
+        <v>111.11</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>54.65</v>
+        <v>111.1</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>59.29</v>
+        <v>111.13</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>59.29</v>
+        <v>111.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2407,22 +2407,22 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>6.4</v>
+        <v>7120</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>6.2</v>
+        <v>6912.83</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>6.63</v>
+        <v>7193.5</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>6.63</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SAMBHAAV</t>
+          <t>HATHWAY</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2436,22 +2436,22 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>5.91</v>
+        <v>9.81</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>5.06</v>
+        <v>9.27</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>5.68</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>5.77</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>283.13</v>
+        <v>709.27</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>269.72</v>
+        <v>695.38</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>282.6</v>
+        <v>704.9</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>284.65</v>
+        <v>704.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>HDFCGROWTH</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2494,22 +2494,22 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1059.3</v>
+        <v>109.94</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1059.28</v>
+        <v>107.96</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>1059.62</v>
+        <v>108.65</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1059.62</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SHIVAUM</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>554.33</v>
+        <v>558.5700000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>547.23</v>
+        <v>547.88</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>552.75</v>
+        <v>559.25</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>555</v>
+        <v>559.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>HDFCNIFIT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2552,22 +2552,22 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>201.81</v>
+        <v>30.62</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>198.28</v>
+        <v>29.72</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>203.98</v>
+        <v>30.25</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>204</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SIMPLXREA</t>
+          <t>HDFCPVTBAN</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>125.5</v>
+        <v>27.86</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>123.48</v>
+        <v>27.42</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>131.65</v>
+        <v>27.68</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>131.65</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>STERTOOLS</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>232.28</v>
+        <v>237.25</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>219.6</v>
+        <v>227.58</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>225.24</v>
+        <v>248.5</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>224.99</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SWANDEF</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2813.27</v>
+        <v>51.58</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2670.37</v>
+        <v>47.98</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2816.8</v>
+        <v>51.8</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2790</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TAKE</t>
+          <t>HINDCOMPOS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>12.73</v>
+        <v>435.88</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>12.54</v>
+        <v>417.03</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>13.35</v>
+        <v>435.85</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>13.35</v>
+        <v>441</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TARAPUR</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>14.22</v>
+        <v>463</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>13.19</v>
+        <v>452.88</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>16.58</v>
+        <v>463.4</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>16.58</v>
+        <v>463.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1524.87</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>1490.8</v>
+        <v>78.39</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1514.1</v>
+        <v>79.44</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1514.1</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TECHNVISN</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>4411.17</v>
+        <v>605.83</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>4223.33</v>
+        <v>582.73</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>4487.7</v>
+        <v>606.65</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>4451</v>
+        <v>609</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>4897.83</v>
+        <v>1198.2</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>4748.17</v>
+        <v>1160.27</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>4889.5</v>
+        <v>1192.7</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>4878</v>
+        <v>1195.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TOYAMSL</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.74</v>
+        <v>1622.67</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.72</v>
+        <v>1580.17</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.76</v>
+        <v>1592.2</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.76</v>
+        <v>1592.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>179.3</v>
+        <v>16.54</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>162.88</v>
+        <v>15.65</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>181.76</v>
+        <v>16.9</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>184.5</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>20.07</v>
+        <v>5.64</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>18.43</v>
+        <v>5.21</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>18.96</v>
+        <v>5.27</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>19</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>941.63</v>
+        <v>1025.78</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>933.52</v>
+        <v>1003.62</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>939.25</v>
+        <v>1020</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>INNOVANA</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2929,22 +2929,22 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>24.1</v>
+        <v>302.08</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>22.48</v>
+        <v>285.43</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>24.76</v>
+        <v>300.95</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>24.82</v>
+        <v>310.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>VASUPRADA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>99.3</v>
+        <v>464.35</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>96.81999999999999</v>
+        <v>452.48</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>99.5</v>
+        <v>462.7</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>99.5</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>VERANDA</t>
+          <t>ITADD</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -2987,22 +2987,22 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>32.78</v>
+        <v>30.55</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>32.1</v>
+        <v>29.62</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>34.39</v>
+        <v>30.69</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>34.39</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>VHLTD-RE1</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.51</v>
+        <v>31.83</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.44</v>
+        <v>30.82</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.68</v>
+        <v>31.46</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.68</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>VHLTD</t>
+          <t>ITIETF</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3045,22 +3045,22 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>136.85</v>
+        <v>32.07</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>132</v>
+        <v>30.97</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>142.9</v>
+        <v>31.5</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>142.9</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>VIRAT</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>416.65</v>
+        <v>476.3</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>376.35</v>
+        <v>464.65</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>435.4</v>
+        <v>469.2</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>425</v>
+        <v>467.85</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>828.75</v>
+        <v>256.87</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>789.4</v>
+        <v>246.63</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>821.95</v>
+        <v>255</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>817.5</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>KIOCL</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>94.98</v>
+        <v>368.7</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>90.56999999999999</v>
+        <v>345.68</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>97.52</v>
+        <v>376.75</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>371.55</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3161,16 +3161,3438 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>455.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>439.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>448.55</v>
+        <v>0.08</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>449.85</v>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>332.27</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>337.65</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>338.9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>LAHOTIOV</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>40.01</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>556.67</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>534.28</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>568</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>LIQGRWBEES</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>1059.05</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>1058.12</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>1059.14</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>1059.15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDADD</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1148.62</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1148.54</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>1148.82</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>1148.83</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDBETA</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>1011.17</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>1011.17</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>1011.55</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>1011.55</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDCASE</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>116.34</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>116.35</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1125.06</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>1125.04</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>1125.29</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>1125.29</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>263.72</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>257.18</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>262.7</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>262.7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>4066.67</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>3947.33</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>4018.9</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>4018.9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>2824.27</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>2764.07</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>2813</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>MADHUCON</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>316.03</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>135.91</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>130.87</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>130.72</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MAYURUNIQ</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>791.23</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>759.33</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>806.1</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>807.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>METROBRAND</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>864.83</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>829.85</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>847.9</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MICEL</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>36.08</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>MINDACORP</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>645.52</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>632.2</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>650.45</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>MLKFOOD</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>MODIS</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>407.43</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>417.95</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>MSUMI</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>NCLIND</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>165.73</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>162.79</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>162.2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>NDGL</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>2430.87</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>2311.33</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>2356.6</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>NESCO</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>1044.3</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>1022.87</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1036.5</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>1035.6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>NGIL</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>NIFMID150</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>224.68</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>224.96</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>225.54</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>NIFTYADD</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>238.85</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>234.68</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>235.31</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>235.22</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>NIFTYBETF</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>233.19</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>229.33</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>230.68</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>230.11</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>NTPCGREEN</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>93.95999999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>NUCLEUS</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>641.97</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>617.77</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>634.4</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>631.6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>333.57</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ONEPOINT</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>83.53</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ONWARDTEC</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>316.6</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>298.23</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>331.1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ORIENTELEC</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>172.28</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>172.29</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>PASUPTAC</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>PATELRMART</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>240.89</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>230.47</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>245.46</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>246.09</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>PAUSHAKLTD</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>715.63</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>679.13</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>724.35</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1681.2</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1607.93</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>PCJEWELLER</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>5749.33</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>5555</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>5787</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>5787</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>PGHH</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>6990</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>6831.83</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>6950.5</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>6976.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>PGIL</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>1316.7</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>1331.4</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>PLASTIBLEN</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>208.3</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>200.62</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>205.21</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>204.45</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>1182.47</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>1148.57</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>461.35</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>437.38</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>449.1</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>PRADPME</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>648.67</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>592.58</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>643.4</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>647.45</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>PRIMESECU</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>289.22</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>307.85</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>PSUBNKBEES</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>PTCIL</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>25153.33</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>24275</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>25845</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>PURVA</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>211.16</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>202.86</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>209.83</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>QUAL30IETF</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>19.65</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>QUALITY30</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>4574.9</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>4448.47</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>4555</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RAJRILTD</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>21.64</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RAMANEWS</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>30.66</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RAMBHAJO</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>353.45</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>375.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>2481.5</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>2547.1</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>2541.1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>RTSPOWR</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>112.78</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>124.66</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SABEVENTS</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SAFARI</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>1356.27</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>1288.97</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>1316.7</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>1314.2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SAICAPI</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>156.33</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>146.33</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>153.92</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>152.01</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SARVESHWAR</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SASTASUNDR</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>283.13</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>284.65</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SBFC</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>87.37</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>564.9299999999999</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>552.83</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>558.7</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>558.7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SBIETFIT</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>307.27</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>312.74</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>311.81</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>1059.54</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>1059.52</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>1059.77</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>1059.77</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SBISILVER</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>215.33</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>212.37</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>214.04</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>213.81</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SCANSTL</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>49.51</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>SETFNIFBK</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>568.29</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>561.13</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>563.9</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>564.6</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SGLRES</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>SGMART</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>778.1</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>742.02</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>764.1</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>762.25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>353.43</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>384.8</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>SHILGRAVQ</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>149.48</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>140.17</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>144.44</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>SHIVAMAUTO</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>18.09</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>22135</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>21570</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>21860</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>21860</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>815.58</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>802.05</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>823.5</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>SILVER1</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>21.21</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>SILVERAXIS</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>215.45</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>217.42</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>SILVERBEES</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>209.98</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>208.7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>SILVERCASE</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>22.13</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>SILVERETF</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>201.81</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>SILVERIETF</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>219.25</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>216.38</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>218.24</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>SIMPLXREA</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>131.76</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>129.35</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>138.19</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>138.19</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>939.27</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>881.63</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>968.25</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>966.95</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SUMMITSEC</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>1341.9</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>1309.47</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>1341.3</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>1354.2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>SVPGLOB</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>SWANDEF</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>2871.63</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>2717.03</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>2931.1</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>TARAPUR</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>3198.8</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>3048.8</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>3257</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>TCPLPACK</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>4354.8</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>4055.73</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>4417</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>4420.2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>TEAMGTY</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>235.67</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>244.03</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>249.95</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>30.83</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>TERAI</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>142.34</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>128.07</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>168.01</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>168.01</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>4938.67</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>4812.33</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>4890.5</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>70.98999999999999</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>TOYAMSL</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>TRAVELFOOD</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>1201.37</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>1169.33</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>TREJHARA</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>134.16</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>124.58</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>129.49</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>UDAYJEW</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>171.05</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>218.11</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>218.11</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>UNIECOM</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>1363.8</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>1323.17</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>1349.7</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>1349.7</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>1117.07</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>1087.97</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>1104.4</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>1104.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>UYFINCORP</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>25.89</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>264.78</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>264.9</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>264.9</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>VERANDA</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>VHL</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>3698.33</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>3536.7</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>3627.6</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>3576.1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD-RE1</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>VHLTD</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>143.01</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>137.53</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>150.04</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>150.04</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>2900.47</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>2788.13</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>2942.2</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>VTMLTD</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>97.98</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>WSI</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>59.77</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>WSTCSTPAPR</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>781.17</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>715.15</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>873.15</v>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>873.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>BNALTD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>237.25</v>
+        <v>383</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>227.58</v>
+        <v>373.23</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>248.5</v>
+        <v>393.65</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>248.5</v>
+        <v>393.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.54</v>
+        <v>237.25</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>15.65</v>
+        <v>227.58</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16.9</v>
+        <v>248.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>16.84</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>16.54</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.08</v>
+        <v>16.9</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>224.68</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>222.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>224.96</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>225.54</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6.4</v>
+        <v>224.68</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6.2</v>
+        <v>222.19</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6.63</v>
+        <v>224.96</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6.63</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>283.13</v>
+        <v>6.4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>269.72</v>
+        <v>6.2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>282.6</v>
+        <v>6.63</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>284.65</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>201.81</v>
+        <v>283.13</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>198.28</v>
+        <v>269.72</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>203.98</v>
+        <v>282.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>204</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,44 +812,73 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>941.63</v>
+        <v>201.81</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>933.52</v>
+        <v>198.28</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>939.25</v>
+        <v>203.98</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>VHLTD-RE1</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>0.68</v>
       </c>
     </row>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>48.61</v>
+        <v>455.6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>47.12</v>
+        <v>439.77</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>50.87</v>
+        <v>459.3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>50.87</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42.88</v>
+        <v>44.66</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>42.88</v>
+        <v>44.65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>44.62</v>
+        <v>46.85</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44.62</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="4">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.77</v>
+        <v>6.63</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5.23</v>
+        <v>6.09</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>6.78</v>
+        <v>7.45</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6.78</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="5">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2178.27</v>
+        <v>2204.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2145.63</v>
+        <v>2161.93</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2200</v>
+        <v>2223</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2200</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ASTRAZEN</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6075.83</v>
+        <v>1082.12</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5894</v>
+        <v>1082.09</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6079.5</v>
+        <v>1082.26</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6064</v>
+        <v>1082.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>ASIANTNE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>593.95</v>
+        <v>8.66</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>597.15</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>597.09</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>120.57</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>118.88</v>
+        <v>593.95</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>121.12</v>
+        <v>597.15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>120.8</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>236.73</v>
+        <v>120.57</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>230.83</v>
+        <v>118.88</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>237.38</v>
+        <v>121.12</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>237.38</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>136.85</v>
+        <v>60.98</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>133.08</v>
+        <v>60.98</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>138.04</v>
+        <v>63.95</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>138.04</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BCPL</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.5</v>
+        <v>2038.97</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>65.53</v>
+        <v>1993.23</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>68.38</v>
+        <v>2043.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>68</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>58.1</v>
+        <v>33.02</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>58.1</v>
+        <v>33.02</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>60.95</v>
+        <v>33.67</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>60.95</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>121.89</v>
+        <v>1053</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>118.59</v>
+        <v>1051.28</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>120.6</v>
+        <v>1053.13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>120.6</v>
+        <v>1053.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1091.86</v>
+        <v>287.38</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1084.67</v>
+        <v>276.57</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1084.88</v>
+        <v>289.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1084.89</v>
+        <v>289.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1961.87</v>
+        <v>860.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1916.03</v>
+        <v>844.37</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1951</v>
+        <v>860.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1951</v>
+        <v>860.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>COMFINTE</t>
+          <t>HALEOSLABS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>9.07</v>
+        <v>1618.7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>8.32</v>
+        <v>1553.73</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>10.18</v>
+        <v>1611.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.19</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1799.5</v>
+        <v>1417.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1738.8</v>
+        <v>1381.43</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1791.7</v>
+        <v>1421.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1785.1</v>
+        <v>1421.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>HDFCNIFIT</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>231.04</v>
+        <v>34.6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>225.15</v>
+        <v>33.61</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>229.84</v>
+        <v>34.17</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>228.35</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1243.33</v>
+        <v>237.25</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1224.53</v>
+        <v>227.58</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1244.5</v>
+        <v>248.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1244.5</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32.37</v>
+        <v>600.52</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>32.37</v>
+        <v>575.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>33.01</v>
+        <v>591.45</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>33.01</v>
+        <v>590.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GSEC10ADD</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>26.14</v>
+        <v>340.83</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>26.14</v>
+        <v>299.77</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>26.29</v>
+        <v>331.75</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>26.29</v>
+        <v>353.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10.66</v>
+        <v>16.54</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.16</v>
+        <v>15.65</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>10.64</v>
+        <v>16.9</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10.79</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HALEOSLABS</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1591.7</v>
+        <v>1918.6</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1532.2</v>
+        <v>1826.27</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1583.8</v>
+        <v>1903.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1585</v>
+        <v>1899.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1402.83</v>
+        <v>35.95</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1365.87</v>
+        <v>35.01</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1424.2</v>
+        <v>35.49</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1424.2</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HDFCNIFIT</t>
+          <t>ITADD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1221,19 +1221,19 @@
         <v>34.37</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>33.21</v>
+        <v>33.58</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>34.4</v>
+        <v>33.99</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.6</v>
+        <v>33.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HDFCPSUBK</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>83.73</v>
+        <v>36.17</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>81.98</v>
+        <v>34.95</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>83.05</v>
+        <v>35.56</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>83.08</v>
+        <v>35.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>237.25</v>
+        <v>1.69</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>227.58</v>
+        <v>1.48</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>248.5</v>
+        <v>1.72</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>248.5</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ICDSLTD</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>48.77</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>50.74</v>
+        <v>0.08</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>49.75</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>16.54</v>
+        <v>223.63</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>15.65</v>
+        <v>208.39</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.9</v>
+        <v>217.49</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16.84</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>35.74</v>
+        <v>1150.38</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>34.36</v>
+        <v>1150.3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>35.85</v>
+        <v>1150.48</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>35.83</v>
+        <v>1150.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>35.76</v>
+        <v>1013.03</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>34.55</v>
+        <v>1013.02</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>35.95</v>
+        <v>1013.17</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>35.97</v>
+        <v>1013.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1246.3</v>
+        <v>116.5</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1207.17</v>
+        <v>116.48</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1222.9</v>
+        <v>116.51</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1222.9</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1714.6</v>
+        <v>1126.72</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1675.6</v>
+        <v>1126.71</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1706.9</v>
+        <v>1126.87</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1706</v>
+        <v>1126.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1357.7</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1291</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.08</v>
+        <v>1420.5</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.08</v>
+        <v>1422.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LAGNAM</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>91.62</v>
+        <v>2565.73</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>84.67</v>
+        <v>2481.17</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>93.84</v>
+        <v>2499.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>98</v>
+        <v>2499.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1150.16</v>
+        <v>72.45</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1150.08</v>
+        <v>71.09</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1150.32</v>
+        <v>72.38</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1150.31</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1012.84</v>
+        <v>224.68</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1012.83</v>
+        <v>222.19</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1013.02</v>
+        <v>224.96</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1013.02</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>116.48</v>
+        <v>454.05</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>116.46</v>
+        <v>446.97</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>116.49</v>
+        <v>456.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>116.49</v>
+        <v>456.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1126.52</v>
+        <v>19.29</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1126.5</v>
+        <v>17.35</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1126.7</v>
+        <v>18.07</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1126.7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>QUINTEGRA</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1293.83</v>
+        <v>2.34</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1227.3</v>
+        <v>2.34</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1355.2</v>
+        <v>2.45</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1357.4</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1857.5</v>
+        <v>6.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1782.7</v>
+        <v>6.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1847.2</v>
+        <v>6.63</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1854</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MICEL</t>
+          <t>SALSTEEL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>36.63</v>
+        <v>86.47</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>35.28</v>
+        <v>79.8</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>38.05</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>38.05</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MIDWESTLTD</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1118.47</v>
+        <v>515.42</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1040.72</v>
+        <v>500.87</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1137.2</v>
+        <v>508.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1140</v>
+        <v>508.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NECLIFE</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>11.07</v>
+        <v>283.13</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>10.67</v>
+        <v>269.72</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>11.29</v>
+        <v>282.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>11.35</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>224.68</v>
+        <v>1061.22</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>222.19</v>
+        <v>1061.15</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>224.96</v>
+        <v>1061.31</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>225.54</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>892.22</v>
+        <v>18.3</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>835.83</v>
+        <v>15.79</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>870.85</v>
+        <v>17.99</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>874.95</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>451.17</v>
+        <v>201.81</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>444.48</v>
+        <v>198.28</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>454</v>
+        <v>203.98</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>454</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>226.15</v>
+        <v>3.32</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>222.99</v>
+        <v>3.17</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>225.62</v>
+        <v>3.34</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>225.62</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ORIRAIL</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>125.47</v>
+        <v>582.4</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>114.12</v>
+        <v>545</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>123.15</v>
+        <v>581.3</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>120.5</v>
+        <v>579.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>OSWALAGRO</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>41.23</v>
+        <v>3879.73</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>34.24</v>
+        <v>3791.23</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>37.07</v>
+        <v>3846.8</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>37.18</v>
+        <v>3846.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PARACABLES</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>66.01000000000001</v>
+        <v>35.42</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>59.86</v>
+        <v>34.44</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>35.04</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PASHUPATI</t>
+          <t>TRANSWORLD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>90.25</v>
+        <v>191.01</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>87.44</v>
+        <v>171.67</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>94.17</v>
+        <v>184.56</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>18.31</v>
+        <v>941.63</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>16.47</v>
+        <v>933.52</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>18.51</v>
+        <v>939.25</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>18.65</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,22 +2059,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>296.6</v>
+        <v>0.51</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>291.75</v>
+        <v>0.44</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>295</v>
+        <v>0.68</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>295</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PIGL</t>
+          <t>VIRAT</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>97.55</v>
+        <v>407.55</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>382.52</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>95.11</v>
+        <v>398.5</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>95.36</v>
+        <v>397.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PRISMX</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2117,973 +2117,16 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.74</v>
+        <v>189.49</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.62</v>
+        <v>184.72</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.7</v>
+        <v>190.41</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>PSUBANK</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>82.81999999999999</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>82.47</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>82.84</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>PSUBANKADD</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>83.76000000000001</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>81.77</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>83.31</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>82.88</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>PSUBNKBEES</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>92.34999999999999</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>90.55</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>91.95</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>PSUBNKIETF</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>83.95999999999999</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>82.44</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>83.27</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>83.11</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>QUINT</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>60.51</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>60.62</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>QUINTEGRA</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>RISHABH</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>710.42</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>675.4</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>701.95</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>700.1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>SABEVENTS</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>512.3</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>496.03</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>510.4</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>1060.97</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>1060.95</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1061.15</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>1061.17</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SHANKESH</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>102.73</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>96.62</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>101.85</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>103.11</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>18.02</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>SMARTLINK</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>247.41</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>214.29</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>225.1</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>224.9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>SMLT</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>74.06</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SOUTHBANK</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SPCENET</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>904.87</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>839.45</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>842.9</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>842.9</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SWARNSAR</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>3865</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>3747.33</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>3848.6</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>3848.6</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>2505</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>2428.1</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>2529</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>35.06</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TOKYOPLAST</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>77.66</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>71.66</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>77.73</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>78.39</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRANSWORLD</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>176.34</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>164.07</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>192.63</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>192.63</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>UDAYJEW</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>239.83</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>221.01</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>229.96</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>181.03</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>174.42</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>VCL</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>VEEGALAND</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>134.7</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>133.17</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>132.93</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>VISACHROME</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>33.74</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>187.1</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>178.4</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>189.17</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>189.17</v>
+        <v>190.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
+          <t>ABMINTLLTD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>455.6</v>
+        <v>46.89</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>439.77</v>
+        <v>46.88</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>459.3</v>
+        <v>49.19</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>460</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABMINTLLTD</t>
+          <t>ALGOQUANT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.66</v>
+        <v>77.13</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>44.65</v>
+        <v>71.48</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46.85</v>
+        <v>74.73</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>46.85</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AGOL</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.63</v>
+        <v>181.7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6.09</v>
+        <v>171.51</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7.45</v>
+        <v>185.11</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7.45</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>181.7</v>
+        <v>2227.73</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>171.51</v>
+        <v>2185.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>185.11</v>
+        <v>2235</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>184.5</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2204.4</v>
+        <v>1082.39</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2161.93</v>
+        <v>1082.36</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2223</v>
+        <v>1082.74</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2223</v>
+        <v>1082.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1082.12</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1082.09</v>
+        <v>593.95</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1082.26</v>
+        <v>597.15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1082.26</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ASIANTNE</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>120.57</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>8.66</v>
+        <v>118.88</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>121.12</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>593.95</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>597.15</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>597.09</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>120.57</v>
+        <v>644.9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>118.88</v>
+        <v>603.73</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>121.12</v>
+        <v>623.35</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>120.8</v>
+        <v>620.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>60.98</v>
+        <v>2052.83</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>60.98</v>
+        <v>2003.97</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>63.95</v>
+        <v>2051.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>63.95</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2038.97</v>
+        <v>33.67</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1993.23</v>
+        <v>33.67</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2043.8</v>
+        <v>34.34</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2042</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>33.02</v>
+        <v>1053.25</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>33.02</v>
+        <v>1053.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>33.67</v>
+        <v>1053.6</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>33.67</v>
+        <v>1053.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1053</v>
+        <v>291.43</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1051.28</v>
+        <v>278.57</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1053.13</v>
+        <v>290.4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1053.13</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>287.38</v>
+        <v>1439.87</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>276.57</v>
+        <v>1400.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>289.4</v>
+        <v>1422.2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>289.5</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>860.9</v>
+        <v>237.25</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>844.37</v>
+        <v>227.58</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>860.2</v>
+        <v>248.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>860.2</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HALEOSLABS</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1618.7</v>
+        <v>357.55</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1553.73</v>
+        <v>333.52</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1611.3</v>
+        <v>381.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1622</v>
+        <v>375.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1417.2</v>
+        <v>16.54</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1381.43</v>
+        <v>15.65</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1421.7</v>
+        <v>16.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1421.7</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HDFCNIFIT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>34.6</v>
+        <v>36.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.61</v>
+        <v>35.21</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>34.17</v>
+        <v>35.56</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>34.1</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>ITAXIS</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>237.25</v>
+        <v>360.22</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>227.58</v>
+        <v>348.67</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>248.5</v>
+        <v>353.65</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>248.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>ITBEES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>600.52</v>
+        <v>36.59</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>575.03</v>
+        <v>35.25</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>591.45</v>
+        <v>35.62</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>590.9</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>JINDALPHOT</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>340.83</v>
+        <v>1064.93</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>299.77</v>
+        <v>1025.5</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>331.75</v>
+        <v>1055.7</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>353.45</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>16.54</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15.65</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16.9</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16.84</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1918.6</v>
+        <v>1150.66</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1826.27</v>
+        <v>1150.57</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1903.5</v>
+        <v>1150.98</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1899.8</v>
+        <v>1150.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>35.95</v>
+        <v>1013.29</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>35.01</v>
+        <v>1013.27</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>35.49</v>
+        <v>1013.65</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>35.47</v>
+        <v>1013.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ITADD</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>34.37</v>
+        <v>1104.48</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>33.58</v>
+        <v>1103.59</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>33.99</v>
+        <v>1104.63</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>33.89</v>
+        <v>1104.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>36.17</v>
+        <v>116.53</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>34.95</v>
+        <v>116.51</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>35.56</v>
+        <v>116.55</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>35.55</v>
+        <v>116.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.69</v>
+        <v>1126.98</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.48</v>
+        <v>1126.97</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.72</v>
+        <v>1127.35</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.79</v>
+        <v>1127.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>NIFMID150</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>224.68</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>222.19</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.08</v>
+        <v>224.96</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.08</v>
+        <v>225.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>ORIENTHOT</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>223.63</v>
+        <v>154.29</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>208.39</v>
+        <v>147.89</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>217.49</v>
+        <v>151.76</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>216</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1150.38</v>
+        <v>2.68</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1150.3</v>
+        <v>2.62</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1150.48</v>
+        <v>2.73</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1150.49</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>QUINTEGRA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1013.03</v>
+        <v>2.45</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1013.02</v>
+        <v>2.45</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1013.17</v>
+        <v>2.57</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1013.17</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>SABEVENTS</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>116.5</v>
+        <v>6.4</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>116.48</v>
+        <v>6.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>116.51</v>
+        <v>6.63</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>116.51</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1126.72</v>
+        <v>1411.97</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1126.71</v>
+        <v>1371.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1126.87</v>
+        <v>1395.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1126.88</v>
+        <v>1391.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1357.7</v>
+        <v>151.47</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1291</v>
+        <v>144.82</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1420.5</v>
+        <v>152.85</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1422.9</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SASKEN</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2565.73</v>
+        <v>1786.83</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2481.17</v>
+        <v>1627.37</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2499.5</v>
+        <v>1788.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2499.5</v>
+        <v>1799.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>SASTASUNDR</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>72.45</v>
+        <v>283.13</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>71.09</v>
+        <v>269.72</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>72.38</v>
+        <v>282.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>72.38</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>224.68</v>
+        <v>1061.48</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>222.19</v>
+        <v>1061.41</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>224.96</v>
+        <v>1061.78</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>225.54</v>
+        <v>1061.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>SILVERETF</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>454.05</v>
+        <v>201.81</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>446.97</v>
+        <v>198.28</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>456.9</v>
+        <v>203.98</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>456.9</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>19.29</v>
+        <v>476.4</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>17.35</v>
+        <v>452.05</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18.07</v>
+        <v>463.15</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>18</v>
+        <v>466.65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QUINTEGRA</t>
+          <t>UTISENSETF</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.34</v>
+        <v>941.63</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.34</v>
+        <v>933.52</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.45</v>
+        <v>939.25</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.45</v>
+        <v>938.3200000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>VHLTD-RE1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,451 +1682,16 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>6.4</v>
+        <v>0.51</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>6.2</v>
+        <v>0.44</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>6.63</v>
+        <v>0.68</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>6.63</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SALSTEEL</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>86.47</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>83.06999999999999</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>82.2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>515.42</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>500.87</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>508.35</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SASTASUNDR</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>283.13</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>269.72</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>282.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>284.65</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>1061.22</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1061.15</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>1061.31</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>1061.33</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>18.14</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>SILVERETF</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>201.81</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>198.28</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SPCENET</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>582.4</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>545</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>581.3</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>579.8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>3879.73</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>3791.23</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>3846.8</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>3846.8</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRANSWORLD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>191.01</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>171.67</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>184.56</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>UTISENSETF</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>941.63</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>933.52</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>939.25</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>938.3200000000001</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>VHLTD-RE1</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F55" s="3" t="n">
         <v>0.68</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>VIRAT</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>407.55</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>382.52</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>398.5</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>397.05</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>189.49</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>184.72</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>190.41</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>190.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_output.xlsx
+++ b/data/uptrend_output.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABMINTLLTD</t>
+          <t>3BBLACKBIO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46.89</v>
+        <v>1417.7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46.88</v>
+        <v>1311.17</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>49.19</v>
+        <v>1392.7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>49.19</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ALGOQUANT</t>
+          <t>ABMINTLLTD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>77.13</v>
+        <v>49.23</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>71.48</v>
+        <v>49.22</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>74.73</v>
+        <v>51.64</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>75.2</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMIRCHAND</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>181.7</v>
+        <v>1750.03</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>171.51</v>
+        <v>1702.4</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>185.11</v>
+        <v>1753.2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>184.5</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2227.73</v>
+        <v>3366.6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2185.5</v>
+        <v>3228.07</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2235</v>
+        <v>3381</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2235</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AKASH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1082.39</v>
+        <v>23.74</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1082.36</v>
+        <v>22.56</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1082.74</v>
+        <v>24.13</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1082.76</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AXISBNKETF</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>599.1900000000001</v>
+        <v>5021.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>593.95</v>
+        <v>4855.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>597.15</v>
+        <v>5030</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>597.09</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AXISCETF</t>
+          <t>AMIRCHAND</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>120.57</v>
+        <v>181.7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>118.88</v>
+        <v>171.51</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>121.12</v>
+        <v>185.11</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>120.8</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>64</v>
+        <v>1139.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>64</v>
+        <v>1033.77</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>1188.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>644.9</v>
+        <v>1082.65</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>603.73</v>
+        <v>1082.63</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>623.35</v>
+        <v>1082.9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>620.5</v>
+        <v>1082.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2052.83</v>
+        <v>7744</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2003.97</v>
+        <v>7549.67</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2051.1</v>
+        <v>7844</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2050</v>
+        <v>7844</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>ARMEE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>33.67</v>
+        <v>274.75</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>33.67</v>
+        <v>255.37</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>34.34</v>
+        <v>279.7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>34.34</v>
+        <v>279.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>AXISBNKETF</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1053.25</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1053.23</v>
+        <v>593.95</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1053.6</v>
+        <v>597.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1053.6</v>
+        <v>597.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>AXISCETF</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>291.43</v>
+        <v>120.57</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>278.57</v>
+        <v>118.88</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>290.4</v>
+        <v>121.12</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>293</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>BCONCEPTS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1439.87</v>
+        <v>150.9</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1400.1</v>
+        <v>134.9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1422.2</v>
+        <v>153.62</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1422.2</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>237.25</v>
+        <v>67.17</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>227.58</v>
+        <v>67.17</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>248.5</v>
+        <v>70.45</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>248.5</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>357.55</v>
+        <v>2278.13</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>333.52</v>
+        <v>2193.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>381.15</v>
+        <v>2273.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>375.4</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>INFIBEAM</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>16.54</v>
+        <v>1528.03</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15.65</v>
+        <v>1414.6</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>16.9</v>
+        <v>1521.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.84</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>36.4</v>
+        <v>1342.97</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35.21</v>
+        <v>1313.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>35.56</v>
+        <v>1355</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>35.47</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITAXIS</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>360.22</v>
+        <v>2067.97</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>348.67</v>
+        <v>2014.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>353.65</v>
+        <v>2041.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>350</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITBEES</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>36.59</v>
+        <v>1242.73</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>35.25</v>
+        <v>1176.17</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>35.62</v>
+        <v>1242.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>35.7</v>
+        <v>1237.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>JINDALPHOT</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1064.93</v>
+        <v>33.67</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1025.5</v>
+        <v>33.67</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1055.7</v>
+        <v>34.34</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1053</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.08</v>
+        <v>5.51</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.08</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1150.66</v>
+        <v>1053.72</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1150.57</v>
+        <v>1053.61</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1150.98</v>
+        <v>1054.4</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1150.99</v>
+        <v>1054.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1013.29</v>
+        <v>300.98</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1013.27</v>
+        <v>283.07</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1013.65</v>
+        <v>300.25</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1013.65</v>
+        <v>299.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1104.48</v>
+        <v>733.47</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1103.59</v>
+        <v>712.98</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1104.63</v>
+        <v>733</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1104.63</v>
+        <v>734.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>GICL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>116.53</v>
+        <v>27.49</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>116.51</v>
+        <v>25.25</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>116.55</v>
+        <v>28.17</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>116.57</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1126.98</v>
+        <v>2915.23</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1126.97</v>
+        <v>2848</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1127.35</v>
+        <v>2950</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1127.34</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NIFMID150</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>224.68</v>
+        <v>111.46</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>222.19</v>
+        <v>111.31</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>224.96</v>
+        <v>111.34</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>225.54</v>
+        <v>111.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ORIENTHOT</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>154.29</v>
+        <v>7158</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>147.89</v>
+        <v>6389.17</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>151.76</v>
+        <v>6977</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>GSPLTRANS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.68</v>
+        <v>117.63</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2.62</v>
+        <v>108.93</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2.73</v>
+        <v>114.13</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.73</v>
+        <v>115.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUINTEGRA</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2.45</v>
+        <v>237.25</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.45</v>
+        <v>227.58</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2.57</v>
+        <v>248.5</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2.57</v>
+        <v>248.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SABEVENTS</t>
+          <t>HILINFRA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>6.4</v>
+        <v>58.15</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>6.2</v>
+        <v>53.62</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>6.63</v>
+        <v>61.53</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1411.97</v>
+        <v>377.73</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1371.5</v>
+        <v>350.77</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1395.3</v>
+        <v>385.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1391.4</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>151.47</v>
+        <v>386.18</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>144.82</v>
+        <v>375.92</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>152.85</v>
+        <v>389</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>153.5</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SASKEN</t>
+          <t>INFIBEAM</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1786.83</v>
+        <v>16.54</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1627.37</v>
+        <v>15.65</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1788.3</v>
+        <v>16.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1799.2</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SASTASUNDR</t>
+          <t>JINDALPHOT</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>283.13</v>
+        <v>1086.67</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>269.72</v>
+        <v>1040</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>282.6</v>
+        <v>1102</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>284.65</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>JUBLCPL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1061.48</v>
+        <v>1873</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1061.41</v>
+        <v>1720.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1061.78</v>
+        <v>1920.8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1061.78</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SILVERETF</t>
+          <t>JYOTISTRUC</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>201.81</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>198.28</v>
+        <v>8.17</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>203.98</v>
+        <v>9.01</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>204</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>476.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>452.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>463.15</v>
+        <v>0.08</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>466.65</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>UTISENSETF</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,45 +1653,828 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>941.63</v>
+        <v>1061.03</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>933.52</v>
+        <v>1060.85</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>939.25</v>
+        <v>1061.29</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>938.3200000000001</v>
+        <v>1061.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>LIQUIDBETA</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1013.29</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1013.27</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1013.65</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1013.65</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDCASE</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>116.56</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>116.58</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>116.59</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>LIQUIDSHRI</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1127.26</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1127.24</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1127.51</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1127.51</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>11255</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>11029</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>11220</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>11220</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>826.7</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>804.02</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>835</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MOREPENLAB</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>126.01</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>NIFMID150</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>224.68</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>224.96</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>225.54</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>OPTIFIN</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>106.63</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>104.02</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PASHUPATI</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>109.87</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>109.93</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>QUINTEGRA</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SABEVENTS</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SADBHAV</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SAMHI</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>153.95</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>153.91</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>152.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SASKEN</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1816.77</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1679.73</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1834.1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SASTASUNDR</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>283.13</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>269.72</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>284.65</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1061.74</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1061.68</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1061.95</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1061.94</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>343</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>350.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SILVERETF</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>201.81</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>153.27</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>143.93</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>154.31</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>154.77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>TTML</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>40.05</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>11068.67</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>10793.67</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>11180</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>11180</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>UTISENSETF</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>941.63</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>933.52</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>939.25</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>938.3200000000001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>UYFINCORP</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>VGCL</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>55.38</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>VHLTD-RE1</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1404.7</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1354.77</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1395.8</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
